--- a/AG_ONE_Team_Tracker_2026.xlsx
+++ b/AG_ONE_Team_Tracker_2026.xlsx
@@ -13,7 +13,8 @@
     <sheet name="Sprint Tracker" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Member Performance" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="2026 Targets" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="How To Use" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="External Projects" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="How To Use" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -162,7 +163,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -233,6 +234,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00EC4899"/>
         <bgColor rgb="00EC4899"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007C3AED"/>
+        <bgColor rgb="007C3AED"/>
       </patternFill>
     </fill>
     <fill>
@@ -319,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -361,6 +368,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -370,10 +380,10 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -382,10 +392,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -424,10 +434,10 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -466,6 +476,9 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -473,8 +486,8 @@
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1197,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1209,9 +1222,12 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -1231,11 +1247,14 @@
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="2" t="n"/>
       <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Shows which member belongs to which team  •  Shared resources highlighted</t>
+          <t>Internal teams + External / Outsource projects  •  Shared &amp; external resources highlighted</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1249,6 +1268,9 @@
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1296,17 +1318,32 @@
           <t>Pulse</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>Total Teams</t>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t>⬡ Form 2</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
           <t>Availability %</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1322,7 +1359,7 @@
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr"/>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="D4" s="22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1332,15 +1369,22 @@
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr"/>
       <c r="I4" s="13" t="inlineStr"/>
-      <c r="J4" s="13" t="n">
+      <c r="J4" s="13" t="inlineStr"/>
+      <c r="K4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="L4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="13" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="L4" s="13" t="inlineStr"/>
+      <c r="O4" s="13" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -1354,7 +1398,7 @@
       <c r="C5" s="9" t="inlineStr"/>
       <c r="D5" s="9" t="inlineStr"/>
       <c r="E5" s="9" t="inlineStr"/>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1362,21 +1406,28 @@
       <c r="G5" s="9" t="inlineStr"/>
       <c r="H5" s="9" t="inlineStr"/>
       <c r="I5" s="9" t="inlineStr"/>
-      <c r="J5" s="9" t="n">
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="L5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr"/>
+      <c r="O5" s="9" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Fatin</t>
         </is>
@@ -1385,26 +1436,33 @@
       <c r="D6" s="13" t="inlineStr"/>
       <c r="E6" s="13" t="inlineStr"/>
       <c r="F6" s="13" t="inlineStr"/>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr"/>
-      <c r="I6" s="25" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J6" s="13" t="n">
+      <c r="J6" s="13" t="inlineStr"/>
+      <c r="K6" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="13" t="inlineStr">
+      <c r="L6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="L6" s="23" t="inlineStr">
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t>Shared</t>
         </is>
@@ -1414,17 +1472,17 @@
       <c r="A7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Geena</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1434,15 +1492,22 @@
       <c r="G7" s="9" t="inlineStr"/>
       <c r="H7" s="9" t="inlineStr"/>
       <c r="I7" s="9" t="inlineStr"/>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="9" t="inlineStr"/>
+      <c r="K7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="L7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" s="9" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="L7" s="26" t="inlineStr">
+      <c r="O7" s="27" t="inlineStr">
         <is>
           <t>Shared</t>
         </is>
@@ -1452,7 +1517,7 @@
       <c r="A8" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Hanis</t>
         </is>
@@ -1461,26 +1526,33 @@
       <c r="D8" s="13" t="inlineStr"/>
       <c r="E8" s="13" t="inlineStr"/>
       <c r="F8" s="13" t="inlineStr"/>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J8" s="13" t="n">
+      <c r="J8" s="13" t="inlineStr"/>
+      <c r="K8" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K8" s="13" t="inlineStr">
+      <c r="L8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="L8" s="23" t="inlineStr">
+      <c r="O8" s="24" t="inlineStr">
         <is>
           <t>Shared</t>
         </is>
@@ -1490,7 +1562,7 @@
       <c r="A9" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Hema</t>
         </is>
@@ -1500,25 +1572,32 @@
       <c r="E9" s="9" t="inlineStr"/>
       <c r="F9" s="9" t="inlineStr"/>
       <c r="G9" s="9" t="inlineStr"/>
-      <c r="H9" s="28" t="inlineStr">
+      <c r="H9" s="29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="I9" s="26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J9" s="9" t="n">
+      <c r="J9" s="9" t="inlineStr"/>
+      <c r="K9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="L9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="L9" s="26" t="inlineStr">
+      <c r="O9" s="27" t="inlineStr">
         <is>
           <t>Shared</t>
         </is>
@@ -1534,7 +1613,7 @@
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr"/>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1544,15 +1623,22 @@
       <c r="G10" s="13" t="inlineStr"/>
       <c r="H10" s="13" t="inlineStr"/>
       <c r="I10" s="13" t="inlineStr"/>
-      <c r="J10" s="13" t="n">
+      <c r="J10" s="13" t="inlineStr"/>
+      <c r="K10" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K10" s="13" t="inlineStr">
+      <c r="L10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="L10" s="13" t="inlineStr"/>
+      <c r="O10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -1566,7 +1652,7 @@
       <c r="C11" s="9" t="inlineStr"/>
       <c r="D11" s="9" t="inlineStr"/>
       <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1574,49 +1660,63 @@
       <c r="G11" s="9" t="inlineStr"/>
       <c r="H11" s="9" t="inlineStr"/>
       <c r="I11" s="9" t="inlineStr"/>
-      <c r="J11" s="9" t="n">
+      <c r="J11" s="9" t="inlineStr"/>
+      <c r="K11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="L11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="L11" s="9" t="inlineStr"/>
+      <c r="O11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Loc</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr"/>
       <c r="D12" s="13" t="inlineStr"/>
-      <c r="E12" s="29" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr"/>
       <c r="G12" s="13" t="inlineStr"/>
-      <c r="H12" s="28" t="inlineStr">
+      <c r="H12" s="29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="I12" s="13" t="inlineStr"/>
-      <c r="J12" s="13" t="n">
+      <c r="J12" s="13" t="inlineStr"/>
+      <c r="K12" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K12" s="13" t="inlineStr">
+      <c r="L12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" s="13" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="L12" s="23" t="inlineStr">
+      <c r="O12" s="24" t="inlineStr">
         <is>
           <t>Shared</t>
         </is>
@@ -1635,28 +1735,35 @@
       <c r="D13" s="9" t="inlineStr"/>
       <c r="E13" s="9" t="inlineStr"/>
       <c r="F13" s="9" t="inlineStr"/>
-      <c r="G13" s="24" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr"/>
       <c r="I13" s="9" t="inlineStr"/>
-      <c r="J13" s="9" t="n">
+      <c r="J13" s="9" t="inlineStr"/>
+      <c r="K13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="L13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="9" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="L13" s="9" t="inlineStr"/>
+      <c r="O13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Majed</t>
         </is>
@@ -1666,25 +1773,32 @@
       <c r="E14" s="13" t="inlineStr"/>
       <c r="F14" s="13" t="inlineStr"/>
       <c r="G14" s="13" t="inlineStr"/>
-      <c r="H14" s="28" t="inlineStr">
+      <c r="H14" s="29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I14" s="25" t="inlineStr">
+      <c r="I14" s="26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J14" s="13" t="n">
+      <c r="J14" s="13" t="inlineStr"/>
+      <c r="K14" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K14" s="13" t="inlineStr">
+      <c r="L14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" s="13" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="L14" s="23" t="inlineStr">
+      <c r="O14" s="24" t="inlineStr">
         <is>
           <t>Shared</t>
         </is>
@@ -1694,17 +1808,17 @@
       <c r="A15" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>Nastaran</t>
         </is>
       </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1714,15 +1828,22 @@
       <c r="G15" s="9" t="inlineStr"/>
       <c r="H15" s="9" t="inlineStr"/>
       <c r="I15" s="9" t="inlineStr"/>
-      <c r="J15" s="9" t="n">
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="L15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="L15" s="26" t="inlineStr">
+      <c r="O15" s="27" t="inlineStr">
         <is>
           <t>Shared</t>
         </is>
@@ -1743,54 +1864,68 @@
       <c r="F16" s="13" t="inlineStr"/>
       <c r="G16" s="13" t="inlineStr"/>
       <c r="H16" s="13" t="inlineStr"/>
-      <c r="I16" s="25" t="inlineStr">
+      <c r="I16" s="26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J16" s="13" t="n">
+      <c r="J16" s="13" t="inlineStr"/>
+      <c r="K16" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K16" s="13" t="inlineStr">
+      <c r="L16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" s="13" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="L16" s="13" t="inlineStr"/>
+      <c r="O16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>Ricky</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr"/>
       <c r="D17" s="9" t="inlineStr"/>
-      <c r="E17" s="29" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr"/>
       <c r="G17" s="9" t="inlineStr"/>
-      <c r="H17" s="28" t="inlineStr">
+      <c r="H17" s="29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr"/>
-      <c r="J17" s="9" t="n">
+      <c r="J17" s="9" t="inlineStr"/>
+      <c r="K17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="L17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" s="9" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="L17" s="26" t="inlineStr">
+      <c r="O17" s="27" t="inlineStr">
         <is>
           <t>Shared</t>
         </is>
@@ -1809,22 +1944,29 @@
       <c r="D18" s="13" t="inlineStr"/>
       <c r="E18" s="13" t="inlineStr"/>
       <c r="F18" s="13" t="inlineStr"/>
-      <c r="G18" s="24" t="inlineStr">
+      <c r="G18" s="25" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr"/>
       <c r="I18" s="13" t="inlineStr"/>
-      <c r="J18" s="13" t="n">
+      <c r="J18" s="13" t="inlineStr"/>
+      <c r="K18" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="K18" s="13" t="inlineStr">
+      <c r="L18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="13" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="L18" s="13" t="inlineStr"/>
+      <c r="O18" s="13" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
@@ -1838,7 +1980,7 @@
       <c r="C19" s="9" t="inlineStr"/>
       <c r="D19" s="9" t="inlineStr"/>
       <c r="E19" s="9" t="inlineStr"/>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -1846,49 +1988,63 @@
       <c r="G19" s="9" t="inlineStr"/>
       <c r="H19" s="9" t="inlineStr"/>
       <c r="I19" s="9" t="inlineStr"/>
-      <c r="J19" s="9" t="n">
+      <c r="J19" s="9" t="inlineStr"/>
+      <c r="K19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="L19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="L19" s="9" t="inlineStr"/>
+      <c r="O19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>Than</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr"/>
       <c r="D20" s="13" t="inlineStr"/>
-      <c r="E20" s="29" t="inlineStr">
+      <c r="E20" s="30" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr"/>
       <c r="G20" s="13" t="inlineStr"/>
-      <c r="H20" s="28" t="inlineStr">
+      <c r="H20" s="29" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr"/>
-      <c r="J20" s="13" t="n">
+      <c r="J20" s="13" t="inlineStr"/>
+      <c r="K20" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K20" s="13" t="inlineStr">
+      <c r="L20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" s="13" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="L20" s="23" t="inlineStr">
+      <c r="O20" s="24" t="inlineStr">
         <is>
           <t>Shared</t>
         </is>
@@ -1909,25 +2065,32 @@
       <c r="F21" s="9" t="inlineStr"/>
       <c r="G21" s="9" t="inlineStr"/>
       <c r="H21" s="9" t="inlineStr"/>
-      <c r="I21" s="25" t="inlineStr">
+      <c r="I21" s="26" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J21" s="9" t="n">
+      <c r="J21" s="9" t="inlineStr"/>
+      <c r="K21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="L21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="L21" s="9" t="inlineStr"/>
+      <c r="O21" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -1989,59 +2152,59 @@
       <c r="J2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>Team / Product</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
+      <c r="C3" s="31" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr">
+      <c r="D3" s="31" t="inlineStr">
         <is>
           <t>Target End</t>
         </is>
       </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="E3" s="31" t="inlineStr">
         <is>
           <t>Current Phase</t>
         </is>
       </c>
-      <c r="F3" s="30" t="inlineStr">
+      <c r="F3" s="31" t="inlineStr">
         <is>
           <t>Achieved So Far</t>
         </is>
       </c>
-      <c r="G3" s="30" t="inlineStr">
+      <c r="G3" s="31" t="inlineStr">
         <is>
           <t>Next Target</t>
         </is>
       </c>
-      <c r="H3" s="30" t="inlineStr">
+      <c r="H3" s="31" t="inlineStr">
         <is>
           <t>Delivery Aligned?</t>
         </is>
       </c>
-      <c r="I3" s="30" t="inlineStr">
+      <c r="I3" s="31" t="inlineStr">
         <is>
           <t>Risk / Blocker</t>
         </is>
       </c>
-      <c r="J3" s="30" t="inlineStr">
+      <c r="J3" s="31" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -2066,7 +2229,7 @@
           <t>Post-MVP</t>
         </is>
       </c>
-      <c r="F4" s="32" t="inlineStr">
+      <c r="F4" s="33" t="inlineStr">
         <is>
           <t>✅ MVP launched (Sprint 6) — Users, Roles, Tenants, SSO, Permissions, Audit, Assign Access all live</t>
         </is>
@@ -2101,7 +2264,7 @@
       <c r="J5" s="9" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -2126,7 +2289,7 @@
           <t>Post-MVP</t>
         </is>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
         <is>
           <t>✅ MVP launched (Sprint 6) — Employee mgmt, workflows, task mgmt, dashboards all live</t>
         </is>
@@ -2161,7 +2324,7 @@
       <c r="J7" s="9" t="n"/>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -2186,7 +2349,7 @@
           <t>Post-MVP</t>
         </is>
       </c>
-      <c r="F8" s="32" t="inlineStr">
+      <c r="F8" s="33" t="inlineStr">
         <is>
           <t>✅ MVP launched (Sprint 6) — Courses, learning paths, assessments, certifications all live</t>
         </is>
@@ -2221,7 +2384,7 @@
       <c r="J9" s="9" t="n"/>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -2246,7 +2409,7 @@
           <t>Post-MVP</t>
         </is>
       </c>
-      <c r="F10" s="32" t="inlineStr">
+      <c r="F10" s="33" t="inlineStr">
         <is>
           <t>✅ MVP launched (Sprint 6) — Policies, compliance tracking, audit workflows, risk matrix all live</t>
         </is>
@@ -2281,7 +2444,7 @@
       <c r="J11" s="9" t="n"/>
     </row>
     <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -2333,7 +2496,7 @@
       <c r="J13" s="9" t="n"/>
     </row>
     <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -2385,7 +2548,7 @@
       <c r="J15" s="9" t="n"/>
     </row>
     <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="38" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -2501,359 +2664,359 @@
       <c r="J2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="40" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B3" s="40" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="C3" s="39" t="inlineStr">
+      <c r="C3" s="40" t="inlineStr">
         <is>
           <t>Dates</t>
         </is>
       </c>
-      <c r="D3" s="39" t="inlineStr">
+      <c r="D3" s="40" t="inlineStr">
         <is>
           <t>Sprint Goal</t>
         </is>
       </c>
-      <c r="E3" s="39" t="inlineStr">
+      <c r="E3" s="40" t="inlineStr">
         <is>
           <t>Achieved</t>
         </is>
       </c>
-      <c r="F3" s="39" t="inlineStr">
+      <c r="F3" s="40" t="inlineStr">
         <is>
           <t>Tech Lead Feedback</t>
         </is>
       </c>
-      <c r="G3" s="39" t="inlineStr">
+      <c r="G3" s="40" t="inlineStr">
         <is>
           <t>Achievement / Win</t>
         </is>
       </c>
-      <c r="H3" s="39" t="inlineStr">
+      <c r="H3" s="40" t="inlineStr">
         <is>
           <t>Failure / Miss</t>
         </is>
       </c>
-      <c r="I3" s="39" t="inlineStr">
+      <c r="I3" s="40" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="J3" s="39" t="inlineStr">
+      <c r="J3" s="40" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
       </c>
-      <c r="B4" s="40" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="41" t="inlineStr">
         <is>
           <t>05 Jan – 18 Jan</t>
         </is>
       </c>
-      <c r="D4" s="41" t="inlineStr">
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>Platform architecture &amp; project setup</t>
         </is>
       </c>
-      <c r="E4" s="41" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>Project scaffolding, CI/CD pipeline, auth foundation</t>
         </is>
       </c>
-      <c r="F4" s="41" t="inlineStr">
+      <c r="F4" s="42" t="inlineStr">
         <is>
           <t>Strong start — clean architecture established</t>
         </is>
       </c>
-      <c r="G4" s="41" t="inlineStr">
+      <c r="G4" s="42" t="inlineStr">
         <is>
           <t>Architecture approved by all tech leads</t>
         </is>
       </c>
-      <c r="H4" s="41" t="inlineStr">
+      <c r="H4" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I4" s="41" t="inlineStr">
+      <c r="I4" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J4" s="40" t="inlineStr">
+      <c r="J4" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="C5" s="40" t="inlineStr">
+      <c r="C5" s="41" t="inlineStr">
         <is>
           <t>19 Jan – 01 Feb</t>
         </is>
       </c>
-      <c r="D5" s="41" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>User management &amp; role system core</t>
         </is>
       </c>
-      <c r="E5" s="41" t="inlineStr">
+      <c r="E5" s="42" t="inlineStr">
         <is>
           <t>Users CRUD, Roles CRUD, permission matrix API</t>
         </is>
       </c>
-      <c r="F5" s="41" t="inlineStr">
+      <c r="F5" s="42" t="inlineStr">
         <is>
           <t>Solid delivery — core IAM features ready</t>
         </is>
       </c>
-      <c r="G5" s="41" t="inlineStr">
+      <c r="G5" s="42" t="inlineStr">
         <is>
           <t>Role-based permission engine live</t>
         </is>
       </c>
-      <c r="H5" s="41" t="inlineStr">
+      <c r="H5" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="41" t="inlineStr">
+      <c r="I5" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="40" t="inlineStr">
+      <c r="J5" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
       </c>
-      <c r="B6" s="40" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C6" s="40" t="inlineStr">
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>02 Feb – 15 Feb</t>
         </is>
       </c>
-      <c r="D6" s="41" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>Tenant management &amp; SSO integration</t>
         </is>
       </c>
-      <c r="E6" s="41" t="inlineStr">
+      <c r="E6" s="42" t="inlineStr">
         <is>
           <t>Tenant settings, SSO middleware, API key management</t>
         </is>
       </c>
-      <c r="F6" s="41" t="inlineStr">
+      <c r="F6" s="42" t="inlineStr">
         <is>
           <t>SSO complexity handled well</t>
         </is>
       </c>
-      <c r="G6" s="41" t="inlineStr">
+      <c r="G6" s="42" t="inlineStr">
         <is>
           <t>Multi-tenant SSO working end-to-end</t>
         </is>
       </c>
-      <c r="H6" s="41" t="inlineStr">
+      <c r="H6" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="41" t="inlineStr">
+      <c r="I6" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="40" t="inlineStr">
+      <c r="J6" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>16 Feb – 01 Mar</t>
         </is>
       </c>
-      <c r="D7" s="41" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>Assign Access wizard &amp; user-role assignment</t>
         </is>
       </c>
-      <c r="E7" s="41" t="inlineStr">
+      <c r="E7" s="42" t="inlineStr">
         <is>
           <t>3-step Assign Access wizard, bulk role assignment, pre-check</t>
         </is>
       </c>
-      <c r="F7" s="41" t="inlineStr">
+      <c r="F7" s="42" t="inlineStr">
         <is>
           <t>UI matches Figma perfectly</t>
         </is>
       </c>
-      <c r="G7" s="41" t="inlineStr">
+      <c r="G7" s="42" t="inlineStr">
         <is>
           <t>Assign Access wizard shipped with all edge cases</t>
         </is>
       </c>
-      <c r="H7" s="41" t="inlineStr">
+      <c r="H7" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I7" s="41" t="inlineStr">
+      <c r="I7" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="40" t="inlineStr">
+      <c r="J7" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
       </c>
-      <c r="B8" s="40" t="inlineStr">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>02 Mar – 15 Mar</t>
         </is>
       </c>
-      <c r="D8" s="41" t="inlineStr">
+      <c r="D8" s="42" t="inlineStr">
         <is>
           <t>Audit logs, login history &amp; polish</t>
         </is>
       </c>
-      <c r="E8" s="41" t="inlineStr">
+      <c r="E8" s="42" t="inlineStr">
         <is>
           <t>Audit trail, login history, pagination, UI polish</t>
         </is>
       </c>
-      <c r="F8" s="41" t="inlineStr">
+      <c r="F8" s="42" t="inlineStr">
         <is>
           <t>Production-quality output</t>
         </is>
       </c>
-      <c r="G8" s="41" t="inlineStr">
+      <c r="G8" s="42" t="inlineStr">
         <is>
           <t>Full audit &amp; compliance features delivered</t>
         </is>
       </c>
-      <c r="H8" s="41" t="inlineStr">
+      <c r="H8" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I8" s="41" t="inlineStr">
+      <c r="I8" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="40" t="inlineStr">
+      <c r="J8" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="C9" s="40" t="inlineStr">
+      <c r="C9" s="41" t="inlineStr">
         <is>
           <t>16 Mar – 29 Mar</t>
         </is>
       </c>
-      <c r="D9" s="41" t="inlineStr">
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>MVP launch — AG ONE platform go-live</t>
         </is>
       </c>
-      <c r="E9" s="32" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>✅ MVP LAUNCHED — AG ONE platform live for all tenants</t>
         </is>
       </c>
-      <c r="F9" s="41" t="inlineStr">
+      <c r="F9" s="42" t="inlineStr">
         <is>
           <t>Excellent execution — platform launched successfully</t>
         </is>
       </c>
-      <c r="G9" s="32" t="inlineStr">
+      <c r="G9" s="33" t="inlineStr">
         <is>
           <t>🚀 AG ONE MVP successfully launched!</t>
         </is>
       </c>
-      <c r="H9" s="41" t="inlineStr">
+      <c r="H9" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I9" s="41" t="inlineStr">
+      <c r="I9" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2865,35 +3028,35 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
       </c>
-      <c r="B10" s="42" t="inlineStr">
+      <c r="B10" s="43" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="C10" s="42" t="inlineStr">
+      <c r="C10" s="43" t="inlineStr">
         <is>
           <t>30 Mar – 12 Apr</t>
         </is>
       </c>
-      <c r="D10" s="43" t="inlineStr"/>
-      <c r="E10" s="43" t="inlineStr"/>
-      <c r="F10" s="43" t="inlineStr"/>
-      <c r="G10" s="43" t="inlineStr"/>
-      <c r="H10" s="43" t="inlineStr"/>
-      <c r="I10" s="43" t="inlineStr"/>
-      <c r="J10" s="42" t="inlineStr">
+      <c r="D10" s="44" t="inlineStr"/>
+      <c r="E10" s="44" t="inlineStr"/>
+      <c r="F10" s="44" t="inlineStr"/>
+      <c r="G10" s="44" t="inlineStr"/>
+      <c r="H10" s="44" t="inlineStr"/>
+      <c r="I10" s="44" t="inlineStr"/>
+      <c r="J10" s="43" t="inlineStr">
         <is>
           <t>▶ In Progress</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -2917,7 +3080,7 @@
       <c r="J11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -2941,7 +3104,7 @@
       <c r="J12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -2965,7 +3128,7 @@
       <c r="J13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -2989,7 +3152,7 @@
       <c r="J14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -3013,7 +3176,7 @@
       <c r="J15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -3037,7 +3200,7 @@
       <c r="J16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -3061,7 +3224,7 @@
       <c r="J17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="inlineStr">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -3085,7 +3248,7 @@
       <c r="J18" s="13" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -3109,7 +3272,7 @@
       <c r="J19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="31" t="inlineStr">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -3133,7 +3296,7 @@
       <c r="J20" s="13" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="31" t="inlineStr">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -3157,7 +3320,7 @@
       <c r="J21" s="9" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -3181,7 +3344,7 @@
       <c r="J22" s="13" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -3205,7 +3368,7 @@
       <c r="J23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -3229,7 +3392,7 @@
       <c r="J24" s="13" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -3253,7 +3416,7 @@
       <c r="J25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -3277,7 +3440,7 @@
       <c r="J26" s="13" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -3301,7 +3464,7 @@
       <c r="J27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="31" t="inlineStr">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -3325,7 +3488,7 @@
       <c r="J28" s="13" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="31" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
@@ -3349,307 +3512,307 @@
       <c r="J29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="33" t="inlineStr">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
       </c>
-      <c r="B30" s="40" t="inlineStr">
+      <c r="B30" s="41" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C30" s="40" t="inlineStr">
+      <c r="C30" s="41" t="inlineStr">
         <is>
           <t>05 Jan – 18 Jan</t>
         </is>
       </c>
-      <c r="D30" s="41" t="inlineStr">
+      <c r="D30" s="42" t="inlineStr">
         <is>
           <t>OneWork module setup &amp; core data models</t>
         </is>
       </c>
-      <c r="E30" s="41" t="inlineStr">
+      <c r="E30" s="42" t="inlineStr">
         <is>
           <t>Project structure, DB schema, base API endpoints</t>
         </is>
       </c>
-      <c r="F30" s="41" t="inlineStr">
+      <c r="F30" s="42" t="inlineStr">
         <is>
           <t>Good foundation — aligned with AG ONE architecture</t>
         </is>
       </c>
-      <c r="G30" s="41" t="inlineStr">
+      <c r="G30" s="42" t="inlineStr">
         <is>
           <t>Schema aligned with platform on day 1</t>
         </is>
       </c>
-      <c r="H30" s="41" t="inlineStr">
+      <c r="H30" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I30" s="41" t="inlineStr">
+      <c r="I30" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J30" s="40" t="inlineStr">
+      <c r="J30" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="33" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
       </c>
-      <c r="B31" s="40" t="inlineStr">
+      <c r="B31" s="41" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="C31" s="40" t="inlineStr">
+      <c r="C31" s="41" t="inlineStr">
         <is>
           <t>19 Jan – 01 Feb</t>
         </is>
       </c>
-      <c r="D31" s="41" t="inlineStr">
+      <c r="D31" s="42" t="inlineStr">
         <is>
           <t>Employee management core features</t>
         </is>
       </c>
-      <c r="E31" s="41" t="inlineStr">
+      <c r="E31" s="42" t="inlineStr">
         <is>
           <t>Employee CRUD, search, filters, list views</t>
         </is>
       </c>
-      <c r="F31" s="41" t="inlineStr">
+      <c r="F31" s="42" t="inlineStr">
         <is>
           <t>Clean implementation, reusable components</t>
         </is>
       </c>
-      <c r="G31" s="41" t="inlineStr">
+      <c r="G31" s="42" t="inlineStr">
         <is>
           <t>Component library started for reuse</t>
         </is>
       </c>
-      <c r="H31" s="41" t="inlineStr">
+      <c r="H31" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I31" s="41" t="inlineStr">
+      <c r="I31" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J31" s="40" t="inlineStr">
+      <c r="J31" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="33" t="inlineStr">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
       </c>
-      <c r="B32" s="40" t="inlineStr">
+      <c r="B32" s="41" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C32" s="40" t="inlineStr">
+      <c r="C32" s="41" t="inlineStr">
         <is>
           <t>02 Feb – 15 Feb</t>
         </is>
       </c>
-      <c r="D32" s="41" t="inlineStr">
+      <c r="D32" s="42" t="inlineStr">
         <is>
           <t>Workflow engine &amp; task management</t>
         </is>
       </c>
-      <c r="E32" s="41" t="inlineStr">
+      <c r="E32" s="42" t="inlineStr">
         <is>
           <t>Workflow builder, task assignment, notifications</t>
         </is>
       </c>
-      <c r="F32" s="41" t="inlineStr">
+      <c r="F32" s="42" t="inlineStr">
         <is>
           <t>Workflow engine exceeded expectations</t>
         </is>
       </c>
-      <c r="G32" s="41" t="inlineStr">
+      <c r="G32" s="42" t="inlineStr">
         <is>
           <t>Dynamic workflow engine working</t>
         </is>
       </c>
-      <c r="H32" s="41" t="inlineStr">
+      <c r="H32" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I32" s="41" t="inlineStr">
+      <c r="I32" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J32" s="40" t="inlineStr">
+      <c r="J32" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="33" t="inlineStr">
+      <c r="A33" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
       </c>
-      <c r="B33" s="40" t="inlineStr">
+      <c r="B33" s="41" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="C33" s="40" t="inlineStr">
+      <c r="C33" s="41" t="inlineStr">
         <is>
           <t>16 Feb – 01 Mar</t>
         </is>
       </c>
-      <c r="D33" s="41" t="inlineStr">
+      <c r="D33" s="42" t="inlineStr">
         <is>
           <t>Dashboard &amp; reporting module</t>
         </is>
       </c>
-      <c r="E33" s="41" t="inlineStr">
+      <c r="E33" s="42" t="inlineStr">
         <is>
           <t>Manager dashboard, team views, KPI widgets</t>
         </is>
       </c>
-      <c r="F33" s="41" t="inlineStr">
+      <c r="F33" s="42" t="inlineStr">
         <is>
           <t>Dashboards look great — director-ready</t>
         </is>
       </c>
-      <c r="G33" s="41" t="inlineStr">
+      <c r="G33" s="42" t="inlineStr">
         <is>
           <t>Real-time KPI dashboard shipped</t>
         </is>
       </c>
-      <c r="H33" s="41" t="inlineStr">
+      <c r="H33" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I33" s="41" t="inlineStr">
+      <c r="I33" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J33" s="40" t="inlineStr">
+      <c r="J33" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="33" t="inlineStr">
+      <c r="A34" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
       </c>
-      <c r="B34" s="40" t="inlineStr">
+      <c r="B34" s="41" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="C34" s="40" t="inlineStr">
+      <c r="C34" s="41" t="inlineStr">
         <is>
           <t>02 Mar – 15 Mar</t>
         </is>
       </c>
-      <c r="D34" s="41" t="inlineStr">
+      <c r="D34" s="42" t="inlineStr">
         <is>
           <t>Integration testing &amp; bug fixes</t>
         </is>
       </c>
-      <c r="E34" s="41" t="inlineStr">
+      <c r="E34" s="42" t="inlineStr">
         <is>
           <t>End-to-end testing, 42 bugs fixed, perf optimization</t>
         </is>
       </c>
-      <c r="F34" s="41" t="inlineStr">
+      <c r="F34" s="42" t="inlineStr">
         <is>
           <t>Thorough testing — production ready</t>
         </is>
       </c>
-      <c r="G34" s="41" t="inlineStr">
+      <c r="G34" s="42" t="inlineStr">
         <is>
           <t>Zero critical bugs in final round</t>
         </is>
       </c>
-      <c r="H34" s="41" t="inlineStr">
+      <c r="H34" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I34" s="41" t="inlineStr">
+      <c r="I34" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J34" s="40" t="inlineStr">
+      <c r="J34" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="33" t="inlineStr">
+      <c r="A35" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
       </c>
-      <c r="B35" s="40" t="inlineStr">
+      <c r="B35" s="41" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="C35" s="40" t="inlineStr">
+      <c r="C35" s="41" t="inlineStr">
         <is>
           <t>16 Mar – 29 Mar</t>
         </is>
       </c>
-      <c r="D35" s="41" t="inlineStr">
+      <c r="D35" s="42" t="inlineStr">
         <is>
           <t>MVP launch — OneWork go-live</t>
         </is>
       </c>
-      <c r="E35" s="32" t="inlineStr">
+      <c r="E35" s="33" t="inlineStr">
         <is>
           <t>✅ MVP LAUNCHED — OneWork live for all tenants</t>
         </is>
       </c>
-      <c r="F35" s="41" t="inlineStr">
+      <c r="F35" s="42" t="inlineStr">
         <is>
           <t>Flawless launch — team delivered on time</t>
         </is>
       </c>
-      <c r="G35" s="32" t="inlineStr">
+      <c r="G35" s="33" t="inlineStr">
         <is>
           <t>🚀 OneWork MVP successfully launched!</t>
         </is>
       </c>
-      <c r="H35" s="41" t="inlineStr">
+      <c r="H35" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I35" s="41" t="inlineStr">
+      <c r="I35" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3661,35 +3824,35 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="33" t="inlineStr">
+      <c r="A36" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
       </c>
-      <c r="B36" s="42" t="inlineStr">
+      <c r="B36" s="43" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="C36" s="42" t="inlineStr">
+      <c r="C36" s="43" t="inlineStr">
         <is>
           <t>30 Mar – 12 Apr</t>
         </is>
       </c>
-      <c r="D36" s="43" t="inlineStr"/>
-      <c r="E36" s="43" t="inlineStr"/>
-      <c r="F36" s="43" t="inlineStr"/>
-      <c r="G36" s="43" t="inlineStr"/>
-      <c r="H36" s="43" t="inlineStr"/>
-      <c r="I36" s="43" t="inlineStr"/>
-      <c r="J36" s="42" t="inlineStr">
+      <c r="D36" s="44" t="inlineStr"/>
+      <c r="E36" s="44" t="inlineStr"/>
+      <c r="F36" s="44" t="inlineStr"/>
+      <c r="G36" s="44" t="inlineStr"/>
+      <c r="H36" s="44" t="inlineStr"/>
+      <c r="I36" s="44" t="inlineStr"/>
+      <c r="J36" s="43" t="inlineStr">
         <is>
           <t>▶ In Progress</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="33" t="inlineStr">
+      <c r="A37" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -3713,7 +3876,7 @@
       <c r="J37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="33" t="inlineStr">
+      <c r="A38" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -3737,7 +3900,7 @@
       <c r="J38" s="13" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="33" t="inlineStr">
+      <c r="A39" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -3761,7 +3924,7 @@
       <c r="J39" s="9" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="33" t="inlineStr">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -3785,7 +3948,7 @@
       <c r="J40" s="13" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="33" t="inlineStr">
+      <c r="A41" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -3809,7 +3972,7 @@
       <c r="J41" s="9" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="33" t="inlineStr">
+      <c r="A42" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -3833,7 +3996,7 @@
       <c r="J42" s="13" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="33" t="inlineStr">
+      <c r="A43" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -3857,7 +4020,7 @@
       <c r="J43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="33" t="inlineStr">
+      <c r="A44" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -3881,7 +4044,7 @@
       <c r="J44" s="13" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="33" t="inlineStr">
+      <c r="A45" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -3905,7 +4068,7 @@
       <c r="J45" s="9" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="33" t="inlineStr">
+      <c r="A46" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -3929,7 +4092,7 @@
       <c r="J46" s="13" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="33" t="inlineStr">
+      <c r="A47" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -3953,7 +4116,7 @@
       <c r="J47" s="9" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="33" t="inlineStr">
+      <c r="A48" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -3977,7 +4140,7 @@
       <c r="J48" s="13" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="33" t="inlineStr">
+      <c r="A49" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -4001,7 +4164,7 @@
       <c r="J49" s="9" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="33" t="inlineStr">
+      <c r="A50" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -4025,7 +4188,7 @@
       <c r="J50" s="13" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="33" t="inlineStr">
+      <c r="A51" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -4049,7 +4212,7 @@
       <c r="J51" s="9" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="33" t="inlineStr">
+      <c r="A52" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -4073,7 +4236,7 @@
       <c r="J52" s="13" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="33" t="inlineStr">
+      <c r="A53" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -4097,7 +4260,7 @@
       <c r="J53" s="9" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="33" t="inlineStr">
+      <c r="A54" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -4121,7 +4284,7 @@
       <c r="J54" s="13" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="33" t="inlineStr">
+      <c r="A55" s="34" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
@@ -4145,307 +4308,307 @@
       <c r="J55" s="9" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="34" t="inlineStr">
+      <c r="A56" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
       </c>
-      <c r="B56" s="40" t="inlineStr">
+      <c r="B56" s="41" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C56" s="40" t="inlineStr">
+      <c r="C56" s="41" t="inlineStr">
         <is>
           <t>05 Jan – 18 Jan</t>
         </is>
       </c>
-      <c r="D56" s="41" t="inlineStr">
+      <c r="D56" s="42" t="inlineStr">
         <is>
           <t>Learn module setup &amp; LMS architecture</t>
         </is>
       </c>
-      <c r="E56" s="41" t="inlineStr">
+      <c r="E56" s="42" t="inlineStr">
         <is>
           <t>Module scaffold, course data model, API skeleton</t>
         </is>
       </c>
-      <c r="F56" s="41" t="inlineStr">
+      <c r="F56" s="42" t="inlineStr">
         <is>
           <t>Clean start — well-structured codebase</t>
         </is>
       </c>
-      <c r="G56" s="41" t="inlineStr">
+      <c r="G56" s="42" t="inlineStr">
         <is>
           <t>LMS data model approved</t>
         </is>
       </c>
-      <c r="H56" s="41" t="inlineStr">
+      <c r="H56" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I56" s="41" t="inlineStr">
+      <c r="I56" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J56" s="40" t="inlineStr">
+      <c r="J56" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="34" t="inlineStr">
+      <c r="A57" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
       </c>
-      <c r="B57" s="40" t="inlineStr">
+      <c r="B57" s="41" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="C57" s="40" t="inlineStr">
+      <c r="C57" s="41" t="inlineStr">
         <is>
           <t>19 Jan – 01 Feb</t>
         </is>
       </c>
-      <c r="D57" s="41" t="inlineStr">
+      <c r="D57" s="42" t="inlineStr">
         <is>
           <t>Course management &amp; content builder</t>
         </is>
       </c>
-      <c r="E57" s="41" t="inlineStr">
+      <c r="E57" s="42" t="inlineStr">
         <is>
           <t>Course CRUD, content upload, module builder</t>
         </is>
       </c>
-      <c r="F57" s="41" t="inlineStr">
+      <c r="F57" s="42" t="inlineStr">
         <is>
           <t>Content builder is intuitive</t>
         </is>
       </c>
-      <c r="G57" s="41" t="inlineStr">
+      <c r="G57" s="42" t="inlineStr">
         <is>
           <t>Drag-and-drop content builder working</t>
         </is>
       </c>
-      <c r="H57" s="41" t="inlineStr">
+      <c r="H57" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I57" s="41" t="inlineStr">
+      <c r="I57" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J57" s="40" t="inlineStr">
+      <c r="J57" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="34" t="inlineStr">
+      <c r="A58" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
       </c>
-      <c r="B58" s="40" t="inlineStr">
+      <c r="B58" s="41" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C58" s="40" t="inlineStr">
+      <c r="C58" s="41" t="inlineStr">
         <is>
           <t>02 Feb – 15 Feb</t>
         </is>
       </c>
-      <c r="D58" s="41" t="inlineStr">
+      <c r="D58" s="42" t="inlineStr">
         <is>
           <t>Learning paths &amp; assignments</t>
         </is>
       </c>
-      <c r="E58" s="41" t="inlineStr">
+      <c r="E58" s="42" t="inlineStr">
         <is>
           <t>Learning path creation, auto-assignment rules, progress tracking</t>
         </is>
       </c>
-      <c r="F58" s="41" t="inlineStr">
+      <c r="F58" s="42" t="inlineStr">
         <is>
           <t>Assignment logic is solid</t>
         </is>
       </c>
-      <c r="G58" s="41" t="inlineStr">
+      <c r="G58" s="42" t="inlineStr">
         <is>
           <t>Auto-assignment engine completed</t>
         </is>
       </c>
-      <c r="H58" s="41" t="inlineStr">
+      <c r="H58" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I58" s="41" t="inlineStr">
+      <c r="I58" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J58" s="40" t="inlineStr">
+      <c r="J58" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="34" t="inlineStr">
+      <c r="A59" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
       </c>
-      <c r="B59" s="40" t="inlineStr">
+      <c r="B59" s="41" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="C59" s="40" t="inlineStr">
+      <c r="C59" s="41" t="inlineStr">
         <is>
           <t>16 Feb – 01 Mar</t>
         </is>
       </c>
-      <c r="D59" s="41" t="inlineStr">
+      <c r="D59" s="42" t="inlineStr">
         <is>
           <t>Assessment engine &amp; certifications</t>
         </is>
       </c>
-      <c r="E59" s="41" t="inlineStr">
+      <c r="E59" s="42" t="inlineStr">
         <is>
           <t>Quiz builder, grading, certificate generation</t>
         </is>
       </c>
-      <c r="F59" s="41" t="inlineStr">
+      <c r="F59" s="42" t="inlineStr">
         <is>
           <t>Assessment engine works perfectly</t>
         </is>
       </c>
-      <c r="G59" s="41" t="inlineStr">
+      <c r="G59" s="42" t="inlineStr">
         <is>
           <t>Certification flow end-to-end</t>
         </is>
       </c>
-      <c r="H59" s="41" t="inlineStr">
+      <c r="H59" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I59" s="41" t="inlineStr">
+      <c r="I59" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J59" s="40" t="inlineStr">
+      <c r="J59" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="34" t="inlineStr">
+      <c r="A60" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
       </c>
-      <c r="B60" s="40" t="inlineStr">
+      <c r="B60" s="41" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="C60" s="40" t="inlineStr">
+      <c r="C60" s="41" t="inlineStr">
         <is>
           <t>02 Mar – 15 Mar</t>
         </is>
       </c>
-      <c r="D60" s="41" t="inlineStr">
+      <c r="D60" s="42" t="inlineStr">
         <is>
           <t>UI polish, testing &amp; launch prep</t>
         </is>
       </c>
-      <c r="E60" s="41" t="inlineStr">
+      <c r="E60" s="42" t="inlineStr">
         <is>
           <t>UI refinements, integration tests, launch checklist done</t>
         </is>
       </c>
-      <c r="F60" s="41" t="inlineStr">
+      <c r="F60" s="42" t="inlineStr">
         <is>
           <t>Ready for production</t>
         </is>
       </c>
-      <c r="G60" s="41" t="inlineStr">
+      <c r="G60" s="42" t="inlineStr">
         <is>
           <t>All acceptance criteria passed</t>
         </is>
       </c>
-      <c r="H60" s="41" t="inlineStr">
+      <c r="H60" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I60" s="41" t="inlineStr">
+      <c r="I60" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J60" s="40" t="inlineStr">
+      <c r="J60" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="34" t="inlineStr">
+      <c r="A61" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
       </c>
-      <c r="B61" s="40" t="inlineStr">
+      <c r="B61" s="41" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="C61" s="40" t="inlineStr">
+      <c r="C61" s="41" t="inlineStr">
         <is>
           <t>16 Mar – 29 Mar</t>
         </is>
       </c>
-      <c r="D61" s="41" t="inlineStr">
+      <c r="D61" s="42" t="inlineStr">
         <is>
           <t>MVP launch — Learn go-live</t>
         </is>
       </c>
-      <c r="E61" s="32" t="inlineStr">
+      <c r="E61" s="33" t="inlineStr">
         <is>
           <t>✅ MVP LAUNCHED — Learn live for all tenants</t>
         </is>
       </c>
-      <c r="F61" s="41" t="inlineStr">
+      <c r="F61" s="42" t="inlineStr">
         <is>
           <t>Smooth launch — great team effort</t>
         </is>
       </c>
-      <c r="G61" s="32" t="inlineStr">
+      <c r="G61" s="33" t="inlineStr">
         <is>
           <t>🚀 Learn MVP successfully launched!</t>
         </is>
       </c>
-      <c r="H61" s="41" t="inlineStr">
+      <c r="H61" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I61" s="41" t="inlineStr">
+      <c r="I61" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4457,35 +4620,35 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="34" t="inlineStr">
+      <c r="A62" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
       </c>
-      <c r="B62" s="42" t="inlineStr">
+      <c r="B62" s="43" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="C62" s="42" t="inlineStr">
+      <c r="C62" s="43" t="inlineStr">
         <is>
           <t>30 Mar – 12 Apr</t>
         </is>
       </c>
-      <c r="D62" s="43" t="inlineStr"/>
-      <c r="E62" s="43" t="inlineStr"/>
-      <c r="F62" s="43" t="inlineStr"/>
-      <c r="G62" s="43" t="inlineStr"/>
-      <c r="H62" s="43" t="inlineStr"/>
-      <c r="I62" s="43" t="inlineStr"/>
-      <c r="J62" s="42" t="inlineStr">
+      <c r="D62" s="44" t="inlineStr"/>
+      <c r="E62" s="44" t="inlineStr"/>
+      <c r="F62" s="44" t="inlineStr"/>
+      <c r="G62" s="44" t="inlineStr"/>
+      <c r="H62" s="44" t="inlineStr"/>
+      <c r="I62" s="44" t="inlineStr"/>
+      <c r="J62" s="43" t="inlineStr">
         <is>
           <t>▶ In Progress</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="34" t="inlineStr">
+      <c r="A63" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4509,7 +4672,7 @@
       <c r="J63" s="9" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="34" t="inlineStr">
+      <c r="A64" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4533,7 +4696,7 @@
       <c r="J64" s="13" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="34" t="inlineStr">
+      <c r="A65" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4557,7 +4720,7 @@
       <c r="J65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="34" t="inlineStr">
+      <c r="A66" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4581,7 +4744,7 @@
       <c r="J66" s="13" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="34" t="inlineStr">
+      <c r="A67" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4605,7 +4768,7 @@
       <c r="J67" s="9" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="34" t="inlineStr">
+      <c r="A68" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4629,7 +4792,7 @@
       <c r="J68" s="13" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="34" t="inlineStr">
+      <c r="A69" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4653,7 +4816,7 @@
       <c r="J69" s="9" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="34" t="inlineStr">
+      <c r="A70" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4677,7 +4840,7 @@
       <c r="J70" s="13" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="34" t="inlineStr">
+      <c r="A71" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4701,7 +4864,7 @@
       <c r="J71" s="9" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="34" t="inlineStr">
+      <c r="A72" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4725,7 +4888,7 @@
       <c r="J72" s="13" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="34" t="inlineStr">
+      <c r="A73" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4749,7 +4912,7 @@
       <c r="J73" s="9" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="34" t="inlineStr">
+      <c r="A74" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4773,7 +4936,7 @@
       <c r="J74" s="13" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="34" t="inlineStr">
+      <c r="A75" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4797,7 +4960,7 @@
       <c r="J75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="34" t="inlineStr">
+      <c r="A76" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4821,7 +4984,7 @@
       <c r="J76" s="13" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="34" t="inlineStr">
+      <c r="A77" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4845,7 +5008,7 @@
       <c r="J77" s="9" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="34" t="inlineStr">
+      <c r="A78" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4869,7 +5032,7 @@
       <c r="J78" s="13" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="34" t="inlineStr">
+      <c r="A79" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4893,7 +5056,7 @@
       <c r="J79" s="9" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="34" t="inlineStr">
+      <c r="A80" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4917,7 +5080,7 @@
       <c r="J80" s="13" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="34" t="inlineStr">
+      <c r="A81" s="35" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
@@ -4941,307 +5104,307 @@
       <c r="J81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="35" t="inlineStr">
+      <c r="A82" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="B82" s="40" t="inlineStr">
+      <c r="B82" s="41" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C82" s="40" t="inlineStr">
+      <c r="C82" s="41" t="inlineStr">
         <is>
           <t>05 Jan – 18 Jan</t>
         </is>
       </c>
-      <c r="D82" s="41" t="inlineStr">
+      <c r="D82" s="42" t="inlineStr">
         <is>
           <t>Safe module setup &amp; compliance framework</t>
         </is>
       </c>
-      <c r="E82" s="41" t="inlineStr">
+      <c r="E82" s="42" t="inlineStr">
         <is>
           <t>Module scaffold, policy data model, compliance engine design</t>
         </is>
       </c>
-      <c r="F82" s="41" t="inlineStr">
+      <c r="F82" s="42" t="inlineStr">
         <is>
           <t>Compliance model is comprehensive</t>
         </is>
       </c>
-      <c r="G82" s="41" t="inlineStr">
+      <c r="G82" s="42" t="inlineStr">
         <is>
           <t>Compliance framework designed and approved</t>
         </is>
       </c>
-      <c r="H82" s="41" t="inlineStr">
+      <c r="H82" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I82" s="41" t="inlineStr">
+      <c r="I82" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J82" s="40" t="inlineStr">
+      <c r="J82" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="35" t="inlineStr">
+      <c r="A83" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="B83" s="40" t="inlineStr">
+      <c r="B83" s="41" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="C83" s="40" t="inlineStr">
+      <c r="C83" s="41" t="inlineStr">
         <is>
           <t>19 Jan – 01 Feb</t>
         </is>
       </c>
-      <c r="D83" s="41" t="inlineStr">
+      <c r="D83" s="42" t="inlineStr">
         <is>
           <t>Policy management &amp; data library</t>
         </is>
       </c>
-      <c r="E83" s="41" t="inlineStr">
+      <c r="E83" s="42" t="inlineStr">
         <is>
           <t>Policy CRUD, version control, data library foundation</t>
         </is>
       </c>
-      <c r="F83" s="41" t="inlineStr">
+      <c r="F83" s="42" t="inlineStr">
         <is>
           <t>Policy versioning is well thought out</t>
         </is>
       </c>
-      <c r="G83" s="41" t="inlineStr">
+      <c r="G83" s="42" t="inlineStr">
         <is>
           <t>Policy versioning system live</t>
         </is>
       </c>
-      <c r="H83" s="41" t="inlineStr">
+      <c r="H83" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I83" s="41" t="inlineStr">
+      <c r="I83" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J83" s="40" t="inlineStr">
+      <c r="J83" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="35" t="inlineStr">
+      <c r="A84" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="B84" s="40" t="inlineStr">
+      <c r="B84" s="41" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C84" s="40" t="inlineStr">
+      <c r="C84" s="41" t="inlineStr">
         <is>
           <t>02 Feb – 15 Feb</t>
         </is>
       </c>
-      <c r="D84" s="41" t="inlineStr">
+      <c r="D84" s="42" t="inlineStr">
         <is>
           <t>Compliance tracking &amp; audit workflows</t>
         </is>
       </c>
-      <c r="E84" s="41" t="inlineStr">
+      <c r="E84" s="42" t="inlineStr">
         <is>
           <t>Compliance checklist, audit trail, automated reminders</t>
         </is>
       </c>
-      <c r="F84" s="41" t="inlineStr">
+      <c r="F84" s="42" t="inlineStr">
         <is>
           <t>Audit workflow exceeds requirements</t>
         </is>
       </c>
-      <c r="G84" s="41" t="inlineStr">
+      <c r="G84" s="42" t="inlineStr">
         <is>
           <t>Automated compliance reminders working</t>
         </is>
       </c>
-      <c r="H84" s="41" t="inlineStr">
+      <c r="H84" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I84" s="41" t="inlineStr">
+      <c r="I84" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J84" s="40" t="inlineStr">
+      <c r="J84" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="35" t="inlineStr">
+      <c r="A85" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="B85" s="40" t="inlineStr">
+      <c r="B85" s="41" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="C85" s="40" t="inlineStr">
+      <c r="C85" s="41" t="inlineStr">
         <is>
           <t>16 Feb – 01 Mar</t>
         </is>
       </c>
-      <c r="D85" s="41" t="inlineStr">
+      <c r="D85" s="42" t="inlineStr">
         <is>
           <t>Reporting &amp; compliance dashboard</t>
         </is>
       </c>
-      <c r="E85" s="41" t="inlineStr">
+      <c r="E85" s="42" t="inlineStr">
         <is>
           <t>Compliance dashboard, risk matrix, export reports</t>
         </is>
       </c>
-      <c r="F85" s="41" t="inlineStr">
+      <c r="F85" s="42" t="inlineStr">
         <is>
           <t>Dashboard is director-ready</t>
         </is>
       </c>
-      <c r="G85" s="41" t="inlineStr">
+      <c r="G85" s="42" t="inlineStr">
         <is>
           <t>Risk matrix visualization shipped</t>
         </is>
       </c>
-      <c r="H85" s="41" t="inlineStr">
+      <c r="H85" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I85" s="41" t="inlineStr">
+      <c r="I85" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J85" s="40" t="inlineStr">
+      <c r="J85" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="35" t="inlineStr">
+      <c r="A86" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="B86" s="40" t="inlineStr">
+      <c r="B86" s="41" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="C86" s="40" t="inlineStr">
+      <c r="C86" s="41" t="inlineStr">
         <is>
           <t>02 Mar – 15 Mar</t>
         </is>
       </c>
-      <c r="D86" s="41" t="inlineStr">
+      <c r="D86" s="42" t="inlineStr">
         <is>
           <t>Integration testing &amp; security hardening</t>
         </is>
       </c>
-      <c r="E86" s="41" t="inlineStr">
+      <c r="E86" s="42" t="inlineStr">
         <is>
           <t>Security audit passed, pen test fixes, perf tuning</t>
         </is>
       </c>
-      <c r="F86" s="41" t="inlineStr">
+      <c r="F86" s="42" t="inlineStr">
         <is>
           <t>Security standards met — production ready</t>
         </is>
       </c>
-      <c r="G86" s="41" t="inlineStr">
+      <c r="G86" s="42" t="inlineStr">
         <is>
           <t>Passed security audit with zero critical findings</t>
         </is>
       </c>
-      <c r="H86" s="41" t="inlineStr">
+      <c r="H86" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I86" s="41" t="inlineStr">
+      <c r="I86" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J86" s="40" t="inlineStr">
+      <c r="J86" s="41" t="inlineStr">
         <is>
           <t>✅ Completed</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="35" t="inlineStr">
+      <c r="A87" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="B87" s="40" t="inlineStr">
+      <c r="B87" s="41" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="C87" s="40" t="inlineStr">
+      <c r="C87" s="41" t="inlineStr">
         <is>
           <t>16 Mar – 29 Mar</t>
         </is>
       </c>
-      <c r="D87" s="41" t="inlineStr">
+      <c r="D87" s="42" t="inlineStr">
         <is>
           <t>MVP launch — Safe go-live</t>
         </is>
       </c>
-      <c r="E87" s="32" t="inlineStr">
+      <c r="E87" s="33" t="inlineStr">
         <is>
           <t>✅ MVP LAUNCHED — Safe live for all tenants</t>
         </is>
       </c>
-      <c r="F87" s="41" t="inlineStr">
+      <c r="F87" s="42" t="inlineStr">
         <is>
           <t>Outstanding delivery — launched on schedule</t>
         </is>
       </c>
-      <c r="G87" s="32" t="inlineStr">
+      <c r="G87" s="33" t="inlineStr">
         <is>
           <t>🚀 Safe MVP successfully launched!</t>
         </is>
       </c>
-      <c r="H87" s="41" t="inlineStr">
+      <c r="H87" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I87" s="41" t="inlineStr">
+      <c r="I87" s="42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5253,35 +5416,35 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="35" t="inlineStr">
+      <c r="A88" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="B88" s="42" t="inlineStr">
+      <c r="B88" s="43" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="C88" s="42" t="inlineStr">
+      <c r="C88" s="43" t="inlineStr">
         <is>
           <t>30 Mar – 12 Apr</t>
         </is>
       </c>
-      <c r="D88" s="43" t="inlineStr"/>
-      <c r="E88" s="43" t="inlineStr"/>
-      <c r="F88" s="43" t="inlineStr"/>
-      <c r="G88" s="43" t="inlineStr"/>
-      <c r="H88" s="43" t="inlineStr"/>
-      <c r="I88" s="43" t="inlineStr"/>
-      <c r="J88" s="42" t="inlineStr">
+      <c r="D88" s="44" t="inlineStr"/>
+      <c r="E88" s="44" t="inlineStr"/>
+      <c r="F88" s="44" t="inlineStr"/>
+      <c r="G88" s="44" t="inlineStr"/>
+      <c r="H88" s="44" t="inlineStr"/>
+      <c r="I88" s="44" t="inlineStr"/>
+      <c r="J88" s="43" t="inlineStr">
         <is>
           <t>▶ In Progress</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="35" t="inlineStr">
+      <c r="A89" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5305,7 +5468,7 @@
       <c r="J89" s="9" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="35" t="inlineStr">
+      <c r="A90" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5329,7 +5492,7 @@
       <c r="J90" s="13" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="35" t="inlineStr">
+      <c r="A91" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5353,7 +5516,7 @@
       <c r="J91" s="9" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="35" t="inlineStr">
+      <c r="A92" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5377,7 +5540,7 @@
       <c r="J92" s="13" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="35" t="inlineStr">
+      <c r="A93" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5401,7 +5564,7 @@
       <c r="J93" s="9" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="35" t="inlineStr">
+      <c r="A94" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5425,7 +5588,7 @@
       <c r="J94" s="13" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="35" t="inlineStr">
+      <c r="A95" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5449,7 +5612,7 @@
       <c r="J95" s="9" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="35" t="inlineStr">
+      <c r="A96" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5473,7 +5636,7 @@
       <c r="J96" s="13" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="35" t="inlineStr">
+      <c r="A97" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5497,7 +5660,7 @@
       <c r="J97" s="9" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="35" t="inlineStr">
+      <c r="A98" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5521,7 +5684,7 @@
       <c r="J98" s="13" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="35" t="inlineStr">
+      <c r="A99" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5545,7 +5708,7 @@
       <c r="J99" s="9" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="35" t="inlineStr">
+      <c r="A100" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5569,7 +5732,7 @@
       <c r="J100" s="13" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="35" t="inlineStr">
+      <c r="A101" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5593,7 +5756,7 @@
       <c r="J101" s="9" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="35" t="inlineStr">
+      <c r="A102" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5617,7 +5780,7 @@
       <c r="J102" s="13" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="35" t="inlineStr">
+      <c r="A103" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5641,7 +5804,7 @@
       <c r="J103" s="9" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="35" t="inlineStr">
+      <c r="A104" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5665,7 +5828,7 @@
       <c r="J104" s="13" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="35" t="inlineStr">
+      <c r="A105" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5689,7 +5852,7 @@
       <c r="J105" s="9" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="35" t="inlineStr">
+      <c r="A106" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5713,7 +5876,7 @@
       <c r="J106" s="13" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="35" t="inlineStr">
+      <c r="A107" s="36" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
@@ -5737,35 +5900,35 @@
       <c r="J107" s="9" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="36" t="inlineStr">
+      <c r="A108" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
       </c>
-      <c r="B108" s="42" t="inlineStr">
+      <c r="B108" s="43" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C108" s="42" t="inlineStr">
+      <c r="C108" s="43" t="inlineStr">
         <is>
           <t>05 Jan – 18 Jan</t>
         </is>
       </c>
-      <c r="D108" s="43" t="inlineStr"/>
-      <c r="E108" s="43" t="inlineStr"/>
-      <c r="F108" s="43" t="inlineStr"/>
-      <c r="G108" s="43" t="inlineStr"/>
-      <c r="H108" s="43" t="inlineStr"/>
-      <c r="I108" s="43" t="inlineStr"/>
-      <c r="J108" s="42" t="inlineStr">
+      <c r="D108" s="44" t="inlineStr"/>
+      <c r="E108" s="44" t="inlineStr"/>
+      <c r="F108" s="44" t="inlineStr"/>
+      <c r="G108" s="44" t="inlineStr"/>
+      <c r="H108" s="44" t="inlineStr"/>
+      <c r="I108" s="44" t="inlineStr"/>
+      <c r="J108" s="43" t="inlineStr">
         <is>
           <t>▶ In Progress</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="36" t="inlineStr">
+      <c r="A109" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -5789,7 +5952,7 @@
       <c r="J109" s="9" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="36" t="inlineStr">
+      <c r="A110" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -5813,7 +5976,7 @@
       <c r="J110" s="13" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="36" t="inlineStr">
+      <c r="A111" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -5837,7 +6000,7 @@
       <c r="J111" s="9" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="36" t="inlineStr">
+      <c r="A112" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -5861,7 +6024,7 @@
       <c r="J112" s="13" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="36" t="inlineStr">
+      <c r="A113" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -5885,7 +6048,7 @@
       <c r="J113" s="9" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="36" t="inlineStr">
+      <c r="A114" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -5909,7 +6072,7 @@
       <c r="J114" s="13" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="36" t="inlineStr">
+      <c r="A115" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -5933,7 +6096,7 @@
       <c r="J115" s="9" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="36" t="inlineStr">
+      <c r="A116" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -5957,7 +6120,7 @@
       <c r="J116" s="13" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="36" t="inlineStr">
+      <c r="A117" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -5981,7 +6144,7 @@
       <c r="J117" s="9" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="36" t="inlineStr">
+      <c r="A118" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -6005,7 +6168,7 @@
       <c r="J118" s="13" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="36" t="inlineStr">
+      <c r="A119" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -6029,7 +6192,7 @@
       <c r="J119" s="9" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="36" t="inlineStr">
+      <c r="A120" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -6053,7 +6216,7 @@
       <c r="J120" s="13" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="36" t="inlineStr">
+      <c r="A121" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -6077,7 +6240,7 @@
       <c r="J121" s="9" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="36" t="inlineStr">
+      <c r="A122" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -6101,7 +6264,7 @@
       <c r="J122" s="13" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="36" t="inlineStr">
+      <c r="A123" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -6125,7 +6288,7 @@
       <c r="J123" s="9" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="36" t="inlineStr">
+      <c r="A124" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -6149,7 +6312,7 @@
       <c r="J124" s="13" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="36" t="inlineStr">
+      <c r="A125" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -6173,7 +6336,7 @@
       <c r="J125" s="9" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="36" t="inlineStr">
+      <c r="A126" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -6197,7 +6360,7 @@
       <c r="J126" s="13" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="36" t="inlineStr">
+      <c r="A127" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -6221,7 +6384,7 @@
       <c r="J127" s="9" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="36" t="inlineStr">
+      <c r="A128" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -6245,7 +6408,7 @@
       <c r="J128" s="13" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="36" t="inlineStr">
+      <c r="A129" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -6269,7 +6432,7 @@
       <c r="J129" s="9" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="36" t="inlineStr">
+      <c r="A130" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -6293,7 +6456,7 @@
       <c r="J130" s="13" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="36" t="inlineStr">
+      <c r="A131" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -6317,7 +6480,7 @@
       <c r="J131" s="9" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="36" t="inlineStr">
+      <c r="A132" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -6341,7 +6504,7 @@
       <c r="J132" s="13" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="36" t="inlineStr">
+      <c r="A133" s="37" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
@@ -6365,35 +6528,35 @@
       <c r="J133" s="9" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="37" t="inlineStr">
+      <c r="A134" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
       </c>
-      <c r="B134" s="42" t="inlineStr">
+      <c r="B134" s="43" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C134" s="42" t="inlineStr">
+      <c r="C134" s="43" t="inlineStr">
         <is>
           <t>05 Jan – 18 Jan</t>
         </is>
       </c>
-      <c r="D134" s="43" t="inlineStr"/>
-      <c r="E134" s="43" t="inlineStr"/>
-      <c r="F134" s="43" t="inlineStr"/>
-      <c r="G134" s="43" t="inlineStr"/>
-      <c r="H134" s="43" t="inlineStr"/>
-      <c r="I134" s="43" t="inlineStr"/>
-      <c r="J134" s="42" t="inlineStr">
+      <c r="D134" s="44" t="inlineStr"/>
+      <c r="E134" s="44" t="inlineStr"/>
+      <c r="F134" s="44" t="inlineStr"/>
+      <c r="G134" s="44" t="inlineStr"/>
+      <c r="H134" s="44" t="inlineStr"/>
+      <c r="I134" s="44" t="inlineStr"/>
+      <c r="J134" s="43" t="inlineStr">
         <is>
           <t>▶ In Progress</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="37" t="inlineStr">
+      <c r="A135" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6417,7 +6580,7 @@
       <c r="J135" s="9" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="37" t="inlineStr">
+      <c r="A136" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6441,7 +6604,7 @@
       <c r="J136" s="13" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="37" t="inlineStr">
+      <c r="A137" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6465,7 +6628,7 @@
       <c r="J137" s="9" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="37" t="inlineStr">
+      <c r="A138" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6489,7 +6652,7 @@
       <c r="J138" s="13" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="37" t="inlineStr">
+      <c r="A139" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6513,7 +6676,7 @@
       <c r="J139" s="9" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="37" t="inlineStr">
+      <c r="A140" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6537,7 +6700,7 @@
       <c r="J140" s="13" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="37" t="inlineStr">
+      <c r="A141" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6561,7 +6724,7 @@
       <c r="J141" s="9" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="37" t="inlineStr">
+      <c r="A142" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6585,7 +6748,7 @@
       <c r="J142" s="13" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="37" t="inlineStr">
+      <c r="A143" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6609,7 +6772,7 @@
       <c r="J143" s="9" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="37" t="inlineStr">
+      <c r="A144" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6633,7 +6796,7 @@
       <c r="J144" s="13" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="37" t="inlineStr">
+      <c r="A145" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6657,7 +6820,7 @@
       <c r="J145" s="9" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="37" t="inlineStr">
+      <c r="A146" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6681,7 +6844,7 @@
       <c r="J146" s="13" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="37" t="inlineStr">
+      <c r="A147" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6705,7 +6868,7 @@
       <c r="J147" s="9" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="37" t="inlineStr">
+      <c r="A148" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6729,7 +6892,7 @@
       <c r="J148" s="13" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="37" t="inlineStr">
+      <c r="A149" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6753,7 +6916,7 @@
       <c r="J149" s="9" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="37" t="inlineStr">
+      <c r="A150" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6777,7 +6940,7 @@
       <c r="J150" s="13" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="37" t="inlineStr">
+      <c r="A151" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6801,7 +6964,7 @@
       <c r="J151" s="9" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="37" t="inlineStr">
+      <c r="A152" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6825,7 +6988,7 @@
       <c r="J152" s="13" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="37" t="inlineStr">
+      <c r="A153" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6849,7 +7012,7 @@
       <c r="J153" s="9" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="37" t="inlineStr">
+      <c r="A154" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6873,7 +7036,7 @@
       <c r="J154" s="13" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="37" t="inlineStr">
+      <c r="A155" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6897,7 +7060,7 @@
       <c r="J155" s="9" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="37" t="inlineStr">
+      <c r="A156" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6921,7 +7084,7 @@
       <c r="J156" s="13" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="37" t="inlineStr">
+      <c r="A157" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6945,7 +7108,7 @@
       <c r="J157" s="9" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="37" t="inlineStr">
+      <c r="A158" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6969,7 +7132,7 @@
       <c r="J158" s="13" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="37" t="inlineStr">
+      <c r="A159" s="38" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
@@ -6993,35 +7156,35 @@
       <c r="J159" s="9" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="38" t="inlineStr">
+      <c r="A160" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
       </c>
-      <c r="B160" s="42" t="inlineStr">
+      <c r="B160" s="43" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C160" s="42" t="inlineStr">
+      <c r="C160" s="43" t="inlineStr">
         <is>
           <t>05 Jan – 18 Jan</t>
         </is>
       </c>
-      <c r="D160" s="43" t="inlineStr"/>
-      <c r="E160" s="43" t="inlineStr"/>
-      <c r="F160" s="43" t="inlineStr"/>
-      <c r="G160" s="43" t="inlineStr"/>
-      <c r="H160" s="43" t="inlineStr"/>
-      <c r="I160" s="43" t="inlineStr"/>
-      <c r="J160" s="42" t="inlineStr">
+      <c r="D160" s="44" t="inlineStr"/>
+      <c r="E160" s="44" t="inlineStr"/>
+      <c r="F160" s="44" t="inlineStr"/>
+      <c r="G160" s="44" t="inlineStr"/>
+      <c r="H160" s="44" t="inlineStr"/>
+      <c r="I160" s="44" t="inlineStr"/>
+      <c r="J160" s="43" t="inlineStr">
         <is>
           <t>▶ In Progress</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="38" t="inlineStr">
+      <c r="A161" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7045,7 +7208,7 @@
       <c r="J161" s="9" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="38" t="inlineStr">
+      <c r="A162" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7069,7 +7232,7 @@
       <c r="J162" s="13" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="38" t="inlineStr">
+      <c r="A163" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7093,7 +7256,7 @@
       <c r="J163" s="9" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="38" t="inlineStr">
+      <c r="A164" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7117,7 +7280,7 @@
       <c r="J164" s="13" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="38" t="inlineStr">
+      <c r="A165" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7141,7 +7304,7 @@
       <c r="J165" s="9" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="38" t="inlineStr">
+      <c r="A166" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7165,7 +7328,7 @@
       <c r="J166" s="13" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="38" t="inlineStr">
+      <c r="A167" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7189,7 +7352,7 @@
       <c r="J167" s="9" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="38" t="inlineStr">
+      <c r="A168" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7213,7 +7376,7 @@
       <c r="J168" s="13" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="38" t="inlineStr">
+      <c r="A169" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7237,7 +7400,7 @@
       <c r="J169" s="9" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="38" t="inlineStr">
+      <c r="A170" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7261,7 +7424,7 @@
       <c r="J170" s="13" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="38" t="inlineStr">
+      <c r="A171" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7285,7 +7448,7 @@
       <c r="J171" s="9" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="38" t="inlineStr">
+      <c r="A172" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7309,7 +7472,7 @@
       <c r="J172" s="13" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="38" t="inlineStr">
+      <c r="A173" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7333,7 +7496,7 @@
       <c r="J173" s="9" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="38" t="inlineStr">
+      <c r="A174" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7357,7 +7520,7 @@
       <c r="J174" s="13" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="38" t="inlineStr">
+      <c r="A175" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7381,7 +7544,7 @@
       <c r="J175" s="9" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="38" t="inlineStr">
+      <c r="A176" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7405,7 +7568,7 @@
       <c r="J176" s="13" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="38" t="inlineStr">
+      <c r="A177" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7429,7 +7592,7 @@
       <c r="J177" s="9" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="38" t="inlineStr">
+      <c r="A178" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7453,7 +7616,7 @@
       <c r="J178" s="13" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="38" t="inlineStr">
+      <c r="A179" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7477,7 +7640,7 @@
       <c r="J179" s="9" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="38" t="inlineStr">
+      <c r="A180" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7501,7 +7664,7 @@
       <c r="J180" s="13" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="38" t="inlineStr">
+      <c r="A181" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7525,7 +7688,7 @@
       <c r="J181" s="9" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="38" t="inlineStr">
+      <c r="A182" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7549,7 +7712,7 @@
       <c r="J182" s="13" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="38" t="inlineStr">
+      <c r="A183" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7573,7 +7736,7 @@
       <c r="J183" s="9" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="38" t="inlineStr">
+      <c r="A184" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7597,7 +7760,7 @@
       <c r="J184" s="13" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="38" t="inlineStr">
+      <c r="A185" s="39" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
@@ -7685,52 +7848,52 @@
       <c r="J2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="44" t="inlineStr">
+      <c r="A3" s="45" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B3" s="44" t="inlineStr">
+      <c r="B3" s="45" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
       </c>
-      <c r="C3" s="44" t="inlineStr">
+      <c r="C3" s="45" t="inlineStr">
         <is>
           <t>Team(s)</t>
         </is>
       </c>
-      <c r="D3" s="44" t="inlineStr">
+      <c r="D3" s="45" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="E3" s="44" t="inlineStr">
+      <c r="E3" s="45" t="inlineStr">
         <is>
           <t>Current Sprint Task</t>
         </is>
       </c>
-      <c r="F3" s="44" t="inlineStr">
+      <c r="F3" s="45" t="inlineStr">
         <is>
           <t>Progress %</t>
         </is>
       </c>
-      <c r="G3" s="44" t="inlineStr">
+      <c r="G3" s="45" t="inlineStr">
         <is>
           <t>Tech Lead Rating</t>
         </is>
       </c>
-      <c r="H3" s="44" t="inlineStr">
+      <c r="H3" s="45" t="inlineStr">
         <is>
           <t>Feedback / Notes</t>
         </is>
       </c>
-      <c r="I3" s="44" t="inlineStr">
+      <c r="I3" s="45" t="inlineStr">
         <is>
           <t>Achievements (YTD)</t>
         </is>
       </c>
-      <c r="J3" s="44" t="inlineStr">
+      <c r="J3" s="45" t="inlineStr">
         <is>
           <t>Areas to Improve</t>
         </is>
@@ -7740,7 +7903,7 @@
       <c r="A4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>Abdullah</t>
         </is>
@@ -7759,7 +7922,7 @@
       <c r="F4" s="13" t="inlineStr"/>
       <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="14" t="inlineStr"/>
-      <c r="I4" s="32" t="inlineStr">
+      <c r="I4" s="33" t="inlineStr">
         <is>
           <t>Contributed to successful MVP launch of 4 products (AG ONE, OneWork, Learn, Safe) in 6 sprints</t>
         </is>
@@ -7770,7 +7933,7 @@
       <c r="A5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="46" t="inlineStr">
+      <c r="B5" s="47" t="inlineStr">
         <is>
           <t>Faisal</t>
         </is>
@@ -7789,7 +7952,7 @@
       <c r="F5" s="9" t="inlineStr"/>
       <c r="G5" s="9" t="inlineStr"/>
       <c r="H5" s="10" t="inlineStr"/>
-      <c r="I5" s="32" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t>Contributed to successful MVP launch of 4 products (AG ONE, OneWork, Learn, Safe) in 6 sprints</t>
         </is>
@@ -7800,7 +7963,7 @@
       <c r="A6" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="45" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>Fatin</t>
         </is>
@@ -7826,7 +7989,7 @@
       <c r="A7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="46" t="inlineStr">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>Geena</t>
         </is>
@@ -7845,7 +8008,7 @@
       <c r="F7" s="9" t="inlineStr"/>
       <c r="G7" s="9" t="inlineStr"/>
       <c r="H7" s="10" t="inlineStr"/>
-      <c r="I7" s="32" t="inlineStr">
+      <c r="I7" s="33" t="inlineStr">
         <is>
           <t>Contributed to successful MVP launch of 4 products (AG ONE, OneWork, Learn, Safe) in 6 sprints</t>
         </is>
@@ -7856,7 +8019,7 @@
       <c r="A8" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="45" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>Hanis</t>
         </is>
@@ -7882,7 +8045,7 @@
       <c r="A9" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="46" t="inlineStr">
+      <c r="B9" s="47" t="inlineStr">
         <is>
           <t>Hema</t>
         </is>
@@ -7908,7 +8071,7 @@
       <c r="A10" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="45" t="inlineStr">
+      <c r="B10" s="46" t="inlineStr">
         <is>
           <t>Jawad</t>
         </is>
@@ -7927,7 +8090,7 @@
       <c r="F10" s="13" t="inlineStr"/>
       <c r="G10" s="13" t="inlineStr"/>
       <c r="H10" s="14" t="inlineStr"/>
-      <c r="I10" s="32" t="inlineStr">
+      <c r="I10" s="33" t="inlineStr">
         <is>
           <t>Contributed to successful MVP launch of 4 products (AG ONE, OneWork, Learn, Safe) in 6 sprints</t>
         </is>
@@ -7938,7 +8101,7 @@
       <c r="A11" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B11" s="47" t="inlineStr">
         <is>
           <t>Kiritini</t>
         </is>
@@ -7957,7 +8120,7 @@
       <c r="F11" s="9" t="inlineStr"/>
       <c r="G11" s="9" t="inlineStr"/>
       <c r="H11" s="10" t="inlineStr"/>
-      <c r="I11" s="32" t="inlineStr">
+      <c r="I11" s="33" t="inlineStr">
         <is>
           <t>Contributed to successful MVP launch of 4 products (AG ONE, OneWork, Learn, Safe) in 6 sprints</t>
         </is>
@@ -7968,7 +8131,7 @@
       <c r="A12" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="45" t="inlineStr">
+      <c r="B12" s="46" t="inlineStr">
         <is>
           <t>Loc</t>
         </is>
@@ -7987,7 +8150,7 @@
       <c r="F12" s="13" t="inlineStr"/>
       <c r="G12" s="13" t="inlineStr"/>
       <c r="H12" s="14" t="inlineStr"/>
-      <c r="I12" s="32" t="inlineStr">
+      <c r="I12" s="33" t="inlineStr">
         <is>
           <t>Contributed to successful MVP launch of 4 products (AG ONE, OneWork, Learn, Safe) in 6 sprints</t>
         </is>
@@ -7998,7 +8161,7 @@
       <c r="A13" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="46" t="inlineStr">
+      <c r="B13" s="47" t="inlineStr">
         <is>
           <t>Logesh</t>
         </is>
@@ -8024,7 +8187,7 @@
       <c r="A14" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="45" t="inlineStr">
+      <c r="B14" s="46" t="inlineStr">
         <is>
           <t>Majed</t>
         </is>
@@ -8050,7 +8213,7 @@
       <c r="A15" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="46" t="inlineStr">
+      <c r="B15" s="47" t="inlineStr">
         <is>
           <t>Nastaran</t>
         </is>
@@ -8069,7 +8232,7 @@
       <c r="F15" s="9" t="inlineStr"/>
       <c r="G15" s="9" t="inlineStr"/>
       <c r="H15" s="10" t="inlineStr"/>
-      <c r="I15" s="32" t="inlineStr">
+      <c r="I15" s="33" t="inlineStr">
         <is>
           <t>Contributed to successful MVP launch of 4 products (AG ONE, OneWork, Learn, Safe) in 6 sprints</t>
         </is>
@@ -8080,7 +8243,7 @@
       <c r="A16" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="45" t="inlineStr">
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>Rahmya</t>
         </is>
@@ -8106,7 +8269,7 @@
       <c r="A17" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="47" t="inlineStr">
         <is>
           <t>Ricky</t>
         </is>
@@ -8125,7 +8288,7 @@
       <c r="F17" s="9" t="inlineStr"/>
       <c r="G17" s="9" t="inlineStr"/>
       <c r="H17" s="10" t="inlineStr"/>
-      <c r="I17" s="32" t="inlineStr">
+      <c r="I17" s="33" t="inlineStr">
         <is>
           <t>Contributed to successful MVP launch of 4 products (AG ONE, OneWork, Learn, Safe) in 6 sprints</t>
         </is>
@@ -8136,7 +8299,7 @@
       <c r="A18" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="45" t="inlineStr">
+      <c r="B18" s="46" t="inlineStr">
         <is>
           <t>Sharuti</t>
         </is>
@@ -8162,7 +8325,7 @@
       <c r="A19" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="46" t="inlineStr">
+      <c r="B19" s="47" t="inlineStr">
         <is>
           <t>Surya</t>
         </is>
@@ -8181,7 +8344,7 @@
       <c r="F19" s="9" t="inlineStr"/>
       <c r="G19" s="9" t="inlineStr"/>
       <c r="H19" s="10" t="inlineStr"/>
-      <c r="I19" s="32" t="inlineStr">
+      <c r="I19" s="33" t="inlineStr">
         <is>
           <t>Contributed to successful MVP launch of 4 products (AG ONE, OneWork, Learn, Safe) in 6 sprints</t>
         </is>
@@ -8192,7 +8355,7 @@
       <c r="A20" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="45" t="inlineStr">
+      <c r="B20" s="46" t="inlineStr">
         <is>
           <t>Than</t>
         </is>
@@ -8211,7 +8374,7 @@
       <c r="F20" s="13" t="inlineStr"/>
       <c r="G20" s="13" t="inlineStr"/>
       <c r="H20" s="14" t="inlineStr"/>
-      <c r="I20" s="32" t="inlineStr">
+      <c r="I20" s="33" t="inlineStr">
         <is>
           <t>Contributed to successful MVP launch of 4 products (AG ONE, OneWork, Learn, Safe) in 6 sprints</t>
         </is>
@@ -8222,7 +8385,7 @@
       <c r="A21" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="46" t="inlineStr">
+      <c r="B21" s="47" t="inlineStr">
         <is>
           <t>Umeshawar</t>
         </is>
@@ -8309,64 +8472,64 @@
       <c r="J2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="47" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="B3" s="47" t="inlineStr">
+      <c r="B3" s="48" t="inlineStr">
         <is>
           <t>Q1 Target (Jan–Mar)</t>
         </is>
       </c>
-      <c r="C3" s="47" t="inlineStr">
+      <c r="C3" s="48" t="inlineStr">
         <is>
           <t>Q1 Status</t>
         </is>
       </c>
-      <c r="D3" s="47" t="inlineStr">
+      <c r="D3" s="48" t="inlineStr">
         <is>
           <t>Q2 Target (Apr–Jun)</t>
         </is>
       </c>
-      <c r="E3" s="47" t="inlineStr">
+      <c r="E3" s="48" t="inlineStr">
         <is>
           <t>Q2 Status</t>
         </is>
       </c>
-      <c r="F3" s="47" t="inlineStr">
+      <c r="F3" s="48" t="inlineStr">
         <is>
           <t>Q3 Target (Jul–Sep)</t>
         </is>
       </c>
-      <c r="G3" s="47" t="inlineStr">
+      <c r="G3" s="48" t="inlineStr">
         <is>
           <t>Q3 Status</t>
         </is>
       </c>
-      <c r="H3" s="47" t="inlineStr">
+      <c r="H3" s="48" t="inlineStr">
         <is>
           <t>Q4 Target (Oct–Dec)</t>
         </is>
       </c>
-      <c r="I3" s="47" t="inlineStr">
+      <c r="I3" s="48" t="inlineStr">
         <is>
           <t>Q4 Status</t>
         </is>
       </c>
-      <c r="J3" s="47" t="inlineStr">
+      <c r="J3" s="48" t="inlineStr">
         <is>
           <t>Year-End Goal</t>
         </is>
       </c>
     </row>
     <row r="4" ht="56" customHeight="1">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>AG ONE</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="50" t="inlineStr">
         <is>
           <t>MVP launch — platform, users, roles, tenants, SSO, permissions</t>
         </is>
@@ -8376,7 +8539,7 @@
           <t>✅ Completed</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="50" t="inlineStr">
         <is>
           <t>Platform hardening, advanced admin, analytics</t>
         </is>
@@ -8386,7 +8549,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="50" t="inlineStr">
         <is>
           <t>Multi-product governance, API marketplace</t>
         </is>
@@ -8396,7 +8559,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H4" s="49" t="inlineStr">
+      <c r="H4" s="50" t="inlineStr">
         <is>
           <t>Enterprise features, scale &amp; performance</t>
         </is>
@@ -8406,19 +8569,19 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="J4" s="49" t="inlineStr">
+      <c r="J4" s="50" t="inlineStr">
         <is>
           <t>Full enterprise IAM platform with all products integrated</t>
         </is>
       </c>
     </row>
     <row r="5" ht="56" customHeight="1">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="51" t="inlineStr">
         <is>
           <t>OneWork</t>
         </is>
       </c>
-      <c r="B5" s="49" t="inlineStr">
+      <c r="B5" s="50" t="inlineStr">
         <is>
           <t>MVP launch — employee mgmt, workflows, dashboards</t>
         </is>
@@ -8428,7 +8591,7 @@
           <t>✅ Completed</t>
         </is>
       </c>
-      <c r="D5" s="49" t="inlineStr">
+      <c r="D5" s="50" t="inlineStr">
         <is>
           <t>Advanced workflows, integrations, reporting v2</t>
         </is>
@@ -8438,7 +8601,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F5" s="49" t="inlineStr">
+      <c r="F5" s="50" t="inlineStr">
         <is>
           <t>Mobile support, AI-powered insights</t>
         </is>
@@ -8448,7 +8611,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H5" s="49" t="inlineStr">
+      <c r="H5" s="50" t="inlineStr">
         <is>
           <t>Enterprise scale, advanced automation</t>
         </is>
@@ -8458,19 +8621,19 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="J5" s="49" t="inlineStr">
+      <c r="J5" s="50" t="inlineStr">
         <is>
           <t>Complete workforce management platform</t>
         </is>
       </c>
     </row>
     <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="51" t="inlineStr">
+      <c r="A6" s="52" t="inlineStr">
         <is>
           <t>Learn</t>
         </is>
       </c>
-      <c r="B6" s="49" t="inlineStr">
+      <c r="B6" s="50" t="inlineStr">
         <is>
           <t>MVP launch — courses, paths, assessments, certs</t>
         </is>
@@ -8480,7 +8643,7 @@
           <t>✅ Completed</t>
         </is>
       </c>
-      <c r="D6" s="49" t="inlineStr">
+      <c r="D6" s="50" t="inlineStr">
         <is>
           <t>Advanced analytics, content marketplace</t>
         </is>
@@ -8490,7 +8653,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F6" s="49" t="inlineStr">
+      <c r="F6" s="50" t="inlineStr">
         <is>
           <t>Mobile learning, AI recommendations</t>
         </is>
@@ -8500,7 +8663,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H6" s="49" t="inlineStr">
+      <c r="H6" s="50" t="inlineStr">
         <is>
           <t>Enterprise LMS with full reporting</t>
         </is>
@@ -8510,19 +8673,19 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="J6" s="49" t="inlineStr">
+      <c r="J6" s="50" t="inlineStr">
         <is>
           <t>Full-featured LMS with marketplace &amp; analytics</t>
         </is>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="52" t="inlineStr">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>Safe</t>
         </is>
       </c>
-      <c r="B7" s="49" t="inlineStr">
+      <c r="B7" s="50" t="inlineStr">
         <is>
           <t>MVP launch — policies, compliance, audit, risk matrix</t>
         </is>
@@ -8532,7 +8695,7 @@
           <t>✅ Completed</t>
         </is>
       </c>
-      <c r="D7" s="49" t="inlineStr">
+      <c r="D7" s="50" t="inlineStr">
         <is>
           <t>Regulatory automation, advanced reporting</t>
         </is>
@@ -8542,7 +8705,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F7" s="49" t="inlineStr">
+      <c r="F7" s="50" t="inlineStr">
         <is>
           <t>Third-party integrations, automated alerts</t>
         </is>
@@ -8552,7 +8715,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H7" s="49" t="inlineStr">
+      <c r="H7" s="50" t="inlineStr">
         <is>
           <t>Enterprise compliance suite</t>
         </is>
@@ -8562,19 +8725,19 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="J7" s="49" t="inlineStr">
+      <c r="J7" s="50" t="inlineStr">
         <is>
           <t>End-to-end compliance &amp; risk management suite</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
-      <c r="A8" s="53" t="inlineStr">
+      <c r="A8" s="54" t="inlineStr">
         <is>
           <t>OneHire</t>
         </is>
       </c>
-      <c r="B8" s="49" t="inlineStr">
+      <c r="B8" s="50" t="inlineStr">
         <is>
           <t>Requirements &amp; design</t>
         </is>
@@ -8584,7 +8747,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="D8" s="49" t="inlineStr">
+      <c r="D8" s="50" t="inlineStr">
         <is>
           <t>MVP development — job postings, applicant tracking</t>
         </is>
@@ -8594,7 +8757,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F8" s="49" t="inlineStr">
+      <c r="F8" s="50" t="inlineStr">
         <is>
           <t>MVP launch &amp; post-launch improvements</t>
         </is>
@@ -8604,7 +8767,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H8" s="49" t="inlineStr">
+      <c r="H8" s="50" t="inlineStr">
         <is>
           <t>Advanced hiring analytics &amp; integrations</t>
         </is>
@@ -8614,19 +8777,19 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="J8" s="49" t="inlineStr">
+      <c r="J8" s="50" t="inlineStr">
         <is>
           <t>Full recruitment &amp; applicant tracking system</t>
         </is>
       </c>
     </row>
     <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="54" t="inlineStr">
+      <c r="A9" s="55" t="inlineStr">
         <is>
           <t>Spot</t>
         </is>
       </c>
-      <c r="B9" s="49" t="inlineStr">
+      <c r="B9" s="50" t="inlineStr">
         <is>
           <t>Requirements &amp; design</t>
         </is>
@@ -8636,7 +8799,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="D9" s="49" t="inlineStr">
+      <c r="D9" s="50" t="inlineStr">
         <is>
           <t>Core city module development</t>
         </is>
@@ -8646,7 +8809,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F9" s="49" t="inlineStr">
+      <c r="F9" s="50" t="inlineStr">
         <is>
           <t>MVP launch — city management features</t>
         </is>
@@ -8656,7 +8819,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H9" s="49" t="inlineStr">
+      <c r="H9" s="50" t="inlineStr">
         <is>
           <t>Advanced features &amp; scale</t>
         </is>
@@ -8666,19 +8829,19 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="J9" s="49" t="inlineStr">
+      <c r="J9" s="50" t="inlineStr">
         <is>
           <t>City management module fully operational</t>
         </is>
       </c>
     </row>
     <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A10" s="56" t="inlineStr">
         <is>
           <t>Pulse</t>
         </is>
       </c>
-      <c r="B10" s="49" t="inlineStr">
+      <c r="B10" s="50" t="inlineStr">
         <is>
           <t>Requirements &amp; design</t>
         </is>
@@ -8688,7 +8851,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="D10" s="49" t="inlineStr">
+      <c r="D10" s="50" t="inlineStr">
         <is>
           <t>Survey builder &amp; distribution engine</t>
         </is>
@@ -8698,7 +8861,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="F10" s="49" t="inlineStr">
+      <c r="F10" s="50" t="inlineStr">
         <is>
           <t>MVP launch — survey analytics &amp; dashboards</t>
         </is>
@@ -8708,7 +8871,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="H10" s="49" t="inlineStr">
+      <c r="H10" s="50" t="inlineStr">
         <is>
           <t>AI-powered insights &amp; benchmarking</t>
         </is>
@@ -8718,7 +8881,7 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="J10" s="49" t="inlineStr">
+      <c r="J10" s="50" t="inlineStr">
         <is>
           <t>Complete employee engagement &amp; survey platform</t>
         </is>
@@ -8737,16 +8900,320 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007C3AED"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>External / Outsource Projects — 2026</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Track resources assigned to external projects, outsourced work, and partner engagements</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="C3" s="21" t="inlineStr">
+        <is>
+          <t>Client / Partner</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Assigned Resources</t>
+        </is>
+      </c>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>Role / Responsibility</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>Allocation %</t>
+        </is>
+      </c>
+      <c r="G3" s="21" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t>End Date</t>
+        </is>
+      </c>
+      <c r="I3" s="21" t="inlineStr">
+        <is>
+          <t>Current Phase</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="K3" s="21" t="inlineStr">
+        <is>
+          <t>Key Deliverables</t>
+        </is>
+      </c>
+      <c r="L3" s="21" t="inlineStr">
+        <is>
+          <t>Notes / Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="57" t="inlineStr">
+        <is>
+          <t>Form 2</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr"/>
+      <c r="E4" s="14" t="inlineStr"/>
+      <c r="F4" s="13" t="inlineStr"/>
+      <c r="G4" s="13" t="inlineStr"/>
+      <c r="H4" s="13" t="inlineStr"/>
+      <c r="I4" s="14" t="inlineStr"/>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr"/>
+      <c r="L4" s="14" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="10" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="13" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="13" t="n"/>
+      <c r="G8" s="13" t="n"/>
+      <c r="H8" s="13" t="n"/>
+      <c r="I8" s="14" t="n"/>
+      <c r="J8" s="13" t="n"/>
+      <c r="K8" s="14" t="n"/>
+      <c r="L8" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="13" t="n"/>
+      <c r="I10" s="14" t="n"/>
+      <c r="J10" s="13" t="n"/>
+      <c r="K10" s="14" t="n"/>
+      <c r="L10" s="14" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="14" t="n"/>
+      <c r="J12" s="13" t="n"/>
+      <c r="K12" s="14" t="n"/>
+      <c r="L12" s="14" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="006B7280"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -8771,22 +9238,22 @@
       <c r="D2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="56" t="inlineStr">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="56" t="inlineStr">
+      <c r="B3" s="58" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="C3" s="56" t="inlineStr">
+      <c r="C3" s="58" t="inlineStr">
         <is>
           <t>Update Frequency</t>
         </is>
       </c>
-      <c r="D3" s="56" t="inlineStr">
+      <c r="D3" s="58" t="inlineStr">
         <is>
           <t>Who Updates</t>
         </is>
@@ -8800,7 +9267,7 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>See all 7 teams, current sprint, status at a glance</t>
+          <t>See all 7 internal teams, current sprint, status at a glance</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
@@ -8822,7 +9289,7 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>View who belongs to which team, spot shared resources</t>
+          <t>Internal + external assignments per member, shared &amp; outsource flags</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -8924,53 +9391,75 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="57" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>External Projects</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Track resources on external / outsource / partner projects</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>When assignments change</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Engineering Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>STATUS LEGEND</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ●  ✅ Completed</t>
-        </is>
-      </c>
-      <c r="B12" s="59" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="60" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ●  ✅ Completed</t>
+        </is>
+      </c>
+      <c r="B13" s="61" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="62" t="inlineStr">
+        <is>
           <t xml:space="preserve">  ●  ▶ In Progress / On Track</t>
         </is>
       </c>
-      <c r="B13" s="59" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="61" t="inlineStr">
+      <c r="B14" s="61" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="63" t="inlineStr">
         <is>
           <t xml:space="preserve">  ●  At Risk</t>
         </is>
       </c>
-      <c r="B14" s="59" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="62" t="inlineStr">
+      <c r="B15" s="61" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">  ●  Blocked</t>
         </is>
       </c>
-      <c r="B15" s="59" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="63" t="inlineStr">
+      <c r="B16" s="61" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">  ●  Not Started</t>
         </is>
       </c>
-      <c r="B16" s="59" t="n"/>
+      <c r="B17" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -8980,7 +9469,7 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A17:B17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/AG_ONE_Team_Tracker_2026.xlsx
+++ b/AG_ONE_Team_Tracker_2026.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Team Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resource Allocation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Project Roadmap" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sprint Tracker" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Member Performance" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2026 Targets" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="External Projects" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="How To Use" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resource Allocation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Roadmap" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint Tracker" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Member Performance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026 Targets" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Projects" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release History" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Standard" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Use" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,14 +138,50 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="001E3A5F"/>
+      <color rgb="000369A1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="001E3A5F"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="005B21B6"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="001E3A5F"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -163,7 +202,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -266,8 +305,26 @@
         <bgColor rgb="00EDE9FE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000EA5E9"/>
+        <bgColor rgb="000EA5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F2FE"/>
+        <bgColor rgb="00E0F2FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000284C7"/>
+        <bgColor rgb="000284C7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -311,6 +368,17 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="00E2E8F0"/>
       </right>
@@ -326,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -479,16 +547,93 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1203,6 +1348,761 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000369A1"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Release Naming Standard &amp; Versioning Policy</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Share this with all teams so everyone follows the same release naming and numbering</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="71" t="inlineStr">
+        <is>
+          <t>Versioning Format</t>
+        </is>
+      </c>
+      <c r="B3" s="72" t="n"/>
+      <c r="C3" s="72" t="n"/>
+      <c r="D3" s="73" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="49" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="B4" s="74" t="inlineStr">
+        <is>
+          <t>vMAJOR.MINOR.PATCH</t>
+        </is>
+      </c>
+      <c r="C4" s="75" t="n"/>
+      <c r="D4" s="76" t="inlineStr">
+        <is>
+          <t>Example: v1.2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="49" t="inlineStr">
+        <is>
+          <t>MAJOR</t>
+        </is>
+      </c>
+      <c r="B5" s="74" t="inlineStr">
+        <is>
+          <t>Breaking changes or major new feature sets</t>
+        </is>
+      </c>
+      <c r="C5" s="75" t="n"/>
+      <c r="D5" s="76" t="inlineStr">
+        <is>
+          <t>v1.0.0 → v2.0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="49" t="inlineStr">
+        <is>
+          <t>MINOR</t>
+        </is>
+      </c>
+      <c r="B6" s="74" t="inlineStr">
+        <is>
+          <t>New features, enhancements (backward compatible)</t>
+        </is>
+      </c>
+      <c r="C6" s="75" t="n"/>
+      <c r="D6" s="76" t="inlineStr">
+        <is>
+          <t>v1.0.0 → v1.1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="49" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="B7" s="74" t="inlineStr">
+        <is>
+          <t>Bug fixes, hotfixes, minor corrections</t>
+        </is>
+      </c>
+      <c r="C7" s="75" t="n"/>
+      <c r="D7" s="76" t="inlineStr">
+        <is>
+          <t>v1.0.0 → v1.0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="58" t="inlineStr">
+        <is>
+          <t>Release Type</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C9" s="58" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="D9" s="58" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="77" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="B10" s="50" t="inlineStr">
+        <is>
+          <t>First production release of a product</t>
+        </is>
+      </c>
+      <c r="C10" s="50" t="inlineStr">
+        <is>
+          <t>Once per product</t>
+        </is>
+      </c>
+      <c r="D10" s="50" t="inlineStr">
+        <is>
+          <t>Director + Tech Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="78" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="B11" s="50" t="inlineStr">
+        <is>
+          <t>Significant new features or breaking changes</t>
+        </is>
+      </c>
+      <c r="C11" s="50" t="inlineStr">
+        <is>
+          <t>1–2 per year</t>
+        </is>
+      </c>
+      <c r="D11" s="50" t="inlineStr">
+        <is>
+          <t>Director + Tech Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="79" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="B12" s="50" t="inlineStr">
+        <is>
+          <t>New features &amp; enhancements, backward compatible</t>
+        </is>
+      </c>
+      <c r="C12" s="50" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D12" s="50" t="inlineStr">
+        <is>
+          <t>Tech Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="80" t="inlineStr">
+        <is>
+          <t>Hotfix</t>
+        </is>
+      </c>
+      <c r="B13" s="50" t="inlineStr">
+        <is>
+          <t>Critical production fix, expedited deployment</t>
+        </is>
+      </c>
+      <c r="C13" s="50" t="inlineStr">
+        <is>
+          <t>As needed (urgent)</t>
+        </is>
+      </c>
+      <c r="D13" s="50" t="inlineStr">
+        <is>
+          <t>Tech Lead + post-mortem</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="81" t="inlineStr">
+        <is>
+          <t>Patch</t>
+        </is>
+      </c>
+      <c r="B14" s="50" t="inlineStr">
+        <is>
+          <t>Non-critical bug fixes, scheduled deployment</t>
+        </is>
+      </c>
+      <c r="C14" s="50" t="inlineStr">
+        <is>
+          <t>As needed</t>
+        </is>
+      </c>
+      <c r="D14" s="50" t="inlineStr">
+        <is>
+          <t>Tech Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="82" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="B15" s="50" t="inlineStr">
+        <is>
+          <t>Sprint-based release (pre-MVP iterations)</t>
+        </is>
+      </c>
+      <c r="C15" s="50" t="inlineStr">
+        <is>
+          <t>Every 2 weeks</t>
+        </is>
+      </c>
+      <c r="D15" s="50" t="inlineStr">
+        <is>
+          <t>Tech Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="71" t="inlineStr">
+        <is>
+          <t>Release Naming Convention</t>
+        </is>
+      </c>
+      <c r="B17" s="72" t="n"/>
+      <c r="C17" s="72" t="n"/>
+      <c r="D17" s="73" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="83" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+      <c r="B18" s="84" t="inlineStr">
+        <is>
+          <t>[Product] [Type] — [Short Description]</t>
+        </is>
+      </c>
+      <c r="C18" s="85" t="inlineStr">
+        <is>
+          <t>Used in Release Name column</t>
+        </is>
+      </c>
+      <c r="D18" s="86" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="83" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="B19" s="84" t="inlineStr">
+        <is>
+          <t>AG ONE MVP</t>
+        </is>
+      </c>
+      <c r="C19" s="85" t="inlineStr">
+        <is>
+          <t>First production release</t>
+        </is>
+      </c>
+      <c r="D19" s="86" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="83" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="B20" s="84" t="inlineStr">
+        <is>
+          <t>AG ONE Q2 Enhancement</t>
+        </is>
+      </c>
+      <c r="C20" s="85" t="inlineStr">
+        <is>
+          <t>Quarterly feature release</t>
+        </is>
+      </c>
+      <c r="D20" s="86" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="83" t="inlineStr">
+        <is>
+          <t>Hotfix</t>
+        </is>
+      </c>
+      <c r="B21" s="84" t="inlineStr">
+        <is>
+          <t>AG ONE Hotfix 1</t>
+        </is>
+      </c>
+      <c r="C21" s="85" t="inlineStr">
+        <is>
+          <t>Numbered sequentially</t>
+        </is>
+      </c>
+      <c r="D21" s="86" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="83" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="B22" s="84" t="inlineStr">
+        <is>
+          <t>AG ONE Enterprise</t>
+        </is>
+      </c>
+      <c r="C22" s="85" t="inlineStr">
+        <is>
+          <t>Named for the theme</t>
+        </is>
+      </c>
+      <c r="D22" s="86" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="83" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="B23" s="84" t="inlineStr">
+        <is>
+          <t>OneHire Alpha / OneHire Beta</t>
+        </is>
+      </c>
+      <c r="C23" s="85" t="inlineStr">
+        <is>
+          <t>Pre-MVP iterations</t>
+        </is>
+      </c>
+      <c r="D23" s="86" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="006B7280"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>How To Use This Tracker</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Quick guide for all stakeholders</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="71" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B3" s="71" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="C3" s="71" t="inlineStr">
+        <is>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+      <c r="D3" s="71" t="inlineStr">
+        <is>
+          <t>Who Updates</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Team Overview</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>See all 7 internal teams, current sprint, status at a glance</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Every sprint</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Engineering Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Resource Allocation</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Internal + external assignments per member, shared &amp; outsource flags</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>When team changes</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Engineering Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Project Roadmap</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Track project start/end, achievements, next targets, alignment</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Every sprint</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Tech Leads</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Sprint Tracker</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Detailed sprint goals, outcomes, tech lead feedback, blockers</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Every sprint</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Tech Leads</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Member Performance</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Individual progress, ratings, achievements</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Every sprint</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Tech Leads</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>2026 Targets</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Quarterly milestones and year-end goals per team</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Engineering Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>External Projects</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Track resources on external / outsource / partner projects</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>When assignments change</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Engineering Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Release Dashboard</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>At-a-glance: latest release, totals, and next planned per product</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Every release</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Engineering Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Release History</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Full log of every release: MVP, minor, major, hotfix, patch, sprint</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Every release</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Tech Leads</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Release Standard</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Versioning policy, naming convention, release types — share with all teams</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Reference only</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="87" t="inlineStr">
+        <is>
+          <t>STATUS LEGEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ●  ✅ Completed</t>
+        </is>
+      </c>
+      <c r="B16" s="73" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ●  ▶ In Progress / On Track</t>
+        </is>
+      </c>
+      <c r="B17" s="73" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ●  At Risk</t>
+        </is>
+      </c>
+      <c r="B18" s="73" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ●  Blocked</t>
+        </is>
+      </c>
+      <c r="B19" s="73" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ●  Not Started</t>
+        </is>
+      </c>
+      <c r="B20" s="73" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -9204,272 +10104,1811 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="006B7280"/>
+    <tabColor rgb="000EA5E9"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>How To Use This Tracker</t>
+          <t>Release Dashboard — All Products 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Quick guide for all stakeholders</t>
+          <t>At-a-glance: latest release, total count, and next planned for every product</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="58" t="inlineStr">
         <is>
-          <t>Sheet</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B3" s="58" t="inlineStr">
         <is>
-          <t>Purpose</t>
+          <t>Latest Version</t>
         </is>
       </c>
       <c r="C3" s="58" t="inlineStr">
         <is>
-          <t>Update Frequency</t>
+          <t>Latest Release</t>
         </is>
       </c>
       <c r="D3" s="58" t="inlineStr">
         <is>
-          <t>Who Updates</t>
+          <t>Release Date</t>
+        </is>
+      </c>
+      <c r="E3" s="58" t="inlineStr">
+        <is>
+          <t>Total Releases</t>
+        </is>
+      </c>
+      <c r="F3" s="58" t="inlineStr">
+        <is>
+          <t>Hotfixes</t>
+        </is>
+      </c>
+      <c r="G3" s="58" t="inlineStr">
+        <is>
+          <t>Next Planned</t>
+        </is>
+      </c>
+      <c r="H3" s="58" t="inlineStr">
+        <is>
+          <t>Next Version</t>
+        </is>
+      </c>
+      <c r="I3" s="58" t="inlineStr">
+        <is>
+          <t>Target Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="59" t="inlineStr">
+        <is>
+          <t>📏  Versioning Standard: vMAJOR.MINOR.PATCH  •  Types: MVP | Major | Minor | Hotfix | Patch | Sprint  •  Quarterly releases + hotfixes as needed</t>
+        </is>
+      </c>
+      <c r="B4" s="60" t="n"/>
+      <c r="C4" s="60" t="n"/>
+      <c r="D4" s="60" t="n"/>
+      <c r="E4" s="60" t="n"/>
+      <c r="F4" s="60" t="n"/>
+      <c r="G4" s="60" t="n"/>
+      <c r="H4" s="60" t="n"/>
+      <c r="I4" s="60" t="n"/>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="49" t="inlineStr">
+        <is>
+          <t>AG ONE</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>v1.0.2</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>AG ONE Hotfix 2</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>08 Apr 2026</t>
+        </is>
+      </c>
+      <c r="E5" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="62" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>AG ONE Q2 Enhancement</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="51" t="inlineStr">
+        <is>
+          <t>OneWork</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>OneWork MVP</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>29 Mar 2026</t>
+        </is>
+      </c>
+      <c r="E6" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>OneWork Q2 Enhancement</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="52" t="inlineStr">
+        <is>
+          <t>Learn</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Learn MVP</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>29 Mar 2026</t>
+        </is>
+      </c>
+      <c r="E7" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Learn Analytics</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="53" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Safe MVP</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>29 Mar 2026</t>
+        </is>
+      </c>
+      <c r="E8" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Safe Regulatory Auto</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="54" t="inlineStr">
+        <is>
+          <t>OneHire</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>OneHire Alpha</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>v0.1.0</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="55" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Spot Alpha</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>v0.1.0</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="56" t="inlineStr">
+        <is>
+          <t>Pulse</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Pulse Alpha</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>v0.1.0</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL ACROSS ALL PRODUCTS</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="64" t="inlineStr">
+        <is>
+          <t>19 releases planned</t>
+        </is>
+      </c>
+      <c r="H13" s="65" t="n"/>
+      <c r="I13" s="65" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A13:D13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000284C7"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Release History — Full Log 2026</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Every release across all products: MVP, minor, major, hotfix, patch, sprint releases</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="66" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="66" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C3" s="66" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="D3" s="66" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="E3" s="66" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F3" s="66" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G3" s="66" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="H3" s="66" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I3" s="66" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Team Overview</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>See all 7 internal teams, current sprint, status at a glance</t>
+      <c r="A4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>AG ONE</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>Every sprint</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Engineering Manager</t>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>AG ONE MVP</t>
+        </is>
+      </c>
+      <c r="E4" s="67" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>29 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>✅ Released</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Full IAM platform: Users, Roles, Tenants, SSO, Permissions, Audit, Assign Access</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Resource Allocation</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>Internal + external assignments per member, shared &amp; outsource flags</t>
+      <c r="A5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>AG ONE</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>When team changes</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Engineering Manager</t>
+          <t>v1.0.1</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>AG ONE Hotfix 1</t>
+        </is>
+      </c>
+      <c r="E5" s="68" t="inlineStr">
+        <is>
+          <t>Hotfix</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>02 Apr 2026</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>✅ Released</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>SSO token refresh loop fix, role sync cache invalidation, tenant switching fix</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Project Roadmap</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>Track project start/end, achievements, next targets, alignment</t>
+      <c r="A6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>AG ONE</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Every sprint</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Tech Leads</t>
+          <t>v1.0.2</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>AG ONE Hotfix 2</t>
+        </is>
+      </c>
+      <c r="E6" s="68" t="inlineStr">
+        <is>
+          <t>Hotfix</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>08 Apr 2026</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>✅ Released</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>Audit log pagination, API key duplicate name validation, timezone fix</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Sprint Tracker</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Detailed sprint goals, outcomes, tech lead feedback, blockers</t>
+      <c r="A7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>AG ONE</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Every sprint</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Tech Leads</t>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>AG ONE Q2 Enhancement</t>
+        </is>
+      </c>
+      <c r="E7" s="69" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 9–10</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Advanced user analytics, bulk role operations, enhanced audit dashboard</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Member Performance</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>Individual progress, ratings, achievements</t>
+      <c r="A8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>AG ONE</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Every sprint</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>Tech Leads</t>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>AG ONE Multi-Product Admin</t>
+        </is>
+      </c>
+      <c r="E8" s="69" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 13–14</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>Multi-product admin console, cross-product role mapping, API marketplace v1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>2026 Targets</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Quarterly milestones and year-end goals per team</t>
+      <c r="A9" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>AG ONE</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Engineering Manager</t>
+          <t>v2.0.0</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>AG ONE Enterprise</t>
+        </is>
+      </c>
+      <c r="E9" s="69" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 20–22</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise SSO (SAML+OIDC), advanced RBAC, white-label branding, scale</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>External Projects</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Track resources on external / outsource / partner projects</t>
+      <c r="A10" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>OneWork</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>When assignments change</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Engineering Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>OneWork MVP</t>
+        </is>
+      </c>
+      <c r="E10" s="67" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>29 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>✅ Released</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Employee mgmt, workflows, task mgmt, dashboards, reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>OneWork</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>OneWork Q2 Enhancement</t>
+        </is>
+      </c>
+      <c r="E11" s="69" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 11–12</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Advanced workflow templates, email notifications, calendar integration</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="59" t="inlineStr">
-        <is>
-          <t>STATUS LEGEND</t>
+      <c r="A12" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>OneWork</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>OneWork Reporting v2</t>
+        </is>
+      </c>
+      <c r="E12" s="69" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 15–16</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Reporting v2 with charts, mobile-responsive, third-party integrations</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ●  ✅ Completed</t>
-        </is>
-      </c>
-      <c r="B13" s="61" t="n"/>
+      <c r="A13" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>OneWork</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>v2.0.0</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>OneWork Enterprise</t>
+        </is>
+      </c>
+      <c r="E13" s="69" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Nov 2026</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 21–23</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>AI-powered insights, advanced automation, enterprise scale</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ●  ▶ In Progress / On Track</t>
-        </is>
-      </c>
-      <c r="B14" s="61" t="n"/>
+      <c r="A14" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>Learn</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Learn MVP</t>
+        </is>
+      </c>
+      <c r="E14" s="67" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>29 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="inlineStr">
+        <is>
+          <t>✅ Released</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Courses, learning paths, assessments, certifications, progress tracking</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ●  At Risk</t>
-        </is>
-      </c>
-      <c r="B15" s="61" t="n"/>
+      <c r="A15" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>Learn</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Learn Analytics</t>
+        </is>
+      </c>
+      <c r="E15" s="69" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 11–12</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Advanced analytics dashboard, learner recommendations, completion reports</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ●  Blocked</t>
-        </is>
-      </c>
-      <c r="B16" s="61" t="n"/>
+      <c r="A16" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>Learn</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Learn Marketplace</t>
+        </is>
+      </c>
+      <c r="E16" s="69" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 15–16</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>Content marketplace, SCORM support, mobile-responsive learning</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ●  Not Started</t>
-        </is>
-      </c>
-      <c r="B17" s="61" t="n"/>
+      <c r="A17" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="35" t="inlineStr">
+        <is>
+          <t>Learn</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>v2.0.0</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Learn Enterprise</t>
+        </is>
+      </c>
+      <c r="E17" s="69" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Nov 2026</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 21–23</t>
+        </is>
+      </c>
+      <c r="H17" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>AI recommendations, adaptive learning, full mobile app</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="36" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Safe MVP</t>
+        </is>
+      </c>
+      <c r="E18" s="67" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>29 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>✅ Released</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Policies, compliance tracking, audit workflows, risk matrix, dashboards</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="36" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Safe Regulatory Auto</t>
+        </is>
+      </c>
+      <c r="E19" s="69" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 11–12</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Regulatory update automation, scheduled compliance checks, advanced reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="36" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Safe Integrations</t>
+        </is>
+      </c>
+      <c r="E20" s="69" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 17–18</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>Third-party GRC integrations, automated alerts, evidence collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="36" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>v2.0.0</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Safe Enterprise</t>
+        </is>
+      </c>
+      <c r="E21" s="69" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 24–26</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise compliance suite with AI-driven risk predictions</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="37" t="inlineStr">
+        <is>
+          <t>OneHire</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>v0.1.0</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>OneHire Alpha</t>
+        </is>
+      </c>
+      <c r="E22" s="70" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 9–10</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>Core job posting and applicant tracking features</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="37" t="inlineStr">
+        <is>
+          <t>OneHire</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>v0.5.0</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>OneHire Beta</t>
+        </is>
+      </c>
+      <c r="E23" s="70" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 11–12</t>
+        </is>
+      </c>
+      <c r="H23" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Interview scheduling, candidate pipeline, basic reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="37" t="inlineStr">
+        <is>
+          <t>OneHire</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>OneHire MVP</t>
+        </is>
+      </c>
+      <c r="E24" s="67" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 13–14</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>Full recruitment portal with applicant tracking and analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="38" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>v0.1.0</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Spot Alpha</t>
+        </is>
+      </c>
+      <c r="E25" s="70" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 9–10</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Core city module, location management</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="38" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Spot MVP</t>
+        </is>
+      </c>
+      <c r="E26" s="67" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 17–18</t>
+        </is>
+      </c>
+      <c r="H26" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>City management, geolocation features, admin dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="39" t="inlineStr">
+        <is>
+          <t>Pulse</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>v0.1.0</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Pulse Alpha</t>
+        </is>
+      </c>
+      <c r="E27" s="70" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 9–10</t>
+        </is>
+      </c>
+      <c r="H27" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Survey builder, basic distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="39" t="inlineStr">
+        <is>
+          <t>Pulse</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>Pulse MVP</t>
+        </is>
+      </c>
+      <c r="E28" s="67" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 17–18</t>
+        </is>
+      </c>
+      <c r="H28" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Survey analytics, employee engagement dashboards, benchmarking</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="13" t="n"/>
+      <c r="I30" s="14" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n"/>
+      <c r="I31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
+      <c r="G32" s="13" t="n"/>
+      <c r="H32" s="13" t="n"/>
+      <c r="I32" s="14" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="13" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="13" t="n"/>
+      <c r="G34" s="13" t="n"/>
+      <c r="H34" s="13" t="n"/>
+      <c r="I34" s="14" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="13" t="n"/>
+      <c r="C36" s="13" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="13" t="n"/>
+      <c r="G36" s="13" t="n"/>
+      <c r="H36" s="13" t="n"/>
+      <c r="I36" s="14" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="13" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="13" t="n"/>
+      <c r="H38" s="13" t="n"/>
+      <c r="I38" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A17:B17"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/AG_ONE_Team_Tracker_2026.xlsx
+++ b/AG_ONE_Team_Tracker_2026.xlsx
@@ -15,9 +15,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026 Targets" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Projects" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release History" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Standard" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Use" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rel-AG ONE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rel-OneWork" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rel-Learn" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rel-Safe" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rel-OneHire" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rel-Spot" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rel-Pulse" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Standard" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Use" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -164,6 +170,18 @@
       <b val="1"/>
       <color rgb="006B7280"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00374151"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="000369A1"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -394,7 +412,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -569,22 +587,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -616,7 +661,7 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -628,12 +673,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1351,6 +1396,2245 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="003B82F6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>OneWork — Release History &amp; Roadmap 2026</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>All releases for OneWork  •  Lead: Abdullah  •  Team: Abdullah, Nastaran, Jawad, Geena</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
+        <is>
+          <t>Released: 1  •  Hotfixes: 0  •  Planned: 3  •  Latest: v1.0.0  •  Next: v1.1.0 (Jun 2026)</t>
+        </is>
+      </c>
+      <c r="B3" s="66" t="n"/>
+      <c r="C3" s="66" t="n"/>
+      <c r="D3" s="66" t="n"/>
+      <c r="E3" s="66" t="n"/>
+      <c r="F3" s="66" t="n"/>
+      <c r="G3" s="66" t="n"/>
+      <c r="H3" s="66" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="67" t="inlineStr">
+        <is>
+          <t>✅  RELEASED</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="69" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>OneWork MVP</t>
+        </is>
+      </c>
+      <c r="D6" s="70" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>29 Mar 2026</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G6" s="70" t="inlineStr">
+        <is>
+          <t>✅ Released</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Employee mgmt, workflows, task mgmt, dashboards, reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="73" t="inlineStr">
+        <is>
+          <t>📋  UPCOMING / PLANNED</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="n"/>
+      <c r="C8" s="60" t="n"/>
+      <c r="D8" s="60" t="n"/>
+      <c r="E8" s="60" t="n"/>
+      <c r="F8" s="60" t="n"/>
+      <c r="G8" s="60" t="n"/>
+      <c r="H8" s="60" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="74" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="74" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C9" s="74" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="D9" s="74" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E9" s="74" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F9" s="74" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="G9" s="74" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H9" s="74" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="69" t="inlineStr">
+        <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>OneWork Q2 Enhancement</t>
+        </is>
+      </c>
+      <c r="D10" s="75" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 11–12</t>
+        </is>
+      </c>
+      <c r="G10" s="76" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>Advanced workflow templates, email notifications, calendar integration</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="71" t="inlineStr">
+        <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>OneWork Reporting v2</t>
+        </is>
+      </c>
+      <c r="D11" s="75" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 15–16</t>
+        </is>
+      </c>
+      <c r="G11" s="76" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Reporting v2 with charts, mobile-responsive, third-party integrations</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="69" t="inlineStr">
+        <is>
+          <t>v2.0.0</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>OneWork Enterprise</t>
+        </is>
+      </c>
+      <c r="D12" s="75" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Nov 2026</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 21–23</t>
+        </is>
+      </c>
+      <c r="G12" s="76" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>AI-powered insights, advanced automation, enterprise scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="14" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A8:H8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="008B5CF6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Learn — Release History &amp; Roadmap 2026</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>All releases for Learn  •  Lead: Ricky  •  Team: Ricky, Loc, Than</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="30" t="inlineStr">
+        <is>
+          <t>Released: 1  •  Hotfixes: 0  •  Planned: 3  •  Latest: v1.0.0  •  Next: v1.1.0 (Jun 2026)</t>
+        </is>
+      </c>
+      <c r="B3" s="77" t="n"/>
+      <c r="C3" s="77" t="n"/>
+      <c r="D3" s="77" t="n"/>
+      <c r="E3" s="77" t="n"/>
+      <c r="F3" s="77" t="n"/>
+      <c r="G3" s="77" t="n"/>
+      <c r="H3" s="77" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="67" t="inlineStr">
+        <is>
+          <t>✅  RELEASED</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H5" s="31" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="69" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Learn MVP</t>
+        </is>
+      </c>
+      <c r="D6" s="70" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>29 Mar 2026</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G6" s="70" t="inlineStr">
+        <is>
+          <t>✅ Released</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Courses, learning paths, assessments, certifications, progress tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="73" t="inlineStr">
+        <is>
+          <t>📋  UPCOMING / PLANNED</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="n"/>
+      <c r="C8" s="60" t="n"/>
+      <c r="D8" s="60" t="n"/>
+      <c r="E8" s="60" t="n"/>
+      <c r="F8" s="60" t="n"/>
+      <c r="G8" s="60" t="n"/>
+      <c r="H8" s="60" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="74" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="74" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C9" s="74" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="D9" s="74" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E9" s="74" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F9" s="74" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="G9" s="74" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H9" s="74" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="69" t="inlineStr">
+        <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Learn Analytics</t>
+        </is>
+      </c>
+      <c r="D10" s="75" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 11–12</t>
+        </is>
+      </c>
+      <c r="G10" s="76" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>Advanced analytics dashboard, learner recommendations, completion reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="71" t="inlineStr">
+        <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Learn Marketplace</t>
+        </is>
+      </c>
+      <c r="D11" s="75" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 15–16</t>
+        </is>
+      </c>
+      <c r="G11" s="76" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Content marketplace, SCORM support, mobile-responsive learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="69" t="inlineStr">
+        <is>
+          <t>v2.0.0</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Learn Enterprise</t>
+        </is>
+      </c>
+      <c r="D12" s="75" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Nov 2026</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 21–23</t>
+        </is>
+      </c>
+      <c r="G12" s="76" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>AI recommendations, adaptive learning, full mobile app</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="14" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A8:H8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0010B981"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Safe — Release History &amp; Roadmap 2026</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>All releases for Safe  •  Lead: Faisal  •  Team: Faisal, Surya, Kiritini</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>Released: 1  •  Hotfixes: 0  •  Planned: 3  •  Latest: v1.0.0  •  Next: v1.1.0 (Jun 2026)</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
+      <c r="F3" s="7" t="n"/>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="67" t="inlineStr">
+        <is>
+          <t>✅  RELEASED</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C5" s="40" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="D5" s="40" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E5" s="40" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F5" s="40" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="G5" s="40" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H5" s="40" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="69" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Safe MVP</t>
+        </is>
+      </c>
+      <c r="D6" s="70" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>29 Mar 2026</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="G6" s="70" t="inlineStr">
+        <is>
+          <t>✅ Released</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Policies, compliance tracking, audit workflows, risk matrix, dashboards</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="73" t="inlineStr">
+        <is>
+          <t>📋  UPCOMING / PLANNED</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="n"/>
+      <c r="C8" s="60" t="n"/>
+      <c r="D8" s="60" t="n"/>
+      <c r="E8" s="60" t="n"/>
+      <c r="F8" s="60" t="n"/>
+      <c r="G8" s="60" t="n"/>
+      <c r="H8" s="60" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="74" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="74" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C9" s="74" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="D9" s="74" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E9" s="74" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F9" s="74" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="G9" s="74" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H9" s="74" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="69" t="inlineStr">
+        <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Safe Regulatory Auto</t>
+        </is>
+      </c>
+      <c r="D10" s="75" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 11–12</t>
+        </is>
+      </c>
+      <c r="G10" s="76" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>Regulatory update automation, scheduled compliance checks, advanced reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="71" t="inlineStr">
+        <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Safe Integrations</t>
+        </is>
+      </c>
+      <c r="D11" s="75" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 17–18</t>
+        </is>
+      </c>
+      <c r="G11" s="76" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Third-party GRC integrations, automated alerts, evidence collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="69" t="inlineStr">
+        <is>
+          <t>v2.0.0</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Safe Enterprise</t>
+        </is>
+      </c>
+      <c r="D12" s="75" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 24–26</t>
+        </is>
+      </c>
+      <c r="G12" s="76" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>Enterprise compliance suite with AI-driven risk predictions</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="14" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A8:H8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>OneHire — Release History &amp; Roadmap 2026</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>All releases for OneHire  •  Lead: Logesh  •  Team: Logesh, Hanis, Fatin, Sharuti</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>Released: 0  •  Hotfixes: 0  •  Planned: 3  •  Latest: —  •  Next: v0.1.0 (May 2026)</t>
+        </is>
+      </c>
+      <c r="B3" s="78" t="n"/>
+      <c r="C3" s="78" t="n"/>
+      <c r="D3" s="78" t="n"/>
+      <c r="E3" s="78" t="n"/>
+      <c r="F3" s="78" t="n"/>
+      <c r="G3" s="78" t="n"/>
+      <c r="H3" s="78" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="67" t="inlineStr">
+        <is>
+          <t>✅  RELEASED</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="45" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="45" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C5" s="45" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="D5" s="45" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E5" s="45" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F5" s="45" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="G5" s="45" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H5" s="45" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="79" t="inlineStr">
+        <is>
+          <t>No releases yet</t>
+        </is>
+      </c>
+      <c r="B6" s="80" t="n"/>
+      <c r="C6" s="80" t="n"/>
+      <c r="D6" s="80" t="n"/>
+      <c r="E6" s="80" t="n"/>
+      <c r="F6" s="80" t="n"/>
+      <c r="G6" s="80" t="n"/>
+      <c r="H6" s="80" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="73" t="inlineStr">
+        <is>
+          <t>📋  UPCOMING / PLANNED</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="n"/>
+      <c r="C8" s="60" t="n"/>
+      <c r="D8" s="60" t="n"/>
+      <c r="E8" s="60" t="n"/>
+      <c r="F8" s="60" t="n"/>
+      <c r="G8" s="60" t="n"/>
+      <c r="H8" s="60" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="74" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="74" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C9" s="74" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="D9" s="74" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E9" s="74" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F9" s="74" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="G9" s="74" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H9" s="74" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="69" t="inlineStr">
+        <is>
+          <t>v0.1.0</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>OneHire Alpha</t>
+        </is>
+      </c>
+      <c r="D10" s="81" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 9–10</t>
+        </is>
+      </c>
+      <c r="G10" s="76" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>Core job posting and applicant tracking features</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="71" t="inlineStr">
+        <is>
+          <t>v0.5.0</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>OneHire Beta</t>
+        </is>
+      </c>
+      <c r="D11" s="81" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 11–12</t>
+        </is>
+      </c>
+      <c r="G11" s="76" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Interview scheduling, candidate pipeline, basic reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="69" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>OneHire MVP</t>
+        </is>
+      </c>
+      <c r="D12" s="70" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 13–14</t>
+        </is>
+      </c>
+      <c r="G12" s="76" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>Full recruitment portal with applicant tracking and analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="14" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A6:H6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00EF4444"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Spot — Release History &amp; Roadmap 2026</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>All releases for Spot  •  Lead: Ricky  •  Team: Ricky, Loc, Than, Majed, Hema</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>Released: 0  •  Hotfixes: 0  •  Planned: 2  •  Latest: —  •  Next: v0.1.0 (May 2026)</t>
+        </is>
+      </c>
+      <c r="B3" s="82" t="n"/>
+      <c r="C3" s="82" t="n"/>
+      <c r="D3" s="82" t="n"/>
+      <c r="E3" s="82" t="n"/>
+      <c r="F3" s="82" t="n"/>
+      <c r="G3" s="82" t="n"/>
+      <c r="H3" s="82" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="67" t="inlineStr">
+        <is>
+          <t>✅  RELEASED</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="48" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C5" s="48" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="D5" s="48" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E5" s="48" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F5" s="48" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H5" s="48" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="79" t="inlineStr">
+        <is>
+          <t>No releases yet</t>
+        </is>
+      </c>
+      <c r="B6" s="80" t="n"/>
+      <c r="C6" s="80" t="n"/>
+      <c r="D6" s="80" t="n"/>
+      <c r="E6" s="80" t="n"/>
+      <c r="F6" s="80" t="n"/>
+      <c r="G6" s="80" t="n"/>
+      <c r="H6" s="80" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="73" t="inlineStr">
+        <is>
+          <t>📋  UPCOMING / PLANNED</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="n"/>
+      <c r="C8" s="60" t="n"/>
+      <c r="D8" s="60" t="n"/>
+      <c r="E8" s="60" t="n"/>
+      <c r="F8" s="60" t="n"/>
+      <c r="G8" s="60" t="n"/>
+      <c r="H8" s="60" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="74" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="74" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C9" s="74" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="D9" s="74" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E9" s="74" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F9" s="74" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="G9" s="74" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H9" s="74" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="69" t="inlineStr">
+        <is>
+          <t>v0.1.0</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Spot Alpha</t>
+        </is>
+      </c>
+      <c r="D10" s="81" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 9–10</t>
+        </is>
+      </c>
+      <c r="G10" s="76" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>Core city module, location management</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="71" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Spot MVP</t>
+        </is>
+      </c>
+      <c r="D11" s="70" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 17–18</t>
+        </is>
+      </c>
+      <c r="G11" s="76" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>City management, geolocation features, admin dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="14" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A6:H6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00EC4899"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pulse — Release History &amp; Roadmap 2026</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>All releases for Pulse  •  Lead: Hanis  •  Team: Hanis, Fatin, Majed, Hema, Rahmya, Umeshawar</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>Released: 0  •  Hotfixes: 0  •  Planned: 2  •  Latest: —  •  Next: v0.1.0 (May 2026)</t>
+        </is>
+      </c>
+      <c r="B3" s="83" t="n"/>
+      <c r="C3" s="83" t="n"/>
+      <c r="D3" s="83" t="n"/>
+      <c r="E3" s="83" t="n"/>
+      <c r="F3" s="83" t="n"/>
+      <c r="G3" s="83" t="n"/>
+      <c r="H3" s="83" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="67" t="inlineStr">
+        <is>
+          <t>✅  RELEASED</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="84" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="84" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C5" s="84" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="D5" s="84" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E5" s="84" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F5" s="84" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="G5" s="84" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H5" s="84" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="79" t="inlineStr">
+        <is>
+          <t>No releases yet</t>
+        </is>
+      </c>
+      <c r="B6" s="80" t="n"/>
+      <c r="C6" s="80" t="n"/>
+      <c r="D6" s="80" t="n"/>
+      <c r="E6" s="80" t="n"/>
+      <c r="F6" s="80" t="n"/>
+      <c r="G6" s="80" t="n"/>
+      <c r="H6" s="80" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="73" t="inlineStr">
+        <is>
+          <t>📋  UPCOMING / PLANNED</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="n"/>
+      <c r="C8" s="60" t="n"/>
+      <c r="D8" s="60" t="n"/>
+      <c r="E8" s="60" t="n"/>
+      <c r="F8" s="60" t="n"/>
+      <c r="G8" s="60" t="n"/>
+      <c r="H8" s="60" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="74" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="74" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C9" s="74" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="D9" s="74" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E9" s="74" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F9" s="74" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="G9" s="74" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H9" s="74" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="69" t="inlineStr">
+        <is>
+          <t>v0.1.0</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Pulse Alpha</t>
+        </is>
+      </c>
+      <c r="D10" s="81" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 9–10</t>
+        </is>
+      </c>
+      <c r="G10" s="76" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>Survey builder, basic distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="71" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Pulse MVP</t>
+        </is>
+      </c>
+      <c r="D11" s="70" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 17–18</t>
+        </is>
+      </c>
+      <c r="G11" s="76" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Survey analytics, employee engagement dashboards, benchmarking</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr"/>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="13" t="n"/>
+      <c r="G14" s="13" t="n"/>
+      <c r="H14" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="14" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A6:H6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="000369A1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1385,14 +3669,14 @@
       <c r="D2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="71" t="inlineStr">
+      <c r="A3" s="68" t="inlineStr">
         <is>
           <t>Versioning Format</t>
         </is>
       </c>
-      <c r="B3" s="72" t="n"/>
-      <c r="C3" s="72" t="n"/>
-      <c r="D3" s="73" t="n"/>
+      <c r="B3" s="85" t="n"/>
+      <c r="C3" s="85" t="n"/>
+      <c r="D3" s="86" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="49" t="inlineStr">
@@ -1400,13 +3684,13 @@
           <t>Format</t>
         </is>
       </c>
-      <c r="B4" s="74" t="inlineStr">
+      <c r="B4" s="87" t="inlineStr">
         <is>
           <t>vMAJOR.MINOR.PATCH</t>
         </is>
       </c>
-      <c r="C4" s="75" t="n"/>
-      <c r="D4" s="76" t="inlineStr">
+      <c r="C4" s="88" t="n"/>
+      <c r="D4" s="89" t="inlineStr">
         <is>
           <t>Example: v1.2.3</t>
         </is>
@@ -1418,13 +3702,13 @@
           <t>MAJOR</t>
         </is>
       </c>
-      <c r="B5" s="74" t="inlineStr">
+      <c r="B5" s="87" t="inlineStr">
         <is>
           <t>Breaking changes or major new feature sets</t>
         </is>
       </c>
-      <c r="C5" s="75" t="n"/>
-      <c r="D5" s="76" t="inlineStr">
+      <c r="C5" s="88" t="n"/>
+      <c r="D5" s="89" t="inlineStr">
         <is>
           <t>v1.0.0 → v2.0.0</t>
         </is>
@@ -1436,13 +3720,13 @@
           <t>MINOR</t>
         </is>
       </c>
-      <c r="B6" s="74" t="inlineStr">
+      <c r="B6" s="87" t="inlineStr">
         <is>
           <t>New features, enhancements (backward compatible)</t>
         </is>
       </c>
-      <c r="C6" s="75" t="n"/>
-      <c r="D6" s="76" t="inlineStr">
+      <c r="C6" s="88" t="n"/>
+      <c r="D6" s="89" t="inlineStr">
         <is>
           <t>v1.0.0 → v1.1.0</t>
         </is>
@@ -1454,13 +3738,13 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="B7" s="74" t="inlineStr">
+      <c r="B7" s="87" t="inlineStr">
         <is>
           <t>Bug fixes, hotfixes, minor corrections</t>
         </is>
       </c>
-      <c r="C7" s="75" t="n"/>
-      <c r="D7" s="76" t="inlineStr">
+      <c r="C7" s="88" t="n"/>
+      <c r="D7" s="89" t="inlineStr">
         <is>
           <t>v1.0.0 → v1.0.1</t>
         </is>
@@ -1490,7 +3774,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="77" t="inlineStr">
+      <c r="A10" s="90" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
@@ -1512,7 +3796,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="78" t="inlineStr">
+      <c r="A11" s="91" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -1534,7 +3818,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="79" t="inlineStr">
+      <c r="A12" s="92" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -1556,7 +3840,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="80" t="inlineStr">
+      <c r="A13" s="93" t="inlineStr">
         <is>
           <t>Hotfix</t>
         </is>
@@ -1578,7 +3862,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="81" t="inlineStr">
+      <c r="A14" s="94" t="inlineStr">
         <is>
           <t>Patch</t>
         </is>
@@ -1600,7 +3884,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="82" t="inlineStr">
+      <c r="A15" s="95" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
@@ -1623,122 +3907,122 @@
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="71" t="inlineStr">
+      <c r="A17" s="68" t="inlineStr">
         <is>
           <t>Release Naming Convention</t>
         </is>
       </c>
-      <c r="B17" s="72" t="n"/>
-      <c r="C17" s="72" t="n"/>
-      <c r="D17" s="73" t="n"/>
+      <c r="B17" s="85" t="n"/>
+      <c r="C17" s="85" t="n"/>
+      <c r="D17" s="86" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="83" t="inlineStr">
+      <c r="A18" s="96" t="inlineStr">
         <is>
           <t>Pattern</t>
         </is>
       </c>
-      <c r="B18" s="84" t="inlineStr">
+      <c r="B18" s="97" t="inlineStr">
         <is>
           <t>[Product] [Type] — [Short Description]</t>
         </is>
       </c>
-      <c r="C18" s="85" t="inlineStr">
+      <c r="C18" s="98" t="inlineStr">
         <is>
           <t>Used in Release Name column</t>
         </is>
       </c>
-      <c r="D18" s="86" t="n"/>
+      <c r="D18" s="99" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="83" t="inlineStr">
+      <c r="A19" s="96" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="B19" s="84" t="inlineStr">
+      <c r="B19" s="97" t="inlineStr">
         <is>
           <t>AG ONE MVP</t>
         </is>
       </c>
-      <c r="C19" s="85" t="inlineStr">
+      <c r="C19" s="98" t="inlineStr">
         <is>
           <t>First production release</t>
         </is>
       </c>
-      <c r="D19" s="86" t="n"/>
+      <c r="D19" s="99" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="83" t="inlineStr">
+      <c r="A20" s="96" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="B20" s="84" t="inlineStr">
+      <c r="B20" s="97" t="inlineStr">
         <is>
           <t>AG ONE Q2 Enhancement</t>
         </is>
       </c>
-      <c r="C20" s="85" t="inlineStr">
+      <c r="C20" s="98" t="inlineStr">
         <is>
           <t>Quarterly feature release</t>
         </is>
       </c>
-      <c r="D20" s="86" t="n"/>
+      <c r="D20" s="99" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="83" t="inlineStr">
+      <c r="A21" s="96" t="inlineStr">
         <is>
           <t>Hotfix</t>
         </is>
       </c>
-      <c r="B21" s="84" t="inlineStr">
+      <c r="B21" s="97" t="inlineStr">
         <is>
           <t>AG ONE Hotfix 1</t>
         </is>
       </c>
-      <c r="C21" s="85" t="inlineStr">
+      <c r="C21" s="98" t="inlineStr">
         <is>
           <t>Numbered sequentially</t>
         </is>
       </c>
-      <c r="D21" s="86" t="n"/>
+      <c r="D21" s="99" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="83" t="inlineStr">
+      <c r="A22" s="96" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="B22" s="84" t="inlineStr">
+      <c r="B22" s="97" t="inlineStr">
         <is>
           <t>AG ONE Enterprise</t>
         </is>
       </c>
-      <c r="C22" s="85" t="inlineStr">
+      <c r="C22" s="98" t="inlineStr">
         <is>
           <t>Named for the theme</t>
         </is>
       </c>
-      <c r="D22" s="86" t="n"/>
+      <c r="D22" s="99" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="83" t="inlineStr">
+      <c r="A23" s="96" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="B23" s="84" t="inlineStr">
+      <c r="B23" s="97" t="inlineStr">
         <is>
           <t>OneHire Alpha / OneHire Beta</t>
         </is>
       </c>
-      <c r="C23" s="85" t="inlineStr">
+      <c r="C23" s="98" t="inlineStr">
         <is>
           <t>Pre-MVP iterations</t>
         </is>
       </c>
-      <c r="D23" s="86" t="n"/>
+      <c r="D23" s="99" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -1762,7 +4046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006B7280"/>
@@ -1799,22 +4083,22 @@
       <c r="D2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="71" t="inlineStr">
+      <c r="A3" s="68" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="71" t="inlineStr">
+      <c r="B3" s="68" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="C3" s="71" t="inlineStr">
+      <c r="C3" s="68" t="inlineStr">
         <is>
           <t>Update Frequency</t>
         </is>
       </c>
-      <c r="D3" s="71" t="inlineStr">
+      <c r="D3" s="68" t="inlineStr">
         <is>
           <t>Who Updates</t>
         </is>
@@ -1999,12 +4283,12 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Release History</t>
+          <t>Rel-[Product]</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Full log of every release: MVP, minor, major, hotfix, patch, sprint</t>
+          <t>Per-product release tab — released + upcoming with highlights (7 tabs)</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -2042,51 +4326,51 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="87" t="inlineStr">
+      <c r="A15" s="100" t="inlineStr">
         <is>
           <t>STATUS LEGEND</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="88" t="inlineStr">
+      <c r="A16" s="101" t="inlineStr">
         <is>
           <t xml:space="preserve">  ●  ✅ Completed</t>
         </is>
       </c>
-      <c r="B16" s="73" t="n"/>
+      <c r="B16" s="86" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="89" t="inlineStr">
+      <c r="A17" s="102" t="inlineStr">
         <is>
           <t xml:space="preserve">  ●  ▶ In Progress / On Track</t>
         </is>
       </c>
-      <c r="B17" s="73" t="n"/>
+      <c r="B17" s="86" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="90" t="inlineStr">
+      <c r="A18" s="103" t="inlineStr">
         <is>
           <t xml:space="preserve">  ●  At Risk</t>
         </is>
       </c>
-      <c r="B18" s="73" t="n"/>
+      <c r="B18" s="86" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="91" t="inlineStr">
+      <c r="A19" s="104" t="inlineStr">
         <is>
           <t xml:space="preserve">  ●  Blocked</t>
         </is>
       </c>
-      <c r="B19" s="73" t="n"/>
+      <c r="B19" s="86" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="92" t="inlineStr">
+      <c r="A20" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">  ●  Not Started</t>
         </is>
       </c>
-      <c r="B20" s="73" t="n"/>
+      <c r="B20" s="86" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -10555,28 +12839,27 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000284C7"/>
+    <tabColor rgb="001E3A5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Release History — Full Log 2026</t>
+          <t>AG ONE — Release History &amp; Roadmap 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10586,12 +12869,11 @@
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
       <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Every release across all products: MVP, minor, major, hotfix, patch, sprint releases</t>
+          <t>All releases for AG ONE  •  Lead: Geena  •  Team: Geena, Nastaran</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10601,1314 +12883,432 @@
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="66" t="inlineStr">
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Released: 3  •  Hotfixes: 2  •  Planned: 3  •  Latest: v1.0.2  •  Next: v1.1.0 (May 2026)</t>
+        </is>
+      </c>
+      <c r="B3" s="66" t="n"/>
+      <c r="C3" s="66" t="n"/>
+      <c r="D3" s="66" t="n"/>
+      <c r="E3" s="66" t="n"/>
+      <c r="F3" s="66" t="n"/>
+      <c r="G3" s="66" t="n"/>
+      <c r="H3" s="66" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="67" t="inlineStr">
+        <is>
+          <t>✅  RELEASED</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="68" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B3" s="66" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="C3" s="66" t="inlineStr">
+      <c r="B5" s="68" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="D3" s="66" t="inlineStr">
+      <c r="C5" s="68" t="inlineStr">
         <is>
           <t>Release Name</t>
         </is>
       </c>
-      <c r="E3" s="66" t="inlineStr">
+      <c r="D5" s="68" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="66" t="inlineStr">
+      <c r="E5" s="68" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="G3" s="66" t="inlineStr">
+      <c r="F5" s="68" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="H3" s="66" t="inlineStr">
+      <c r="G5" s="68" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I3" s="66" t="inlineStr">
+      <c r="H5" s="68" t="inlineStr">
         <is>
           <t>Highlights / What's Included</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="13" t="n">
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="32" t="inlineStr">
-        <is>
-          <t>AG ONE</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="B6" s="69" t="inlineStr">
         <is>
           <t>v1.0.0</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>AG ONE MVP</t>
         </is>
       </c>
-      <c r="E4" s="67" t="inlineStr">
+      <c r="D6" s="70" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>29 Mar 2026</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="G6" s="70" t="inlineStr">
         <is>
           <t>✅ Released</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>Full IAM platform: Users, Roles, Tenants, SSO, Permissions, Audit, Assign Access</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="9" t="n">
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>AG ONE</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="B7" s="71" t="inlineStr">
         <is>
           <t>v1.0.1</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>AG ONE Hotfix 1</t>
         </is>
       </c>
-      <c r="E5" s="68" t="inlineStr">
+      <c r="D7" s="72" t="inlineStr">
         <is>
           <t>Hotfix</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>02 Apr 2026</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="G7" s="70" t="inlineStr">
         <is>
           <t>✅ Released</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>SSO token refresh loop fix, role sync cache invalidation, tenant switching fix</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="n">
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="32" t="inlineStr">
-        <is>
-          <t>AG ONE</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="B8" s="69" t="inlineStr">
         <is>
           <t>v1.0.2</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>AG ONE Hotfix 2</t>
         </is>
       </c>
-      <c r="E6" s="68" t="inlineStr">
+      <c r="D8" s="72" t="inlineStr">
         <is>
           <t>Hotfix</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>08 Apr 2026</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>Sprint 7</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="G8" s="70" t="inlineStr">
         <is>
           <t>✅ Released</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>Audit log pagination, API key duplicate name validation, timezone fix</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="32" t="inlineStr">
-        <is>
-          <t>AG ONE</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="73" t="inlineStr">
+        <is>
+          <t>📋  UPCOMING / PLANNED</t>
+        </is>
+      </c>
+      <c r="B10" s="60" t="n"/>
+      <c r="C10" s="60" t="n"/>
+      <c r="D10" s="60" t="n"/>
+      <c r="E10" s="60" t="n"/>
+      <c r="F10" s="60" t="n"/>
+      <c r="G10" s="60" t="n"/>
+      <c r="H10" s="60" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="74" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B11" s="74" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C11" s="74" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="D11" s="74" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E11" s="74" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="F11" s="74" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="G11" s="74" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H11" s="74" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="69" t="inlineStr">
         <is>
           <t>v1.1.0</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>AG ONE Q2 Enhancement</t>
         </is>
       </c>
-      <c r="E7" s="69" t="inlineStr">
+      <c r="D12" s="75" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>Sprint 9–10</t>
         </is>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="G12" s="76" t="inlineStr">
         <is>
           <t>📋 Planned</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>Advanced user analytics, bulk role operations, enhanced audit dashboard</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="32" t="inlineStr">
-        <is>
-          <t>AG ONE</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="71" t="inlineStr">
         <is>
           <t>v1.2.0</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>AG ONE Multi-Product Admin</t>
         </is>
       </c>
-      <c r="E8" s="69" t="inlineStr">
+      <c r="D13" s="75" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Sprint 13–14</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="G13" s="76" t="inlineStr">
         <is>
           <t>📋 Planned</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Multi-product admin console, cross-product role mapping, API marketplace v1</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="32" t="inlineStr">
-        <is>
-          <t>AG ONE</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="69" t="inlineStr">
         <is>
           <t>v2.0.0</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>AG ONE Enterprise</t>
         </is>
       </c>
-      <c r="E9" s="69" t="inlineStr">
+      <c r="D14" s="75" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>Sprint 20–22</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="G14" s="76" t="inlineStr">
         <is>
           <t>📋 Planned</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>Enterprise SSO (SAML+OIDC), advanced RBAC, white-label branding, scale</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="34" t="inlineStr">
-        <is>
-          <t>OneWork</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>OneWork MVP</t>
-        </is>
-      </c>
-      <c r="E10" s="67" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>29 Mar 2026</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>✅ Released</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>Employee mgmt, workflows, task mgmt, dashboards, reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>OneWork</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>OneWork Q2 Enhancement</t>
-        </is>
-      </c>
-      <c r="E11" s="69" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 11–12</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>Advanced workflow templates, email notifications, calendar integration</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="34" t="inlineStr">
-        <is>
-          <t>OneWork</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>v1.2.0</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>OneWork Reporting v2</t>
-        </is>
-      </c>
-      <c r="E12" s="69" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>Aug 2026</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 15–16</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>Reporting v2 with charts, mobile-responsive, third-party integrations</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="34" t="inlineStr">
-        <is>
-          <t>OneWork</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>v2.0.0</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>OneWork Enterprise</t>
-        </is>
-      </c>
-      <c r="E13" s="69" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 21–23</t>
-        </is>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>AI-powered insights, advanced automation, enterprise scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="35" t="inlineStr">
-        <is>
-          <t>Learn</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>Learn MVP</t>
-        </is>
-      </c>
-      <c r="E14" s="67" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>29 Mar 2026</t>
-        </is>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t>✅ Released</t>
-        </is>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>Courses, learning paths, assessments, certifications, progress tracking</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>Learn</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Learn Analytics</t>
-        </is>
-      </c>
-      <c r="E15" s="69" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 11–12</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>Advanced analytics dashboard, learner recommendations, completion reports</t>
-        </is>
-      </c>
-    </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>Learn</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>v1.2.0</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>Learn Marketplace</t>
-        </is>
-      </c>
-      <c r="E16" s="69" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>Aug 2026</t>
-        </is>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 15–16</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>Content marketplace, SCORM support, mobile-responsive learning</t>
-        </is>
-      </c>
+      <c r="A16" s="13" t="inlineStr"/>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="14" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="35" t="inlineStr">
-        <is>
-          <t>Learn</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>v2.0.0</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>Learn Enterprise</t>
-        </is>
-      </c>
-      <c r="E17" s="69" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 21–23</t>
-        </is>
-      </c>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>AI recommendations, adaptive learning, full mobile app</t>
-        </is>
-      </c>
+      <c r="A17" s="9" t="inlineStr"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="36" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>Safe MVP</t>
-        </is>
-      </c>
-      <c r="E18" s="67" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>29 Mar 2026</t>
-        </is>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr">
-        <is>
-          <t>✅ Released</t>
-        </is>
-      </c>
-      <c r="I18" s="14" t="inlineStr">
-        <is>
-          <t>Policies, compliance tracking, audit workflows, risk matrix, dashboards</t>
-        </is>
-      </c>
+      <c r="A18" s="13" t="inlineStr"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="36" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Safe Regulatory Auto</t>
-        </is>
-      </c>
-      <c r="E19" s="69" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 11–12</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>Regulatory update automation, scheduled compliance checks, advanced reporting</t>
-        </is>
-      </c>
+      <c r="A19" s="9" t="inlineStr"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="36" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>v1.2.0</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>Safe Integrations</t>
-        </is>
-      </c>
-      <c r="E20" s="69" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G20" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 17–18</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>Third-party GRC integrations, automated alerts, evidence collection</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="36" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>v2.0.0</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Safe Enterprise</t>
-        </is>
-      </c>
-      <c r="E21" s="69" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 24–26</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
-        <is>
-          <t>Enterprise compliance suite with AI-driven risk predictions</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="37" t="inlineStr">
-        <is>
-          <t>OneHire</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>v0.1.0</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>OneHire Alpha</t>
-        </is>
-      </c>
-      <c r="E22" s="70" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 9–10</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>Core job posting and applicant tracking features</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="37" t="inlineStr">
-        <is>
-          <t>OneHire</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>v0.5.0</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>OneHire Beta</t>
-        </is>
-      </c>
-      <c r="E23" s="70" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 11–12</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Interview scheduling, candidate pipeline, basic reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="37" t="inlineStr">
-        <is>
-          <t>OneHire</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>OneHire MVP</t>
-        </is>
-      </c>
-      <c r="E24" s="67" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 13–14</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>Full recruitment portal with applicant tracking and analytics</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="38" t="inlineStr">
-        <is>
-          <t>Spot</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>v0.1.0</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>Spot Alpha</t>
-        </is>
-      </c>
-      <c r="E25" s="70" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 9–10</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
-        <is>
-          <t>Core city module, location management</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="38" t="inlineStr">
-        <is>
-          <t>Spot</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>Spot MVP</t>
-        </is>
-      </c>
-      <c r="E26" s="67" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 17–18</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>City management, geolocation features, admin dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="39" t="inlineStr">
-        <is>
-          <t>Pulse</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>v0.1.0</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>Pulse Alpha</t>
-        </is>
-      </c>
-      <c r="E27" s="70" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 9–10</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>Survey builder, basic distribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" s="39" t="inlineStr">
-        <is>
-          <t>Pulse</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Pulse MVP</t>
-        </is>
-      </c>
-      <c r="E28" s="67" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 17–18</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>Survey analytics, employee engagement dashboards, benchmarking</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="10" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="14" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="10" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="14" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="10" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="13" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="14" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="14" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="10" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="14" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="13" t="n"/>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="14" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="10" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="14" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="13" t="n"/>
-      <c r="H38" s="13" t="n"/>
-      <c r="I38" s="14" t="n"/>
+      <c r="A20" s="13" t="inlineStr"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="n"/>
+      <c r="H20" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+  <mergeCells count="5">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/AG_ONE_Team_Tracker_2026.xlsx
+++ b/AG_ONE_Team_Tracker_2026.xlsx
@@ -15,15 +15,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026 Targets" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Projects" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rel-AG ONE" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rel-OneWork" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rel-Learn" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rel-Safe" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rel-OneHire" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rel-Spot" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rel-Pulse" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Standard" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Use" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release History" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Standard" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Use" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="31">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -170,18 +164,6 @@
       <b val="1"/>
       <color rgb="006B7280"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="00374151"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="000369A1"/>
-      <sz val="12"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -337,8 +319,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000284C7"/>
-        <bgColor rgb="000284C7"/>
+        <fgColor rgb="00475569"/>
+        <bgColor rgb="00475569"/>
       </patternFill>
     </fill>
   </fills>
@@ -412,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -587,49 +569,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -661,7 +647,7 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -673,12 +659,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1396,2245 +1382,6 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="003B82F6"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>OneWork — Release History &amp; Roadmap 2026</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>All releases for OneWork  •  Lead: Abdullah  •  Team: Abdullah, Nastaran, Jawad, Geena</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
-        <is>
-          <t>Released: 1  •  Hotfixes: 0  •  Planned: 3  •  Latest: v1.0.0  •  Next: v1.1.0 (Jun 2026)</t>
-        </is>
-      </c>
-      <c r="B3" s="66" t="n"/>
-      <c r="C3" s="66" t="n"/>
-      <c r="D3" s="66" t="n"/>
-      <c r="E3" s="66" t="n"/>
-      <c r="F3" s="66" t="n"/>
-      <c r="G3" s="66" t="n"/>
-      <c r="H3" s="66" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="67" t="inlineStr">
-        <is>
-          <t>✅  RELEASED</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="69" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>OneWork MVP</t>
-        </is>
-      </c>
-      <c r="D6" s="70" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>29 Mar 2026</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G6" s="70" t="inlineStr">
-        <is>
-          <t>✅ Released</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>Employee mgmt, workflows, task mgmt, dashboards, reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="73" t="inlineStr">
-        <is>
-          <t>📋  UPCOMING / PLANNED</t>
-        </is>
-      </c>
-      <c r="B8" s="60" t="n"/>
-      <c r="C8" s="60" t="n"/>
-      <c r="D8" s="60" t="n"/>
-      <c r="E8" s="60" t="n"/>
-      <c r="F8" s="60" t="n"/>
-      <c r="G8" s="60" t="n"/>
-      <c r="H8" s="60" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="74" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B9" s="74" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C9" s="74" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="D9" s="74" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E9" s="74" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F9" s="74" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="G9" s="74" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H9" s="74" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="69" t="inlineStr">
-        <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>OneWork Q2 Enhancement</t>
-        </is>
-      </c>
-      <c r="D10" s="75" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 11–12</t>
-        </is>
-      </c>
-      <c r="G10" s="76" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>Advanced workflow templates, email notifications, calendar integration</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="71" t="inlineStr">
-        <is>
-          <t>v1.2.0</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>OneWork Reporting v2</t>
-        </is>
-      </c>
-      <c r="D11" s="75" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Aug 2026</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 15–16</t>
-        </is>
-      </c>
-      <c r="G11" s="76" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Reporting v2 with charts, mobile-responsive, third-party integrations</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="69" t="inlineStr">
-        <is>
-          <t>v2.0.0</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>OneWork Enterprise</t>
-        </is>
-      </c>
-      <c r="D12" s="75" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 21–23</t>
-        </is>
-      </c>
-      <c r="G12" s="76" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>AI-powered insights, advanced automation, enterprise scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr"/>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="13" t="n"/>
-      <c r="H14" s="14" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr"/>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="10" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr"/>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="14" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr"/>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="14" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A8:H8"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="008B5CF6"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Learn — Release History &amp; Roadmap 2026</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>All releases for Learn  •  Lead: Ricky  •  Team: Ricky, Loc, Than</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="30" t="inlineStr">
-        <is>
-          <t>Released: 1  •  Hotfixes: 0  •  Planned: 3  •  Latest: v1.0.0  •  Next: v1.1.0 (Jun 2026)</t>
-        </is>
-      </c>
-      <c r="B3" s="77" t="n"/>
-      <c r="C3" s="77" t="n"/>
-      <c r="D3" s="77" t="n"/>
-      <c r="E3" s="77" t="n"/>
-      <c r="F3" s="77" t="n"/>
-      <c r="G3" s="77" t="n"/>
-      <c r="H3" s="77" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="67" t="inlineStr">
-        <is>
-          <t>✅  RELEASED</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F5" s="31" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="G5" s="31" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H5" s="31" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="69" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>Learn MVP</t>
-        </is>
-      </c>
-      <c r="D6" s="70" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>29 Mar 2026</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G6" s="70" t="inlineStr">
-        <is>
-          <t>✅ Released</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>Courses, learning paths, assessments, certifications, progress tracking</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="73" t="inlineStr">
-        <is>
-          <t>📋  UPCOMING / PLANNED</t>
-        </is>
-      </c>
-      <c r="B8" s="60" t="n"/>
-      <c r="C8" s="60" t="n"/>
-      <c r="D8" s="60" t="n"/>
-      <c r="E8" s="60" t="n"/>
-      <c r="F8" s="60" t="n"/>
-      <c r="G8" s="60" t="n"/>
-      <c r="H8" s="60" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="74" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B9" s="74" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C9" s="74" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="D9" s="74" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E9" s="74" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F9" s="74" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="G9" s="74" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H9" s="74" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="69" t="inlineStr">
-        <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Learn Analytics</t>
-        </is>
-      </c>
-      <c r="D10" s="75" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 11–12</t>
-        </is>
-      </c>
-      <c r="G10" s="76" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>Advanced analytics dashboard, learner recommendations, completion reports</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="71" t="inlineStr">
-        <is>
-          <t>v1.2.0</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Learn Marketplace</t>
-        </is>
-      </c>
-      <c r="D11" s="75" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Aug 2026</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 15–16</t>
-        </is>
-      </c>
-      <c r="G11" s="76" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Content marketplace, SCORM support, mobile-responsive learning</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="69" t="inlineStr">
-        <is>
-          <t>v2.0.0</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Learn Enterprise</t>
-        </is>
-      </c>
-      <c r="D12" s="75" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 21–23</t>
-        </is>
-      </c>
-      <c r="G12" s="76" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>AI recommendations, adaptive learning, full mobile app</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr"/>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="13" t="n"/>
-      <c r="H14" s="14" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr"/>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="10" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr"/>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="14" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr"/>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="14" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A8:H8"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0010B981"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Safe — Release History &amp; Roadmap 2026</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>All releases for Safe  •  Lead: Faisal  •  Team: Faisal, Surya, Kiritini</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
-        <is>
-          <t>Released: 1  •  Hotfixes: 0  •  Planned: 3  •  Latest: v1.0.0  •  Next: v1.1.0 (Jun 2026)</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="67" t="inlineStr">
-        <is>
-          <t>✅  RELEASED</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="40" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B5" s="40" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C5" s="40" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="D5" s="40" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E5" s="40" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F5" s="40" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="G5" s="40" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H5" s="40" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="69" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>Safe MVP</t>
-        </is>
-      </c>
-      <c r="D6" s="70" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>29 Mar 2026</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="G6" s="70" t="inlineStr">
-        <is>
-          <t>✅ Released</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>Policies, compliance tracking, audit workflows, risk matrix, dashboards</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="73" t="inlineStr">
-        <is>
-          <t>📋  UPCOMING / PLANNED</t>
-        </is>
-      </c>
-      <c r="B8" s="60" t="n"/>
-      <c r="C8" s="60" t="n"/>
-      <c r="D8" s="60" t="n"/>
-      <c r="E8" s="60" t="n"/>
-      <c r="F8" s="60" t="n"/>
-      <c r="G8" s="60" t="n"/>
-      <c r="H8" s="60" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="74" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B9" s="74" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C9" s="74" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="D9" s="74" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E9" s="74" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F9" s="74" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="G9" s="74" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H9" s="74" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="69" t="inlineStr">
-        <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Safe Regulatory Auto</t>
-        </is>
-      </c>
-      <c r="D10" s="75" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 11–12</t>
-        </is>
-      </c>
-      <c r="G10" s="76" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>Regulatory update automation, scheduled compliance checks, advanced reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="71" t="inlineStr">
-        <is>
-          <t>v1.2.0</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Safe Integrations</t>
-        </is>
-      </c>
-      <c r="D11" s="75" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 17–18</t>
-        </is>
-      </c>
-      <c r="G11" s="76" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Third-party GRC integrations, automated alerts, evidence collection</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="69" t="inlineStr">
-        <is>
-          <t>v2.0.0</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Safe Enterprise</t>
-        </is>
-      </c>
-      <c r="D12" s="75" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 24–26</t>
-        </is>
-      </c>
-      <c r="G12" s="76" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>Enterprise compliance suite with AI-driven risk predictions</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr"/>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="13" t="n"/>
-      <c r="H14" s="14" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr"/>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="10" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr"/>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="14" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr"/>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="14" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A8:H8"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>OneHire — Release History &amp; Roadmap 2026</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>All releases for OneHire  •  Lead: Logesh  •  Team: Logesh, Hanis, Fatin, Sharuti</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
-        <is>
-          <t>Released: 0  •  Hotfixes: 0  •  Planned: 3  •  Latest: —  •  Next: v0.1.0 (May 2026)</t>
-        </is>
-      </c>
-      <c r="B3" s="78" t="n"/>
-      <c r="C3" s="78" t="n"/>
-      <c r="D3" s="78" t="n"/>
-      <c r="E3" s="78" t="n"/>
-      <c r="F3" s="78" t="n"/>
-      <c r="G3" s="78" t="n"/>
-      <c r="H3" s="78" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="67" t="inlineStr">
-        <is>
-          <t>✅  RELEASED</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="45" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B5" s="45" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C5" s="45" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="D5" s="45" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E5" s="45" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F5" s="45" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="G5" s="45" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H5" s="45" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="79" t="inlineStr">
-        <is>
-          <t>No releases yet</t>
-        </is>
-      </c>
-      <c r="B6" s="80" t="n"/>
-      <c r="C6" s="80" t="n"/>
-      <c r="D6" s="80" t="n"/>
-      <c r="E6" s="80" t="n"/>
-      <c r="F6" s="80" t="n"/>
-      <c r="G6" s="80" t="n"/>
-      <c r="H6" s="80" t="n"/>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="73" t="inlineStr">
-        <is>
-          <t>📋  UPCOMING / PLANNED</t>
-        </is>
-      </c>
-      <c r="B8" s="60" t="n"/>
-      <c r="C8" s="60" t="n"/>
-      <c r="D8" s="60" t="n"/>
-      <c r="E8" s="60" t="n"/>
-      <c r="F8" s="60" t="n"/>
-      <c r="G8" s="60" t="n"/>
-      <c r="H8" s="60" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="74" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B9" s="74" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C9" s="74" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="D9" s="74" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E9" s="74" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F9" s="74" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="G9" s="74" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H9" s="74" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="69" t="inlineStr">
-        <is>
-          <t>v0.1.0</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>OneHire Alpha</t>
-        </is>
-      </c>
-      <c r="D10" s="81" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 9–10</t>
-        </is>
-      </c>
-      <c r="G10" s="76" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>Core job posting and applicant tracking features</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="71" t="inlineStr">
-        <is>
-          <t>v0.5.0</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>OneHire Beta</t>
-        </is>
-      </c>
-      <c r="D11" s="81" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 11–12</t>
-        </is>
-      </c>
-      <c r="G11" s="76" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Interview scheduling, candidate pipeline, basic reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="69" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>OneHire MVP</t>
-        </is>
-      </c>
-      <c r="D12" s="70" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 13–14</t>
-        </is>
-      </c>
-      <c r="G12" s="76" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>Full recruitment portal with applicant tracking and analytics</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr"/>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="13" t="n"/>
-      <c r="H14" s="14" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr"/>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="10" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr"/>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="14" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr"/>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="14" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A6:H6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00EF4444"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Spot — Release History &amp; Roadmap 2026</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>All releases for Spot  •  Lead: Ricky  •  Team: Ricky, Loc, Than, Majed, Hema</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="29" t="inlineStr">
-        <is>
-          <t>Released: 0  •  Hotfixes: 0  •  Planned: 2  •  Latest: —  •  Next: v0.1.0 (May 2026)</t>
-        </is>
-      </c>
-      <c r="B3" s="82" t="n"/>
-      <c r="C3" s="82" t="n"/>
-      <c r="D3" s="82" t="n"/>
-      <c r="E3" s="82" t="n"/>
-      <c r="F3" s="82" t="n"/>
-      <c r="G3" s="82" t="n"/>
-      <c r="H3" s="82" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="67" t="inlineStr">
-        <is>
-          <t>✅  RELEASED</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="48" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B5" s="48" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C5" s="48" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="D5" s="48" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E5" s="48" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F5" s="48" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="G5" s="48" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H5" s="48" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="79" t="inlineStr">
-        <is>
-          <t>No releases yet</t>
-        </is>
-      </c>
-      <c r="B6" s="80" t="n"/>
-      <c r="C6" s="80" t="n"/>
-      <c r="D6" s="80" t="n"/>
-      <c r="E6" s="80" t="n"/>
-      <c r="F6" s="80" t="n"/>
-      <c r="G6" s="80" t="n"/>
-      <c r="H6" s="80" t="n"/>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="73" t="inlineStr">
-        <is>
-          <t>📋  UPCOMING / PLANNED</t>
-        </is>
-      </c>
-      <c r="B8" s="60" t="n"/>
-      <c r="C8" s="60" t="n"/>
-      <c r="D8" s="60" t="n"/>
-      <c r="E8" s="60" t="n"/>
-      <c r="F8" s="60" t="n"/>
-      <c r="G8" s="60" t="n"/>
-      <c r="H8" s="60" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="74" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B9" s="74" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C9" s="74" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="D9" s="74" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E9" s="74" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F9" s="74" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="G9" s="74" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H9" s="74" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="69" t="inlineStr">
-        <is>
-          <t>v0.1.0</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Spot Alpha</t>
-        </is>
-      </c>
-      <c r="D10" s="81" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 9–10</t>
-        </is>
-      </c>
-      <c r="G10" s="76" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>Core city module, location management</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="71" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Spot MVP</t>
-        </is>
-      </c>
-      <c r="D11" s="70" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 17–18</t>
-        </is>
-      </c>
-      <c r="G11" s="76" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>City management, geolocation features, admin dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr"/>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="10" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr"/>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="13" t="n"/>
-      <c r="H14" s="14" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr"/>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="10" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr"/>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="14" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="10" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A6:H6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00EC4899"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pulse — Release History &amp; Roadmap 2026</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>All releases for Pulse  •  Lead: Hanis  •  Team: Hanis, Fatin, Majed, Hema, Rahmya, Umeshawar</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="26" t="inlineStr">
-        <is>
-          <t>Released: 0  •  Hotfixes: 0  •  Planned: 2  •  Latest: —  •  Next: v0.1.0 (May 2026)</t>
-        </is>
-      </c>
-      <c r="B3" s="83" t="n"/>
-      <c r="C3" s="83" t="n"/>
-      <c r="D3" s="83" t="n"/>
-      <c r="E3" s="83" t="n"/>
-      <c r="F3" s="83" t="n"/>
-      <c r="G3" s="83" t="n"/>
-      <c r="H3" s="83" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="67" t="inlineStr">
-        <is>
-          <t>✅  RELEASED</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="84" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B5" s="84" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C5" s="84" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="D5" s="84" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E5" s="84" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F5" s="84" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="G5" s="84" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H5" s="84" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="79" t="inlineStr">
-        <is>
-          <t>No releases yet</t>
-        </is>
-      </c>
-      <c r="B6" s="80" t="n"/>
-      <c r="C6" s="80" t="n"/>
-      <c r="D6" s="80" t="n"/>
-      <c r="E6" s="80" t="n"/>
-      <c r="F6" s="80" t="n"/>
-      <c r="G6" s="80" t="n"/>
-      <c r="H6" s="80" t="n"/>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="73" t="inlineStr">
-        <is>
-          <t>📋  UPCOMING / PLANNED</t>
-        </is>
-      </c>
-      <c r="B8" s="60" t="n"/>
-      <c r="C8" s="60" t="n"/>
-      <c r="D8" s="60" t="n"/>
-      <c r="E8" s="60" t="n"/>
-      <c r="F8" s="60" t="n"/>
-      <c r="G8" s="60" t="n"/>
-      <c r="H8" s="60" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="74" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B9" s="74" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="C9" s="74" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="D9" s="74" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E9" s="74" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="F9" s="74" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="G9" s="74" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H9" s="74" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="69" t="inlineStr">
-        <is>
-          <t>v0.1.0</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Pulse Alpha</t>
-        </is>
-      </c>
-      <c r="D10" s="81" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 9–10</t>
-        </is>
-      </c>
-      <c r="G10" s="76" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>Survey builder, basic distribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="71" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Pulse MVP</t>
-        </is>
-      </c>
-      <c r="D11" s="70" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 17–18</t>
-        </is>
-      </c>
-      <c r="G11" s="76" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Survey analytics, employee engagement dashboards, benchmarking</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr"/>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="10" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr"/>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="13" t="n"/>
-      <c r="H14" s="14" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr"/>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="10" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr"/>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="14" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="10" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A6:H6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
     <tabColor rgb="000369A1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -3669,14 +1416,14 @@
       <c r="D2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="68" t="inlineStr">
+      <c r="A3" s="86" t="inlineStr">
         <is>
           <t>Versioning Format</t>
         </is>
       </c>
-      <c r="B3" s="85" t="n"/>
-      <c r="C3" s="85" t="n"/>
-      <c r="D3" s="86" t="n"/>
+      <c r="B3" s="87" t="n"/>
+      <c r="C3" s="87" t="n"/>
+      <c r="D3" s="88" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="49" t="inlineStr">
@@ -3684,13 +1431,13 @@
           <t>Format</t>
         </is>
       </c>
-      <c r="B4" s="87" t="inlineStr">
+      <c r="B4" s="89" t="inlineStr">
         <is>
           <t>vMAJOR.MINOR.PATCH</t>
         </is>
       </c>
-      <c r="C4" s="88" t="n"/>
-      <c r="D4" s="89" t="inlineStr">
+      <c r="C4" s="90" t="n"/>
+      <c r="D4" s="91" t="inlineStr">
         <is>
           <t>Example: v1.2.3</t>
         </is>
@@ -3702,13 +1449,13 @@
           <t>MAJOR</t>
         </is>
       </c>
-      <c r="B5" s="87" t="inlineStr">
+      <c r="B5" s="89" t="inlineStr">
         <is>
           <t>Breaking changes or major new feature sets</t>
         </is>
       </c>
-      <c r="C5" s="88" t="n"/>
-      <c r="D5" s="89" t="inlineStr">
+      <c r="C5" s="90" t="n"/>
+      <c r="D5" s="91" t="inlineStr">
         <is>
           <t>v1.0.0 → v2.0.0</t>
         </is>
@@ -3720,13 +1467,13 @@
           <t>MINOR</t>
         </is>
       </c>
-      <c r="B6" s="87" t="inlineStr">
+      <c r="B6" s="89" t="inlineStr">
         <is>
           <t>New features, enhancements (backward compatible)</t>
         </is>
       </c>
-      <c r="C6" s="88" t="n"/>
-      <c r="D6" s="89" t="inlineStr">
+      <c r="C6" s="90" t="n"/>
+      <c r="D6" s="91" t="inlineStr">
         <is>
           <t>v1.0.0 → v1.1.0</t>
         </is>
@@ -3738,13 +1485,13 @@
           <t>PATCH</t>
         </is>
       </c>
-      <c r="B7" s="87" t="inlineStr">
+      <c r="B7" s="89" t="inlineStr">
         <is>
           <t>Bug fixes, hotfixes, minor corrections</t>
         </is>
       </c>
-      <c r="C7" s="88" t="n"/>
-      <c r="D7" s="89" t="inlineStr">
+      <c r="C7" s="90" t="n"/>
+      <c r="D7" s="91" t="inlineStr">
         <is>
           <t>v1.0.0 → v1.0.1</t>
         </is>
@@ -3774,7 +1521,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="90" t="inlineStr">
+      <c r="A10" s="92" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
@@ -3796,7 +1543,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="91" t="inlineStr">
+      <c r="A11" s="93" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
@@ -3818,7 +1565,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="92" t="inlineStr">
+      <c r="A12" s="94" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
@@ -3840,7 +1587,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="93" t="inlineStr">
+      <c r="A13" s="95" t="inlineStr">
         <is>
           <t>Hotfix</t>
         </is>
@@ -3862,7 +1609,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="94" t="inlineStr">
+      <c r="A14" s="96" t="inlineStr">
         <is>
           <t>Patch</t>
         </is>
@@ -3884,7 +1631,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="95" t="inlineStr">
+      <c r="A15" s="97" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
@@ -3907,122 +1654,122 @@
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="68" t="inlineStr">
+      <c r="A17" s="86" t="inlineStr">
         <is>
           <t>Release Naming Convention</t>
         </is>
       </c>
-      <c r="B17" s="85" t="n"/>
-      <c r="C17" s="85" t="n"/>
-      <c r="D17" s="86" t="n"/>
+      <c r="B17" s="87" t="n"/>
+      <c r="C17" s="87" t="n"/>
+      <c r="D17" s="88" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="96" t="inlineStr">
+      <c r="A18" s="98" t="inlineStr">
         <is>
           <t>Pattern</t>
         </is>
       </c>
-      <c r="B18" s="97" t="inlineStr">
+      <c r="B18" s="99" t="inlineStr">
         <is>
           <t>[Product] [Type] — [Short Description]</t>
         </is>
       </c>
-      <c r="C18" s="98" t="inlineStr">
+      <c r="C18" s="100" t="inlineStr">
         <is>
           <t>Used in Release Name column</t>
         </is>
       </c>
-      <c r="D18" s="99" t="n"/>
+      <c r="D18" s="101" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="96" t="inlineStr">
+      <c r="A19" s="98" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="B19" s="97" t="inlineStr">
+      <c r="B19" s="99" t="inlineStr">
         <is>
           <t>AG ONE MVP</t>
         </is>
       </c>
-      <c r="C19" s="98" t="inlineStr">
+      <c r="C19" s="100" t="inlineStr">
         <is>
           <t>First production release</t>
         </is>
       </c>
-      <c r="D19" s="99" t="n"/>
+      <c r="D19" s="101" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="96" t="inlineStr">
+      <c r="A20" s="98" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>
       </c>
-      <c r="B20" s="97" t="inlineStr">
+      <c r="B20" s="99" t="inlineStr">
         <is>
           <t>AG ONE Q2 Enhancement</t>
         </is>
       </c>
-      <c r="C20" s="98" t="inlineStr">
+      <c r="C20" s="100" t="inlineStr">
         <is>
           <t>Quarterly feature release</t>
         </is>
       </c>
-      <c r="D20" s="99" t="n"/>
+      <c r="D20" s="101" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="96" t="inlineStr">
+      <c r="A21" s="98" t="inlineStr">
         <is>
           <t>Hotfix</t>
         </is>
       </c>
-      <c r="B21" s="97" t="inlineStr">
+      <c r="B21" s="99" t="inlineStr">
         <is>
           <t>AG ONE Hotfix 1</t>
         </is>
       </c>
-      <c r="C21" s="98" t="inlineStr">
+      <c r="C21" s="100" t="inlineStr">
         <is>
           <t>Numbered sequentially</t>
         </is>
       </c>
-      <c r="D21" s="99" t="n"/>
+      <c r="D21" s="101" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="96" t="inlineStr">
+      <c r="A22" s="98" t="inlineStr">
         <is>
           <t>Major</t>
         </is>
       </c>
-      <c r="B22" s="97" t="inlineStr">
+      <c r="B22" s="99" t="inlineStr">
         <is>
           <t>AG ONE Enterprise</t>
         </is>
       </c>
-      <c r="C22" s="98" t="inlineStr">
+      <c r="C22" s="100" t="inlineStr">
         <is>
           <t>Named for the theme</t>
         </is>
       </c>
-      <c r="D22" s="99" t="n"/>
+      <c r="D22" s="101" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="96" t="inlineStr">
+      <c r="A23" s="98" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="B23" s="97" t="inlineStr">
+      <c r="B23" s="99" t="inlineStr">
         <is>
           <t>OneHire Alpha / OneHire Beta</t>
         </is>
       </c>
-      <c r="C23" s="98" t="inlineStr">
+      <c r="C23" s="100" t="inlineStr">
         <is>
           <t>Pre-MVP iterations</t>
         </is>
       </c>
-      <c r="D23" s="99" t="n"/>
+      <c r="D23" s="101" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -4046,7 +1793,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006B7280"/>
@@ -4083,22 +1830,22 @@
       <c r="D2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="68" t="inlineStr">
+      <c r="A3" s="86" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="68" t="inlineStr">
+      <c r="B3" s="86" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="C3" s="68" t="inlineStr">
+      <c r="C3" s="86" t="inlineStr">
         <is>
           <t>Update Frequency</t>
         </is>
       </c>
-      <c r="D3" s="68" t="inlineStr">
+      <c r="D3" s="86" t="inlineStr">
         <is>
           <t>Who Updates</t>
         </is>
@@ -4283,12 +2030,12 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Rel-[Product]</t>
+          <t>Release History</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Per-product release tab — released + upcoming with highlights (7 tabs)</t>
+          <t>All releases grouped by product — released + upcoming with highlights</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -4326,51 +2073,51 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="100" t="inlineStr">
+      <c r="A15" s="102" t="inlineStr">
         <is>
           <t>STATUS LEGEND</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="101" t="inlineStr">
+      <c r="A16" s="103" t="inlineStr">
         <is>
           <t xml:space="preserve">  ●  ✅ Completed</t>
         </is>
       </c>
-      <c r="B16" s="86" t="n"/>
+      <c r="B16" s="88" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="102" t="inlineStr">
+      <c r="A17" s="104" t="inlineStr">
         <is>
           <t xml:space="preserve">  ●  ▶ In Progress / On Track</t>
         </is>
       </c>
-      <c r="B17" s="86" t="n"/>
+      <c r="B17" s="88" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="103" t="inlineStr">
+      <c r="A18" s="105" t="inlineStr">
         <is>
           <t xml:space="preserve">  ●  At Risk</t>
         </is>
       </c>
-      <c r="B18" s="86" t="n"/>
+      <c r="B18" s="88" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="104" t="inlineStr">
+      <c r="A19" s="106" t="inlineStr">
         <is>
           <t xml:space="preserve">  ●  Blocked</t>
         </is>
       </c>
-      <c r="B19" s="86" t="n"/>
+      <c r="B19" s="88" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="105" t="inlineStr">
+      <c r="A20" s="107" t="inlineStr">
         <is>
           <t xml:space="preserve">  ●  Not Started</t>
         </is>
       </c>
-      <c r="B20" s="86" t="n"/>
+      <c r="B20" s="88" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -12839,27 +10586,28 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001E3A5F"/>
+    <tabColor rgb="000284C7"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AG ONE — Release History &amp; Roadmap 2026</t>
+          <t>Release History — All Products 2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -12869,11 +10617,12 @@
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
       <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>All releases for AG ONE  •  Lead: Geena  •  Team: Geena, Nastaran</t>
+          <t>Every release grouped by product: Released ✅ + Upcoming 📋  •  Scroll down for each team</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -12883,432 +10632,1899 @@
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="28" t="inlineStr">
-        <is>
-          <t>Released: 3  •  Hotfixes: 2  •  Planned: 3  •  Latest: v1.0.2  •  Next: v1.1.0 (May 2026)</t>
-        </is>
-      </c>
-      <c r="B3" s="66" t="n"/>
-      <c r="C3" s="66" t="n"/>
-      <c r="D3" s="66" t="n"/>
-      <c r="E3" s="66" t="n"/>
-      <c r="F3" s="66" t="n"/>
-      <c r="G3" s="66" t="n"/>
-      <c r="H3" s="66" t="n"/>
+      <c r="A3" s="66" t="inlineStr">
+        <is>
+          <t>AG ONE  —  Released: 3  •  Hotfixes: 2  •  Planned: 3  •  Latest: v1.0.2  •  Next: v1.1.0</t>
+        </is>
+      </c>
+      <c r="B3" s="67" t="n"/>
+      <c r="C3" s="67" t="n"/>
+      <c r="D3" s="67" t="n"/>
+      <c r="E3" s="67" t="n"/>
+      <c r="F3" s="67" t="n"/>
+      <c r="G3" s="67" t="n"/>
+      <c r="H3" s="67" t="n"/>
+      <c r="I3" s="67" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="67" t="inlineStr">
-        <is>
-          <t>✅  RELEASED</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="68" t="inlineStr">
+      <c r="A4" s="68" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="68" t="inlineStr">
+      <c r="B4" s="68" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C4" s="68" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="C5" s="68" t="inlineStr">
+      <c r="D4" s="68" t="inlineStr">
         <is>
           <t>Release Name</t>
         </is>
       </c>
-      <c r="D5" s="68" t="inlineStr">
+      <c r="E4" s="68" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E5" s="68" t="inlineStr">
+      <c r="F4" s="68" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="F5" s="68" t="inlineStr">
+      <c r="G4" s="68" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="G5" s="68" t="inlineStr">
+      <c r="H4" s="68" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H5" s="68" t="inlineStr">
+      <c r="I4" s="68" t="inlineStr">
         <is>
           <t>Highlights / What's Included</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>AG ONE</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>AG ONE MVP</t>
+        </is>
+      </c>
+      <c r="E5" s="69" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>29 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>✅ Released</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Full IAM platform: Users, Roles, Tenants, SSO, Permissions, Audit, Assign Access</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="69" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>AG ONE</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>v1.0.1</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>AG ONE Hotfix 1</t>
+        </is>
+      </c>
+      <c r="E6" s="70" t="inlineStr">
+        <is>
+          <t>Hotfix</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>02 Apr 2026</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>✅ Released</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>SSO token refresh loop fix, role sync cache invalidation, tenant switching fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>AG ONE</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>v1.0.2</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>AG ONE Hotfix 2</t>
+        </is>
+      </c>
+      <c r="E7" s="70" t="inlineStr">
+        <is>
+          <t>Hotfix</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>08 Apr 2026</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 7</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>✅ Released</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Audit log pagination, API key duplicate name validation, timezone fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>AG ONE</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>AG ONE Q2 Enhancement</t>
+        </is>
+      </c>
+      <c r="E8" s="71" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 9–10</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>Advanced user analytics, bulk role operations, enhanced audit dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>AG ONE</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>AG ONE Multi-Product Admin</t>
+        </is>
+      </c>
+      <c r="E9" s="71" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 13–14</t>
+        </is>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Multi-product admin console, cross-product role mapping, API marketplace v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>AG ONE</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>v2.0.0</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>AG ONE Enterprise</t>
+        </is>
+      </c>
+      <c r="E10" s="71" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Oct 2026</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 20–22</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Enterprise SSO (SAML+OIDC), advanced RBAC, white-label branding, scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr"/>
+      <c r="B11" s="72" t="inlineStr">
+        <is>
+          <t>AG ONE</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr"/>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>AG ONE</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="14" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr"/>
+      <c r="B13" s="72" t="inlineStr">
+        <is>
+          <t>AG ONE</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="10" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="73" t="inlineStr">
+        <is>
+          <t>OneWork  —  Released: 1  •  Hotfixes: 0  •  Planned: 3  •  Latest: v1.0.0  •  Next: v1.1.0</t>
+        </is>
+      </c>
+      <c r="B15" s="74" t="n"/>
+      <c r="C15" s="74" t="n"/>
+      <c r="D15" s="74" t="n"/>
+      <c r="E15" s="74" t="n"/>
+      <c r="F15" s="74" t="n"/>
+      <c r="G15" s="74" t="n"/>
+      <c r="H15" s="74" t="n"/>
+      <c r="I15" s="74" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="68" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B16" s="68" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C16" s="68" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="D16" s="68" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="E16" s="68" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F16" s="68" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G16" s="68" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="H16" s="68" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I16" s="68" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>OneWork</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>v1.0.0</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>AG ONE MVP</t>
-        </is>
-      </c>
-      <c r="D6" s="70" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>OneWork MVP</t>
+        </is>
+      </c>
+      <c r="E17" s="69" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>29 Mar 2026</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Sprint 6</t>
         </is>
       </c>
-      <c r="G6" s="70" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>✅ Released</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>Full IAM platform: Users, Roles, Tenants, SSO, Permissions, Audit, Assign Access</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="71" t="inlineStr">
-        <is>
-          <t>v1.0.1</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>AG ONE Hotfix 1</t>
-        </is>
-      </c>
-      <c r="D7" s="72" t="inlineStr">
-        <is>
-          <t>Hotfix</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>02 Apr 2026</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="G7" s="70" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Employee mgmt, workflows, task mgmt, dashboards, reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>OneWork</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>OneWork Q2 Enhancement</t>
+        </is>
+      </c>
+      <c r="E18" s="71" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 11–12</t>
+        </is>
+      </c>
+      <c r="H18" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>Advanced workflow templates, email notifications, calendar integration</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>OneWork</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>OneWork Reporting v2</t>
+        </is>
+      </c>
+      <c r="E19" s="71" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 15–16</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Reporting v2 with charts, mobile-responsive, third-party integrations</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>OneWork</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>v2.0.0</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>OneWork Enterprise</t>
+        </is>
+      </c>
+      <c r="E20" s="71" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Nov 2026</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 21–23</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>AI-powered insights, advanced automation, enterprise scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr"/>
+      <c r="B21" s="72" t="inlineStr">
+        <is>
+          <t>OneWork</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr"/>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>OneWork</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+      <c r="G22" s="13" t="n"/>
+      <c r="H22" s="13" t="n"/>
+      <c r="I22" s="14" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr"/>
+      <c r="B23" s="72" t="inlineStr">
+        <is>
+          <t>OneWork</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="10" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="75" t="inlineStr">
+        <is>
+          <t>Learn  —  Released: 1  •  Hotfixes: 0  •  Planned: 3  •  Latest: v1.0.0  •  Next: v1.1.0</t>
+        </is>
+      </c>
+      <c r="B25" s="76" t="n"/>
+      <c r="C25" s="76" t="n"/>
+      <c r="D25" s="76" t="n"/>
+      <c r="E25" s="76" t="n"/>
+      <c r="F25" s="76" t="n"/>
+      <c r="G25" s="76" t="n"/>
+      <c r="H25" s="76" t="n"/>
+      <c r="I25" s="76" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="68" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B26" s="68" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C26" s="68" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="D26" s="68" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="E26" s="68" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F26" s="68" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G26" s="68" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="H26" s="68" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I26" s="68" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Learn</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Learn MVP</t>
+        </is>
+      </c>
+      <c r="E27" s="69" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>29 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>✅ Released</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>SSO token refresh loop fix, role sync cache invalidation, tenant switching fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="69" t="inlineStr">
-        <is>
-          <t>v1.0.2</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>AG ONE Hotfix 2</t>
-        </is>
-      </c>
-      <c r="D8" s="72" t="inlineStr">
-        <is>
-          <t>Hotfix</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>08 Apr 2026</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="G8" s="70" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Courses, learning paths, assessments, certifications, progress tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>Learn</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>Learn Analytics</t>
+        </is>
+      </c>
+      <c r="E28" s="71" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 11–12</t>
+        </is>
+      </c>
+      <c r="H28" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>Advanced analytics dashboard, learner recommendations, completion reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Learn</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Learn Marketplace</t>
+        </is>
+      </c>
+      <c r="E29" s="71" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 15–16</t>
+        </is>
+      </c>
+      <c r="H29" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Content marketplace, SCORM support, mobile-responsive learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Learn</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>v2.0.0</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Learn Enterprise</t>
+        </is>
+      </c>
+      <c r="E30" s="71" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Nov 2026</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 21–23</t>
+        </is>
+      </c>
+      <c r="H30" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>AI recommendations, adaptive learning, full mobile app</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr"/>
+      <c r="B31" s="72" t="inlineStr">
+        <is>
+          <t>Learn</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n"/>
+      <c r="I31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr"/>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Learn</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
+      <c r="G32" s="13" t="n"/>
+      <c r="H32" s="13" t="n"/>
+      <c r="I32" s="14" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr"/>
+      <c r="B33" s="72" t="inlineStr">
+        <is>
+          <t>Learn</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="10" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="77" t="inlineStr">
+        <is>
+          <t>Safe  —  Released: 1  •  Hotfixes: 0  •  Planned: 3  •  Latest: v1.0.0  •  Next: v1.1.0</t>
+        </is>
+      </c>
+      <c r="B35" s="78" t="n"/>
+      <c r="C35" s="78" t="n"/>
+      <c r="D35" s="78" t="n"/>
+      <c r="E35" s="78" t="n"/>
+      <c r="F35" s="78" t="n"/>
+      <c r="G35" s="78" t="n"/>
+      <c r="H35" s="78" t="n"/>
+      <c r="I35" s="78" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="68" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B36" s="68" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C36" s="68" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="D36" s="68" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="E36" s="68" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F36" s="68" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G36" s="68" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="H36" s="68" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I36" s="68" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Safe MVP</t>
+        </is>
+      </c>
+      <c r="E37" s="69" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>29 Mar 2026</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 6</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>✅ Released</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>Audit log pagination, API key duplicate name validation, timezone fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="73" t="inlineStr">
-        <is>
-          <t>📋  UPCOMING / PLANNED</t>
-        </is>
-      </c>
-      <c r="B10" s="60" t="n"/>
-      <c r="C10" s="60" t="n"/>
-      <c r="D10" s="60" t="n"/>
-      <c r="E10" s="60" t="n"/>
-      <c r="F10" s="60" t="n"/>
-      <c r="G10" s="60" t="n"/>
-      <c r="H10" s="60" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="74" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Policies, compliance tracking, audit workflows, risk matrix, dashboards</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>v1.1.0</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>Safe Regulatory Auto</t>
+        </is>
+      </c>
+      <c r="E38" s="71" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 11–12</t>
+        </is>
+      </c>
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>Regulatory update automation, scheduled compliance checks, advanced reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>v1.2.0</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Safe Integrations</t>
+        </is>
+      </c>
+      <c r="E39" s="71" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 17–18</t>
+        </is>
+      </c>
+      <c r="H39" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Third-party GRC integrations, automated alerts, evidence collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>v2.0.0</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Safe Enterprise</t>
+        </is>
+      </c>
+      <c r="E40" s="71" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>Dec 2026</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 24–26</t>
+        </is>
+      </c>
+      <c r="H40" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>Enterprise compliance suite with AI-driven risk predictions</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr"/>
+      <c r="B41" s="72" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="9" t="n"/>
+      <c r="I41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr"/>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="13" t="n"/>
+      <c r="H42" s="13" t="n"/>
+      <c r="I42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr"/>
+      <c r="B43" s="72" t="inlineStr">
+        <is>
+          <t>Safe</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="10" t="n"/>
+    </row>
+    <row r="44"/>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="79" t="inlineStr">
+        <is>
+          <t>OneHire  —  Released: 0  •  Hotfixes: 0  •  Planned: 3  •  Latest: —  •  Next: v0.1.0</t>
+        </is>
+      </c>
+      <c r="B45" s="80" t="n"/>
+      <c r="C45" s="80" t="n"/>
+      <c r="D45" s="80" t="n"/>
+      <c r="E45" s="80" t="n"/>
+      <c r="F45" s="80" t="n"/>
+      <c r="G45" s="80" t="n"/>
+      <c r="H45" s="80" t="n"/>
+      <c r="I45" s="80" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="68" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="74" t="inlineStr">
+      <c r="B46" s="68" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C46" s="68" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="C11" s="74" t="inlineStr">
+      <c r="D46" s="68" t="inlineStr">
         <is>
           <t>Release Name</t>
         </is>
       </c>
-      <c r="D11" s="74" t="inlineStr">
+      <c r="E46" s="68" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E11" s="74" t="inlineStr">
+      <c r="F46" s="68" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="F11" s="74" t="inlineStr">
+      <c r="G46" s="68" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="G11" s="74" t="inlineStr">
+      <c r="H46" s="68" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H11" s="74" t="inlineStr">
+      <c r="I46" s="68" t="inlineStr">
         <is>
           <t>Highlights / What's Included</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="69" t="inlineStr">
-        <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>AG ONE Q2 Enhancement</t>
-        </is>
-      </c>
-      <c r="D12" s="75" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>OneHire</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>v0.1.0</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>OneHire Alpha</t>
+        </is>
+      </c>
+      <c r="E47" s="81" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr">
         <is>
           <t>Sprint 9–10</t>
         </is>
       </c>
-      <c r="G12" s="76" t="inlineStr">
+      <c r="H47" s="18" t="inlineStr">
         <is>
           <t>📋 Planned</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>Advanced user analytics, bulk role operations, enhanced audit dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="71" t="inlineStr">
-        <is>
-          <t>v1.2.0</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>AG ONE Multi-Product Admin</t>
-        </is>
-      </c>
-      <c r="D13" s="75" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Core job posting and applicant tracking features</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>OneHire</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>v0.5.0</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>OneHire Beta</t>
+        </is>
+      </c>
+      <c r="E48" s="81" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 11–12</t>
+        </is>
+      </c>
+      <c r="H48" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>Interview scheduling, candidate pipeline, basic reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>OneHire</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>OneHire MVP</t>
+        </is>
+      </c>
+      <c r="E49" s="69" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
         <is>
           <t>Jul 2026</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="G49" s="9" t="inlineStr">
         <is>
           <t>Sprint 13–14</t>
         </is>
       </c>
-      <c r="G13" s="76" t="inlineStr">
+      <c r="H49" s="18" t="inlineStr">
         <is>
           <t>📋 Planned</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>Multi-product admin console, cross-product role mapping, API marketplace v1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B14" s="69" t="inlineStr">
-        <is>
-          <t>v2.0.0</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>AG ONE Enterprise</t>
-        </is>
-      </c>
-      <c r="D14" s="75" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>Oct 2026</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 20–22</t>
-        </is>
-      </c>
-      <c r="G14" s="76" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Full recruitment portal with applicant tracking and analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr"/>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>OneHire</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="n"/>
+      <c r="D50" s="14" t="n"/>
+      <c r="E50" s="13" t="n"/>
+      <c r="F50" s="13" t="n"/>
+      <c r="G50" s="13" t="n"/>
+      <c r="H50" s="13" t="n"/>
+      <c r="I50" s="14" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr"/>
+      <c r="B51" s="72" t="inlineStr">
+        <is>
+          <t>OneHire</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="9" t="n"/>
+      <c r="I51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr"/>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>OneHire</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="n"/>
+      <c r="D52" s="14" t="n"/>
+      <c r="E52" s="13" t="n"/>
+      <c r="F52" s="13" t="n"/>
+      <c r="G52" s="13" t="n"/>
+      <c r="H52" s="13" t="n"/>
+      <c r="I52" s="14" t="n"/>
+    </row>
+    <row r="53"/>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="82" t="inlineStr">
+        <is>
+          <t>Spot  —  Released: 0  •  Hotfixes: 0  •  Planned: 2  •  Latest: —  •  Next: v0.1.0</t>
+        </is>
+      </c>
+      <c r="B54" s="83" t="n"/>
+      <c r="C54" s="83" t="n"/>
+      <c r="D54" s="83" t="n"/>
+      <c r="E54" s="83" t="n"/>
+      <c r="F54" s="83" t="n"/>
+      <c r="G54" s="83" t="n"/>
+      <c r="H54" s="83" t="n"/>
+      <c r="I54" s="83" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="68" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B55" s="68" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C55" s="68" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="D55" s="68" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="E55" s="68" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F55" s="68" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G55" s="68" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="H55" s="68" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I55" s="68" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>v0.1.0</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>Spot Alpha</t>
+        </is>
+      </c>
+      <c r="E56" s="81" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="F56" s="13" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="G56" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 9–10</t>
+        </is>
+      </c>
+      <c r="H56" s="18" t="inlineStr">
         <is>
           <t>📋 Planned</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>Enterprise SSO (SAML+OIDC), advanced RBAC, white-label branding, scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr"/>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="14" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr"/>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="14" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr"/>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="10" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr"/>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="13" t="n"/>
-      <c r="H20" s="14" t="n"/>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>Core city module, location management</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>Spot MVP</t>
+        </is>
+      </c>
+      <c r="E57" s="69" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 17–18</t>
+        </is>
+      </c>
+      <c r="H57" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>City management, geolocation features, admin dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr"/>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="n"/>
+      <c r="D58" s="14" t="n"/>
+      <c r="E58" s="13" t="n"/>
+      <c r="F58" s="13" t="n"/>
+      <c r="G58" s="13" t="n"/>
+      <c r="H58" s="13" t="n"/>
+      <c r="I58" s="14" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr"/>
+      <c r="B59" s="72" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="9" t="n"/>
+      <c r="G59" s="9" t="n"/>
+      <c r="H59" s="9" t="n"/>
+      <c r="I59" s="10" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr"/>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="n"/>
+      <c r="D60" s="14" t="n"/>
+      <c r="E60" s="13" t="n"/>
+      <c r="F60" s="13" t="n"/>
+      <c r="G60" s="13" t="n"/>
+      <c r="H60" s="13" t="n"/>
+      <c r="I60" s="14" t="n"/>
+    </row>
+    <row r="61"/>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="84" t="inlineStr">
+        <is>
+          <t>Pulse  —  Released: 0  •  Hotfixes: 0  •  Planned: 2  •  Latest: —  •  Next: v0.1.0</t>
+        </is>
+      </c>
+      <c r="B62" s="85" t="n"/>
+      <c r="C62" s="85" t="n"/>
+      <c r="D62" s="85" t="n"/>
+      <c r="E62" s="85" t="n"/>
+      <c r="F62" s="85" t="n"/>
+      <c r="G62" s="85" t="n"/>
+      <c r="H62" s="85" t="n"/>
+      <c r="I62" s="85" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="68" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B63" s="68" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C63" s="68" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="D63" s="68" t="inlineStr">
+        <is>
+          <t>Release Name</t>
+        </is>
+      </c>
+      <c r="E63" s="68" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F63" s="68" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G63" s="68" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="H63" s="68" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I63" s="68" t="inlineStr">
+        <is>
+          <t>Highlights / What's Included</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="13" t="n">
+        <v>42</v>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>Pulse</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>v0.1.0</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>Pulse Alpha</t>
+        </is>
+      </c>
+      <c r="E64" s="81" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="F64" s="13" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="G64" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 9–10</t>
+        </is>
+      </c>
+      <c r="H64" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>Survey builder, basic distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>Pulse</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>v1.0.0</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Pulse MVP</t>
+        </is>
+      </c>
+      <c r="E65" s="69" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 17–18</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="inlineStr">
+        <is>
+          <t>📋 Planned</t>
+        </is>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>Survey analytics, employee engagement dashboards, benchmarking</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr"/>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>Pulse</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="n"/>
+      <c r="D66" s="14" t="n"/>
+      <c r="E66" s="13" t="n"/>
+      <c r="F66" s="13" t="n"/>
+      <c r="G66" s="13" t="n"/>
+      <c r="H66" s="13" t="n"/>
+      <c r="I66" s="14" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr"/>
+      <c r="B67" s="72" t="inlineStr">
+        <is>
+          <t>Pulse</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="n"/>
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="9" t="n"/>
+      <c r="F67" s="9" t="n"/>
+      <c r="G67" s="9" t="n"/>
+      <c r="H67" s="9" t="n"/>
+      <c r="I67" s="10" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr"/>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>Pulse</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="n"/>
+      <c r="D68" s="14" t="n"/>
+      <c r="E68" s="13" t="n"/>
+      <c r="F68" s="13" t="n"/>
+      <c r="G68" s="13" t="n"/>
+      <c r="H68" s="13" t="n"/>
+      <c r="I68" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="9">
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/AG_ONE_Team_Tracker_2026.xlsx
+++ b/AG_ONE_Team_Tracker_2026.xlsx
@@ -14,10 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Member Performance" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026 Targets" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="External Projects" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Dashboard" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release History" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Standard" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Use" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How To Use" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="29">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -138,50 +135,14 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="000369A1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="00065F46"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="00991B1B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="00991B1B"/>
+      <color rgb="001E3A5F"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="001E3A5F"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="005B21B6"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="001E3A5F"/>
-      <sz val="12"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -202,7 +163,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -305,26 +266,8 @@
         <bgColor rgb="00EDE9FE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000EA5E9"/>
-        <bgColor rgb="000EA5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E0F2FE"/>
-        <bgColor rgb="00E0F2FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00475569"/>
-        <bgColor rgb="00475569"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -368,17 +311,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00E2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E2E8F0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="00E2E8F0"/>
       </right>
@@ -394,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -547,124 +479,16 @@
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1379,761 +1203,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000369A1"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Release Naming Standard &amp; Versioning Policy</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Share this with all teams so everyone follows the same release naming and numbering</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="86" t="inlineStr">
-        <is>
-          <t>Versioning Format</t>
-        </is>
-      </c>
-      <c r="B3" s="87" t="n"/>
-      <c r="C3" s="87" t="n"/>
-      <c r="D3" s="88" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="49" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="B4" s="89" t="inlineStr">
-        <is>
-          <t>vMAJOR.MINOR.PATCH</t>
-        </is>
-      </c>
-      <c r="C4" s="90" t="n"/>
-      <c r="D4" s="91" t="inlineStr">
-        <is>
-          <t>Example: v1.2.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="49" t="inlineStr">
-        <is>
-          <t>MAJOR</t>
-        </is>
-      </c>
-      <c r="B5" s="89" t="inlineStr">
-        <is>
-          <t>Breaking changes or major new feature sets</t>
-        </is>
-      </c>
-      <c r="C5" s="90" t="n"/>
-      <c r="D5" s="91" t="inlineStr">
-        <is>
-          <t>v1.0.0 → v2.0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="49" t="inlineStr">
-        <is>
-          <t>MINOR</t>
-        </is>
-      </c>
-      <c r="B6" s="89" t="inlineStr">
-        <is>
-          <t>New features, enhancements (backward compatible)</t>
-        </is>
-      </c>
-      <c r="C6" s="90" t="n"/>
-      <c r="D6" s="91" t="inlineStr">
-        <is>
-          <t>v1.0.0 → v1.1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="49" t="inlineStr">
-        <is>
-          <t>PATCH</t>
-        </is>
-      </c>
-      <c r="B7" s="89" t="inlineStr">
-        <is>
-          <t>Bug fixes, hotfixes, minor corrections</t>
-        </is>
-      </c>
-      <c r="C7" s="90" t="n"/>
-      <c r="D7" s="91" t="inlineStr">
-        <is>
-          <t>v1.0.0 → v1.0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="58" t="inlineStr">
-        <is>
-          <t>Release Type</t>
-        </is>
-      </c>
-      <c r="B9" s="58" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C9" s="58" t="inlineStr">
-        <is>
-          <t>Frequency</t>
-        </is>
-      </c>
-      <c r="D9" s="58" t="inlineStr">
-        <is>
-          <t>Approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="92" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="B10" s="50" t="inlineStr">
-        <is>
-          <t>First production release of a product</t>
-        </is>
-      </c>
-      <c r="C10" s="50" t="inlineStr">
-        <is>
-          <t>Once per product</t>
-        </is>
-      </c>
-      <c r="D10" s="50" t="inlineStr">
-        <is>
-          <t>Director + Tech Lead</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="93" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="B11" s="50" t="inlineStr">
-        <is>
-          <t>Significant new features or breaking changes</t>
-        </is>
-      </c>
-      <c r="C11" s="50" t="inlineStr">
-        <is>
-          <t>1–2 per year</t>
-        </is>
-      </c>
-      <c r="D11" s="50" t="inlineStr">
-        <is>
-          <t>Director + Tech Lead</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="94" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="B12" s="50" t="inlineStr">
-        <is>
-          <t>New features &amp; enhancements, backward compatible</t>
-        </is>
-      </c>
-      <c r="C12" s="50" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D12" s="50" t="inlineStr">
-        <is>
-          <t>Tech Lead</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="95" t="inlineStr">
-        <is>
-          <t>Hotfix</t>
-        </is>
-      </c>
-      <c r="B13" s="50" t="inlineStr">
-        <is>
-          <t>Critical production fix, expedited deployment</t>
-        </is>
-      </c>
-      <c r="C13" s="50" t="inlineStr">
-        <is>
-          <t>As needed (urgent)</t>
-        </is>
-      </c>
-      <c r="D13" s="50" t="inlineStr">
-        <is>
-          <t>Tech Lead + post-mortem</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="96" t="inlineStr">
-        <is>
-          <t>Patch</t>
-        </is>
-      </c>
-      <c r="B14" s="50" t="inlineStr">
-        <is>
-          <t>Non-critical bug fixes, scheduled deployment</t>
-        </is>
-      </c>
-      <c r="C14" s="50" t="inlineStr">
-        <is>
-          <t>As needed</t>
-        </is>
-      </c>
-      <c r="D14" s="50" t="inlineStr">
-        <is>
-          <t>Tech Lead</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="97" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="B15" s="50" t="inlineStr">
-        <is>
-          <t>Sprint-based release (pre-MVP iterations)</t>
-        </is>
-      </c>
-      <c r="C15" s="50" t="inlineStr">
-        <is>
-          <t>Every 2 weeks</t>
-        </is>
-      </c>
-      <c r="D15" s="50" t="inlineStr">
-        <is>
-          <t>Tech Lead</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="86" t="inlineStr">
-        <is>
-          <t>Release Naming Convention</t>
-        </is>
-      </c>
-      <c r="B17" s="87" t="n"/>
-      <c r="C17" s="87" t="n"/>
-      <c r="D17" s="88" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="98" t="inlineStr">
-        <is>
-          <t>Pattern</t>
-        </is>
-      </c>
-      <c r="B18" s="99" t="inlineStr">
-        <is>
-          <t>[Product] [Type] — [Short Description]</t>
-        </is>
-      </c>
-      <c r="C18" s="100" t="inlineStr">
-        <is>
-          <t>Used in Release Name column</t>
-        </is>
-      </c>
-      <c r="D18" s="101" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="98" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="B19" s="99" t="inlineStr">
-        <is>
-          <t>AG ONE MVP</t>
-        </is>
-      </c>
-      <c r="C19" s="100" t="inlineStr">
-        <is>
-          <t>First production release</t>
-        </is>
-      </c>
-      <c r="D19" s="101" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="98" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="B20" s="99" t="inlineStr">
-        <is>
-          <t>AG ONE Q2 Enhancement</t>
-        </is>
-      </c>
-      <c r="C20" s="100" t="inlineStr">
-        <is>
-          <t>Quarterly feature release</t>
-        </is>
-      </c>
-      <c r="D20" s="101" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="98" t="inlineStr">
-        <is>
-          <t>Hotfix</t>
-        </is>
-      </c>
-      <c r="B21" s="99" t="inlineStr">
-        <is>
-          <t>AG ONE Hotfix 1</t>
-        </is>
-      </c>
-      <c r="C21" s="100" t="inlineStr">
-        <is>
-          <t>Numbered sequentially</t>
-        </is>
-      </c>
-      <c r="D21" s="101" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="98" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="B22" s="99" t="inlineStr">
-        <is>
-          <t>AG ONE Enterprise</t>
-        </is>
-      </c>
-      <c r="C22" s="100" t="inlineStr">
-        <is>
-          <t>Named for the theme</t>
-        </is>
-      </c>
-      <c r="D22" s="101" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="98" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="B23" s="99" t="inlineStr">
-        <is>
-          <t>OneHire Alpha / OneHire Beta</t>
-        </is>
-      </c>
-      <c r="C23" s="100" t="inlineStr">
-        <is>
-          <t>Pre-MVP iterations</t>
-        </is>
-      </c>
-      <c r="D23" s="101" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="B4:C4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="006B7280"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>How To Use This Tracker</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Quick guide for all stakeholders</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="86" t="inlineStr">
-        <is>
-          <t>Sheet</t>
-        </is>
-      </c>
-      <c r="B3" s="86" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="C3" s="86" t="inlineStr">
-        <is>
-          <t>Update Frequency</t>
-        </is>
-      </c>
-      <c r="D3" s="86" t="inlineStr">
-        <is>
-          <t>Who Updates</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Team Overview</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>See all 7 internal teams, current sprint, status at a glance</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Every sprint</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Engineering Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Resource Allocation</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>Internal + external assignments per member, shared &amp; outsource flags</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>When team changes</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>Engineering Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Project Roadmap</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>Track project start/end, achievements, next targets, alignment</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Every sprint</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Tech Leads</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Sprint Tracker</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Detailed sprint goals, outcomes, tech lead feedback, blockers</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Every sprint</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Tech Leads</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Member Performance</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>Individual progress, ratings, achievements</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>Every sprint</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>Tech Leads</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>2026 Targets</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Quarterly milestones and year-end goals per team</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Quarterly</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Engineering Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>External Projects</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Track resources on external / outsource / partner projects</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>When assignments change</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Engineering Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Release Dashboard</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>At-a-glance: latest release, totals, and next planned per product</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Every release</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Engineering Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Release History</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>All releases grouped by product — released + upcoming with highlights</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Every release</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>Tech Leads</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Release Standard</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Versioning policy, naming convention, release types — share with all teams</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Reference only</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="102" t="inlineStr">
-        <is>
-          <t>STATUS LEGEND</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ●  ✅ Completed</t>
-        </is>
-      </c>
-      <c r="B16" s="88" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ●  ▶ In Progress / On Track</t>
-        </is>
-      </c>
-      <c r="B17" s="88" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ●  At Risk</t>
-        </is>
-      </c>
-      <c r="B18" s="88" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ●  Blocked</t>
-        </is>
-      </c>
-      <c r="B19" s="88" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ●  Not Started</t>
-        </is>
-      </c>
-      <c r="B20" s="88" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -10135,2396 +9204,272 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000EA5E9"/>
+    <tabColor rgb="006B7280"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Release Dashboard — All Products 2026</t>
+          <t>How To Use This Tracker</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>At-a-glance: latest release, total count, and next planned for every product</t>
+          <t>Quick guide for all stakeholders</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="58" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Sheet</t>
         </is>
       </c>
       <c r="B3" s="58" t="inlineStr">
         <is>
-          <t>Latest Version</t>
+          <t>Purpose</t>
         </is>
       </c>
       <c r="C3" s="58" t="inlineStr">
         <is>
-          <t>Latest Release</t>
+          <t>Update Frequency</t>
         </is>
       </c>
       <c r="D3" s="58" t="inlineStr">
         <is>
-          <t>Release Date</t>
-        </is>
-      </c>
-      <c r="E3" s="58" t="inlineStr">
-        <is>
-          <t>Total Releases</t>
-        </is>
-      </c>
-      <c r="F3" s="58" t="inlineStr">
-        <is>
-          <t>Hotfixes</t>
-        </is>
-      </c>
-      <c r="G3" s="58" t="inlineStr">
-        <is>
-          <t>Next Planned</t>
-        </is>
-      </c>
-      <c r="H3" s="58" t="inlineStr">
-        <is>
-          <t>Next Version</t>
-        </is>
-      </c>
-      <c r="I3" s="58" t="inlineStr">
-        <is>
-          <t>Target Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="59" t="inlineStr">
-        <is>
-          <t>📏  Versioning Standard: vMAJOR.MINOR.PATCH  •  Types: MVP | Major | Minor | Hotfix | Patch | Sprint  •  Quarterly releases + hotfixes as needed</t>
-        </is>
-      </c>
-      <c r="B4" s="60" t="n"/>
-      <c r="C4" s="60" t="n"/>
-      <c r="D4" s="60" t="n"/>
-      <c r="E4" s="60" t="n"/>
-      <c r="F4" s="60" t="n"/>
-      <c r="G4" s="60" t="n"/>
-      <c r="H4" s="60" t="n"/>
-      <c r="I4" s="60" t="n"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="49" t="inlineStr">
-        <is>
-          <t>AG ONE</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>v1.0.2</t>
+          <t>Who Updates</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Team Overview</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>See all 7 internal teams, current sprint, status at a glance</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Every sprint</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Engineering Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Resource Allocation</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Internal + external assignments per member, shared &amp; outsource flags</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>AG ONE Hotfix 2</t>
+          <t>When team changes</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>08 Apr 2026</t>
-        </is>
-      </c>
-      <c r="E5" s="61" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="62" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>AG ONE Q2 Enhancement</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="51" t="inlineStr">
-        <is>
-          <t>OneWork</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
+          <t>Engineering Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Project Roadmap</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Track project start/end, achievements, next targets, alignment</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>OneWork MVP</t>
+          <t>Every sprint</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>29 Mar 2026</t>
-        </is>
-      </c>
-      <c r="E6" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>OneWork Q2 Enhancement</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="52" t="inlineStr">
-        <is>
-          <t>Learn</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
+          <t>Tech Leads</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Sprint Tracker</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Detailed sprint goals, outcomes, tech lead feedback, blockers</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Learn MVP</t>
+          <t>Every sprint</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>29 Mar 2026</t>
-        </is>
-      </c>
-      <c r="E7" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>Learn Analytics</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="53" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
+          <t>Tech Leads</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Member Performance</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Individual progress, ratings, achievements</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Safe MVP</t>
+          <t>Every sprint</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>29 Mar 2026</t>
-        </is>
-      </c>
-      <c r="E8" s="61" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>Safe Regulatory Auto</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="54" t="inlineStr">
-        <is>
-          <t>OneHire</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Tech Leads</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>2026 Targets</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Quarterly milestones and year-end goals per team</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Quarterly</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>OneHire Alpha</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>v0.1.0</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="55" t="inlineStr">
-        <is>
-          <t>Spot</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Engineering Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>External Projects</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Track resources on external / outsource / partner projects</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>When assignments change</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>Spot Alpha</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>v0.1.0</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="56" t="inlineStr">
-        <is>
-          <t>Pulse</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>Pulse Alpha</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>v0.1.0</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>Engineering Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="59" t="inlineStr">
+        <is>
+          <t>STATUS LEGEND</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>TOTAL ACROSS ALL PRODUCTS</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" s="63" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" s="64" t="inlineStr">
-        <is>
-          <t>19 releases planned</t>
-        </is>
-      </c>
-      <c r="H13" s="65" t="n"/>
-      <c r="I13" s="65" t="n"/>
+      <c r="A13" s="60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ●  ✅ Completed</t>
+        </is>
+      </c>
+      <c r="B13" s="61" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ●  ▶ In Progress / On Track</t>
+        </is>
+      </c>
+      <c r="B14" s="61" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ●  At Risk</t>
+        </is>
+      </c>
+      <c r="B15" s="61" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ●  Blocked</t>
+        </is>
+      </c>
+      <c r="B16" s="61" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ●  Not Started</t>
+        </is>
+      </c>
+      <c r="B17" s="61" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A13:D13"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000284C7"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Release History — All Products 2026</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Every release grouped by product: Released ✅ + Upcoming 📋  •  Scroll down for each team</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="66" t="inlineStr">
-        <is>
-          <t>AG ONE  —  Released: 3  •  Hotfixes: 2  •  Planned: 3  •  Latest: v1.0.2  •  Next: v1.1.0</t>
-        </is>
-      </c>
-      <c r="B3" s="67" t="n"/>
-      <c r="C3" s="67" t="n"/>
-      <c r="D3" s="67" t="n"/>
-      <c r="E3" s="67" t="n"/>
-      <c r="F3" s="67" t="n"/>
-      <c r="G3" s="67" t="n"/>
-      <c r="H3" s="67" t="n"/>
-      <c r="I3" s="67" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="68" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="68" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="C4" s="68" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="D4" s="68" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="E4" s="68" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="F4" s="68" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="G4" s="68" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="H4" s="68" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I4" s="68" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>AG ONE</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>AG ONE MVP</t>
-        </is>
-      </c>
-      <c r="E5" s="69" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>29 Mar 2026</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>✅ Released</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>Full IAM platform: Users, Roles, Tenants, SSO, Permissions, Audit, Assign Access</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>AG ONE</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>v1.0.1</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>AG ONE Hotfix 1</t>
-        </is>
-      </c>
-      <c r="E6" s="70" t="inlineStr">
-        <is>
-          <t>Hotfix</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>02 Apr 2026</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>✅ Released</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
-        <is>
-          <t>SSO token refresh loop fix, role sync cache invalidation, tenant switching fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>AG ONE</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>v1.0.2</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>AG ONE Hotfix 2</t>
-        </is>
-      </c>
-      <c r="E7" s="70" t="inlineStr">
-        <is>
-          <t>Hotfix</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>08 Apr 2026</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 7</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>✅ Released</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>Audit log pagination, API key duplicate name validation, timezone fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>AG ONE</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>AG ONE Q2 Enhancement</t>
-        </is>
-      </c>
-      <c r="E8" s="71" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 9–10</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>Advanced user analytics, bulk role operations, enhanced audit dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>AG ONE</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>v1.2.0</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>AG ONE Multi-Product Admin</t>
-        </is>
-      </c>
-      <c r="E9" s="71" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 13–14</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>Multi-product admin console, cross-product role mapping, API marketplace v1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>AG ONE</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>v2.0.0</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>AG ONE Enterprise</t>
-        </is>
-      </c>
-      <c r="E10" s="71" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Oct 2026</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 20–22</t>
-        </is>
-      </c>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>Enterprise SSO (SAML+OIDC), advanced RBAC, white-label branding, scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr"/>
-      <c r="B11" s="72" t="inlineStr">
-        <is>
-          <t>AG ONE</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="10" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr"/>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>AG ONE</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="13" t="n"/>
-      <c r="H12" s="13" t="n"/>
-      <c r="I12" s="14" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr"/>
-      <c r="B13" s="72" t="inlineStr">
-        <is>
-          <t>AG ONE</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n"/>
-      <c r="I13" s="10" t="n"/>
-    </row>
-    <row r="14"/>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="73" t="inlineStr">
-        <is>
-          <t>OneWork  —  Released: 1  •  Hotfixes: 0  •  Planned: 3  •  Latest: v1.0.0  •  Next: v1.1.0</t>
-        </is>
-      </c>
-      <c r="B15" s="74" t="n"/>
-      <c r="C15" s="74" t="n"/>
-      <c r="D15" s="74" t="n"/>
-      <c r="E15" s="74" t="n"/>
-      <c r="F15" s="74" t="n"/>
-      <c r="G15" s="74" t="n"/>
-      <c r="H15" s="74" t="n"/>
-      <c r="I15" s="74" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="68" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B16" s="68" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="C16" s="68" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="D16" s="68" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="E16" s="68" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="F16" s="68" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="G16" s="68" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="H16" s="68" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I16" s="68" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>OneWork</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>OneWork MVP</t>
-        </is>
-      </c>
-      <c r="E17" s="69" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>29 Mar 2026</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>✅ Released</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>Employee mgmt, workflows, task mgmt, dashboards, reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>OneWork</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>OneWork Q2 Enhancement</t>
-        </is>
-      </c>
-      <c r="E18" s="71" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 11–12</t>
-        </is>
-      </c>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I18" s="14" t="inlineStr">
-        <is>
-          <t>Advanced workflow templates, email notifications, calendar integration</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>OneWork</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>v1.2.0</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>OneWork Reporting v2</t>
-        </is>
-      </c>
-      <c r="E19" s="71" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>Aug 2026</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 15–16</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>Reporting v2 with charts, mobile-responsive, third-party integrations</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>OneWork</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>v2.0.0</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>OneWork Enterprise</t>
-        </is>
-      </c>
-      <c r="E20" s="71" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="G20" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 21–23</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>AI-powered insights, advanced automation, enterprise scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr"/>
-      <c r="B21" s="72" t="inlineStr">
-        <is>
-          <t>OneWork</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="10" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr"/>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>OneWork</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="14" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="14" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr"/>
-      <c r="B23" s="72" t="inlineStr">
-        <is>
-          <t>OneWork</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="10" t="n"/>
-    </row>
-    <row r="24"/>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="75" t="inlineStr">
-        <is>
-          <t>Learn  —  Released: 1  •  Hotfixes: 0  •  Planned: 3  •  Latest: v1.0.0  •  Next: v1.1.0</t>
-        </is>
-      </c>
-      <c r="B25" s="76" t="n"/>
-      <c r="C25" s="76" t="n"/>
-      <c r="D25" s="76" t="n"/>
-      <c r="E25" s="76" t="n"/>
-      <c r="F25" s="76" t="n"/>
-      <c r="G25" s="76" t="n"/>
-      <c r="H25" s="76" t="n"/>
-      <c r="I25" s="76" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="68" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B26" s="68" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="C26" s="68" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="D26" s="68" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="E26" s="68" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="F26" s="68" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="G26" s="68" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="H26" s="68" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I26" s="68" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Learn</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>Learn MVP</t>
-        </is>
-      </c>
-      <c r="E27" s="69" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>29 Mar 2026</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="H27" s="11" t="inlineStr">
-        <is>
-          <t>✅ Released</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>Courses, learning paths, assessments, certifications, progress tracking</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>Learn</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Learn Analytics</t>
-        </is>
-      </c>
-      <c r="E28" s="71" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 11–12</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>Advanced analytics dashboard, learner recommendations, completion reports</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Learn</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>v1.2.0</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>Learn Marketplace</t>
-        </is>
-      </c>
-      <c r="E29" s="71" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Aug 2026</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 15–16</t>
-        </is>
-      </c>
-      <c r="H29" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>Content marketplace, SCORM support, mobile-responsive learning</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>Learn</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>v2.0.0</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>Learn Enterprise</t>
-        </is>
-      </c>
-      <c r="E30" s="71" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="inlineStr">
-        <is>
-          <t>Nov 2026</t>
-        </is>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 21–23</t>
-        </is>
-      </c>
-      <c r="H30" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I30" s="14" t="inlineStr">
-        <is>
-          <t>AI recommendations, adaptive learning, full mobile app</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr"/>
-      <c r="B31" s="72" t="inlineStr">
-        <is>
-          <t>Learn</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="10" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr"/>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>Learn</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="13" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="14" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr"/>
-      <c r="B33" s="72" t="inlineStr">
-        <is>
-          <t>Learn</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="10" t="n"/>
-    </row>
-    <row r="34"/>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="77" t="inlineStr">
-        <is>
-          <t>Safe  —  Released: 1  •  Hotfixes: 0  •  Planned: 3  •  Latest: v1.0.0  •  Next: v1.1.0</t>
-        </is>
-      </c>
-      <c r="B35" s="78" t="n"/>
-      <c r="C35" s="78" t="n"/>
-      <c r="D35" s="78" t="n"/>
-      <c r="E35" s="78" t="n"/>
-      <c r="F35" s="78" t="n"/>
-      <c r="G35" s="78" t="n"/>
-      <c r="H35" s="78" t="n"/>
-      <c r="I35" s="78" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="68" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B36" s="68" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="C36" s="68" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="D36" s="68" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="E36" s="68" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="F36" s="68" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="G36" s="68" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="H36" s="68" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I36" s="68" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="inlineStr">
-        <is>
-          <t>Safe MVP</t>
-        </is>
-      </c>
-      <c r="E37" s="69" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>29 Mar 2026</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="H37" s="11" t="inlineStr">
-        <is>
-          <t>✅ Released</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
-        <is>
-          <t>Policies, compliance tracking, audit workflows, risk matrix, dashboards</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
-        <is>
-          <t>v1.1.0</t>
-        </is>
-      </c>
-      <c r="D38" s="14" t="inlineStr">
-        <is>
-          <t>Safe Regulatory Auto</t>
-        </is>
-      </c>
-      <c r="E38" s="71" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="G38" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 11–12</t>
-        </is>
-      </c>
-      <c r="H38" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
-        <is>
-          <t>Regulatory update automation, scheduled compliance checks, advanced reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>v1.2.0</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>Safe Integrations</t>
-        </is>
-      </c>
-      <c r="E39" s="71" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 17–18</t>
-        </is>
-      </c>
-      <c r="H39" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
-        <is>
-          <t>Third-party GRC integrations, automated alerts, evidence collection</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="13" t="n">
-        <v>27</v>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="C40" s="13" t="inlineStr">
-        <is>
-          <t>v2.0.0</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="inlineStr">
-        <is>
-          <t>Safe Enterprise</t>
-        </is>
-      </c>
-      <c r="E40" s="71" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="F40" s="13" t="inlineStr">
-        <is>
-          <t>Dec 2026</t>
-        </is>
-      </c>
-      <c r="G40" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 24–26</t>
-        </is>
-      </c>
-      <c r="H40" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
-        <is>
-          <t>Enterprise compliance suite with AI-driven risk predictions</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr"/>
-      <c r="B41" s="72" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="9" t="n"/>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="9" t="n"/>
-      <c r="I41" s="10" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="13" t="inlineStr"/>
-      <c r="B42" s="18" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="14" t="n"/>
-      <c r="E42" s="13" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="13" t="n"/>
-      <c r="H42" s="13" t="n"/>
-      <c r="I42" s="14" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr"/>
-      <c r="B43" s="72" t="inlineStr">
-        <is>
-          <t>Safe</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="9" t="n"/>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="9" t="n"/>
-      <c r="H43" s="9" t="n"/>
-      <c r="I43" s="10" t="n"/>
-    </row>
-    <row r="44"/>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="79" t="inlineStr">
-        <is>
-          <t>OneHire  —  Released: 0  •  Hotfixes: 0  •  Planned: 3  •  Latest: —  •  Next: v0.1.0</t>
-        </is>
-      </c>
-      <c r="B45" s="80" t="n"/>
-      <c r="C45" s="80" t="n"/>
-      <c r="D45" s="80" t="n"/>
-      <c r="E45" s="80" t="n"/>
-      <c r="F45" s="80" t="n"/>
-      <c r="G45" s="80" t="n"/>
-      <c r="H45" s="80" t="n"/>
-      <c r="I45" s="80" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="68" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B46" s="68" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="C46" s="68" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="D46" s="68" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="E46" s="68" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="F46" s="68" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="G46" s="68" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="H46" s="68" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I46" s="68" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>OneHire</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>v0.1.0</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>OneHire Alpha</t>
-        </is>
-      </c>
-      <c r="E47" s="81" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="G47" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 9–10</t>
-        </is>
-      </c>
-      <c r="H47" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>Core job posting and applicant tracking features</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="13" t="n">
-        <v>32</v>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>OneHire</t>
-        </is>
-      </c>
-      <c r="C48" s="13" t="inlineStr">
-        <is>
-          <t>v0.5.0</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr">
-        <is>
-          <t>OneHire Beta</t>
-        </is>
-      </c>
-      <c r="E48" s="81" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="F48" s="13" t="inlineStr">
-        <is>
-          <t>Jun 2026</t>
-        </is>
-      </c>
-      <c r="G48" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 11–12</t>
-        </is>
-      </c>
-      <c r="H48" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I48" s="14" t="inlineStr">
-        <is>
-          <t>Interview scheduling, candidate pipeline, basic reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>OneHire</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="D49" s="10" t="inlineStr">
-        <is>
-          <t>OneHire MVP</t>
-        </is>
-      </c>
-      <c r="E49" s="69" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>Jul 2026</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 13–14</t>
-        </is>
-      </c>
-      <c r="H49" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I49" s="10" t="inlineStr">
-        <is>
-          <t>Full recruitment portal with applicant tracking and analytics</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr"/>
-      <c r="B50" s="18" t="inlineStr">
-        <is>
-          <t>OneHire</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="n"/>
-      <c r="D50" s="14" t="n"/>
-      <c r="E50" s="13" t="n"/>
-      <c r="F50" s="13" t="n"/>
-      <c r="G50" s="13" t="n"/>
-      <c r="H50" s="13" t="n"/>
-      <c r="I50" s="14" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr"/>
-      <c r="B51" s="72" t="inlineStr">
-        <is>
-          <t>OneHire</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="n"/>
-      <c r="D51" s="10" t="n"/>
-      <c r="E51" s="9" t="n"/>
-      <c r="F51" s="9" t="n"/>
-      <c r="G51" s="9" t="n"/>
-      <c r="H51" s="9" t="n"/>
-      <c r="I51" s="10" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="13" t="inlineStr"/>
-      <c r="B52" s="18" t="inlineStr">
-        <is>
-          <t>OneHire</t>
-        </is>
-      </c>
-      <c r="C52" s="13" t="n"/>
-      <c r="D52" s="14" t="n"/>
-      <c r="E52" s="13" t="n"/>
-      <c r="F52" s="13" t="n"/>
-      <c r="G52" s="13" t="n"/>
-      <c r="H52" s="13" t="n"/>
-      <c r="I52" s="14" t="n"/>
-    </row>
-    <row r="53"/>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="82" t="inlineStr">
-        <is>
-          <t>Spot  —  Released: 0  •  Hotfixes: 0  •  Planned: 2  •  Latest: —  •  Next: v0.1.0</t>
-        </is>
-      </c>
-      <c r="B54" s="83" t="n"/>
-      <c r="C54" s="83" t="n"/>
-      <c r="D54" s="83" t="n"/>
-      <c r="E54" s="83" t="n"/>
-      <c r="F54" s="83" t="n"/>
-      <c r="G54" s="83" t="n"/>
-      <c r="H54" s="83" t="n"/>
-      <c r="I54" s="83" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="68" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B55" s="68" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="C55" s="68" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="D55" s="68" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="E55" s="68" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="F55" s="68" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="G55" s="68" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="H55" s="68" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I55" s="68" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="13" t="n">
-        <v>37</v>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>Spot</t>
-        </is>
-      </c>
-      <c r="C56" s="13" t="inlineStr">
-        <is>
-          <t>v0.1.0</t>
-        </is>
-      </c>
-      <c r="D56" s="14" t="inlineStr">
-        <is>
-          <t>Spot Alpha</t>
-        </is>
-      </c>
-      <c r="E56" s="81" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="F56" s="13" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="G56" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 9–10</t>
-        </is>
-      </c>
-      <c r="H56" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I56" s="14" t="inlineStr">
-        <is>
-          <t>Core city module, location management</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="9" t="n">
-        <v>38</v>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>Spot</t>
-        </is>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="inlineStr">
-        <is>
-          <t>Spot MVP</t>
-        </is>
-      </c>
-      <c r="E57" s="69" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 17–18</t>
-        </is>
-      </c>
-      <c r="H57" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I57" s="10" t="inlineStr">
-        <is>
-          <t>City management, geolocation features, admin dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="13" t="inlineStr"/>
-      <c r="B58" s="18" t="inlineStr">
-        <is>
-          <t>Spot</t>
-        </is>
-      </c>
-      <c r="C58" s="13" t="n"/>
-      <c r="D58" s="14" t="n"/>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="13" t="n"/>
-      <c r="G58" s="13" t="n"/>
-      <c r="H58" s="13" t="n"/>
-      <c r="I58" s="14" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="9" t="inlineStr"/>
-      <c r="B59" s="72" t="inlineStr">
-        <is>
-          <t>Spot</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="n"/>
-      <c r="D59" s="10" t="n"/>
-      <c r="E59" s="9" t="n"/>
-      <c r="F59" s="9" t="n"/>
-      <c r="G59" s="9" t="n"/>
-      <c r="H59" s="9" t="n"/>
-      <c r="I59" s="10" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="13" t="inlineStr"/>
-      <c r="B60" s="18" t="inlineStr">
-        <is>
-          <t>Spot</t>
-        </is>
-      </c>
-      <c r="C60" s="13" t="n"/>
-      <c r="D60" s="14" t="n"/>
-      <c r="E60" s="13" t="n"/>
-      <c r="F60" s="13" t="n"/>
-      <c r="G60" s="13" t="n"/>
-      <c r="H60" s="13" t="n"/>
-      <c r="I60" s="14" t="n"/>
-    </row>
-    <row r="61"/>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="84" t="inlineStr">
-        <is>
-          <t>Pulse  —  Released: 0  •  Hotfixes: 0  •  Planned: 2  •  Latest: —  •  Next: v0.1.0</t>
-        </is>
-      </c>
-      <c r="B62" s="85" t="n"/>
-      <c r="C62" s="85" t="n"/>
-      <c r="D62" s="85" t="n"/>
-      <c r="E62" s="85" t="n"/>
-      <c r="F62" s="85" t="n"/>
-      <c r="G62" s="85" t="n"/>
-      <c r="H62" s="85" t="n"/>
-      <c r="I62" s="85" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="68" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B63" s="68" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="C63" s="68" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="D63" s="68" t="inlineStr">
-        <is>
-          <t>Release Name</t>
-        </is>
-      </c>
-      <c r="E63" s="68" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="F63" s="68" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="G63" s="68" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="H63" s="68" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I63" s="68" t="inlineStr">
-        <is>
-          <t>Highlights / What's Included</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="13" t="n">
-        <v>42</v>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>Pulse</t>
-        </is>
-      </c>
-      <c r="C64" s="13" t="inlineStr">
-        <is>
-          <t>v0.1.0</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>Pulse Alpha</t>
-        </is>
-      </c>
-      <c r="E64" s="81" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="F64" s="13" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="G64" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 9–10</t>
-        </is>
-      </c>
-      <c r="H64" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I64" s="14" t="inlineStr">
-        <is>
-          <t>Survey builder, basic distribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>Pulse</t>
-        </is>
-      </c>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>v1.0.0</t>
-        </is>
-      </c>
-      <c r="D65" s="10" t="inlineStr">
-        <is>
-          <t>Pulse MVP</t>
-        </is>
-      </c>
-      <c r="E65" s="69" t="inlineStr">
-        <is>
-          <t>MVP</t>
-        </is>
-      </c>
-      <c r="F65" s="9" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>Sprint 17–18</t>
-        </is>
-      </c>
-      <c r="H65" s="18" t="inlineStr">
-        <is>
-          <t>📋 Planned</t>
-        </is>
-      </c>
-      <c r="I65" s="10" t="inlineStr">
-        <is>
-          <t>Survey analytics, employee engagement dashboards, benchmarking</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="13" t="inlineStr"/>
-      <c r="B66" s="18" t="inlineStr">
-        <is>
-          <t>Pulse</t>
-        </is>
-      </c>
-      <c r="C66" s="13" t="n"/>
-      <c r="D66" s="14" t="n"/>
-      <c r="E66" s="13" t="n"/>
-      <c r="F66" s="13" t="n"/>
-      <c r="G66" s="13" t="n"/>
-      <c r="H66" s="13" t="n"/>
-      <c r="I66" s="14" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="9" t="inlineStr"/>
-      <c r="B67" s="72" t="inlineStr">
-        <is>
-          <t>Pulse</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="n"/>
-      <c r="D67" s="10" t="n"/>
-      <c r="E67" s="9" t="n"/>
-      <c r="F67" s="9" t="n"/>
-      <c r="G67" s="9" t="n"/>
-      <c r="H67" s="9" t="n"/>
-      <c r="I67" s="10" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="13" t="inlineStr"/>
-      <c r="B68" s="18" t="inlineStr">
-        <is>
-          <t>Pulse</t>
-        </is>
-      </c>
-      <c r="C68" s="13" t="n"/>
-      <c r="D68" s="14" t="n"/>
-      <c r="E68" s="13" t="n"/>
-      <c r="F68" s="13" t="n"/>
-      <c r="G68" s="13" t="n"/>
-      <c r="H68" s="13" t="n"/>
-      <c r="I68" s="14" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A62:I62"/>
-    <mergeCell ref="A54:I54"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A17:B17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
